--- a/02-VALUATION/M06/bus311-valuation-m06-l01-starter.xlsx
+++ b/02-VALUATION/M06/bus311-valuation-m06-l01-starter.xlsx
@@ -2,14 +2,17 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="START HERE" sheetId="1" r:id="R928b2cf963b348c3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1 Assumptions-Baseline" sheetId="2" r:id="Rf41776540f714c21"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2 Bond Pricing" sheetId="3" r:id="Rd6aeb4253fed4f81"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3 Sources-Uses" sheetId="4" r:id="Rbaa930d729604cd7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="4 Scenario Impact" sheetId="5" r:id="R9d014ab127ec4ca8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5 Capacity-Decision" sheetId="6" r:id="Rfea223d977a64dc0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="6 Checks" sheetId="7" r:id="R926834358c8e46e1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BUS311 Guide" sheetId="8" r:id="R3b48228d9c504a2d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="START HERE" sheetId="1" r:id="R970e9f1f28fc46e8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Example 1 - At Par" sheetId="2" r:id="R0e5861704b554f50"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Example 2 - Premium" sheetId="3" r:id="R74f165e6597b465c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Example 3 - Discount" sheetId="4" r:id="Re7b44f1def7043ea"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1 Assumptions-Baseline" sheetId="5" r:id="Rab1492dd51a343c8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2 Bond Pricing" sheetId="6" r:id="R4c741c6ea79e4e25"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3 Sources-Uses" sheetId="7" r:id="Rdaf022011f31496e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="4 Scenario Impact" sheetId="8" r:id="Rb675859985d84a16"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5 Capacity-Decision" sheetId="9" r:id="R11b7b95b30164578"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="6 Checks" sheetId="10" r:id="Re0adc72e9d2f44fd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BUS311 Guide" sheetId="11" r:id="Rb174bc1498d546c7"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -20,15 +23,16 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="8">
-    <x:numFmt numFmtId="200" formatCode="#,##0;[Red](#,##0);-"/>
+  <x:numFmts count="9">
+    <x:numFmt numFmtId="200" formatCode="$#,##0.00;[Red]($#,##0.00);-"/>
     <x:numFmt numFmtId="201" formatCode="0.00%;[Red](0.00%);-"/>
-    <x:numFmt numFmtId="202" formatCode="$0.00;[Red]($0.00);-"/>
-    <x:numFmt numFmtId="203" formatCode="yyyy-mm-dd"/>
-    <x:numFmt numFmtId="204" formatCode="$#,##0.00;[Red]($#,##0.00);-"/>
-    <x:numFmt numFmtId="205" formatCode="0.00x;[Red](0.00x);-"/>
-    <x:numFmt numFmtId="206" formatCode="$#,##0.0;[Red]($#,##0.0);-"/>
-    <x:numFmt numFmtId="207" formatCode="@"/>
+    <x:numFmt numFmtId="202" formatCode="#,##0;[Red](#,##0);-"/>
+    <x:numFmt numFmtId="203" formatCode="0.0000"/>
+    <x:numFmt numFmtId="204" formatCode="@"/>
+    <x:numFmt numFmtId="205" formatCode="$0.00;[Red]($0.00);-"/>
+    <x:numFmt numFmtId="206" formatCode="yyyy-mm-dd"/>
+    <x:numFmt numFmtId="207" formatCode="0.00x;[Red](0.00x);-"/>
+    <x:numFmt numFmtId="208" formatCode="$#,##0.0;[Red]($#,##0.0);-"/>
   </x:numFmts>
   <x:fonts count="12">
     <x:font>
@@ -315,7 +319,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="150">
+  <x:cellXfs count="156">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -522,6 +526,12 @@
     <x:xf numFmtId="0" fontId="1" fillId="9" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
     <x:xf numFmtId="0" fontId="9" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center"/>
     </x:xf>
@@ -533,6 +543,15 @@
     </x:xf>
     <x:xf numFmtId="201" fontId="9" fillId="5" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="202" fontId="9" fillId="5" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="8" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="8" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="1" fillId="7" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center"/>
@@ -546,6 +565,24 @@
     <x:xf numFmtId="200" fontId="1" fillId="7" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="top" wrapText="1"/>
     </x:xf>
+    <x:xf numFmtId="203" fontId="1" fillId="7" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="203" fontId="1" fillId="7" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="203" fontId="1" fillId="7" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="204" fontId="1" fillId="7" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="204" fontId="1" fillId="7" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="204" fontId="1" fillId="7" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
     <x:xf numFmtId="202" fontId="1" fillId="7" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center"/>
     </x:xf>
@@ -555,10 +592,16 @@
     <x:xf numFmtId="202" fontId="1" fillId="7" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="top" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="203" fontId="9" fillId="5" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="204" fontId="9" fillId="5" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="205" fontId="1" fillId="7" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="205" fontId="1" fillId="7" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="205" fontId="1" fillId="7" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="206" fontId="9" fillId="5" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center"/>
     </x:xf>
     <x:xf numFmtId="201" fontId="1" fillId="7" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -573,7 +616,7 @@
     <x:xf numFmtId="0" fontId="9" fillId="5" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center"/>
     </x:xf>
-    <x:xf numFmtId="205" fontId="9" fillId="5" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="207" fontId="9" fillId="5" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="5" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -606,40 +649,28 @@
     <x:xf numFmtId="0" fontId="10" fillId="8" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center"/>
     </x:xf>
-    <x:xf numFmtId="200" fontId="10" fillId="8" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="202" fontId="10" fillId="8" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center"/>
     </x:xf>
     <x:xf numFmtId="201" fontId="10" fillId="8" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center"/>
     </x:xf>
-    <x:xf numFmtId="203" fontId="10" fillId="8" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="204" fontId="1" fillId="7" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="204" fontId="1" fillId="7" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="206" fontId="10" fillId="8" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="208" fontId="1" fillId="7" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="208" fontId="1" fillId="7" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="204" fontId="1" fillId="7" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="208" fontId="1" fillId="7" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="top" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="206" fontId="1" fillId="7" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="206" fontId="1" fillId="7" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="206" fontId="1" fillId="7" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="top" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="8" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="1" fillId="8" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="206" fontId="10" fillId="8" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="208" fontId="10" fillId="8" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -648,62 +679,53 @@
     <x:xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center"/>
     </x:xf>
-    <x:xf numFmtId="206" fontId="1" fillId="8" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="208" fontId="1" fillId="8" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="top" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="206" fontId="8" fillId="8" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="206" fontId="7" fillId="8" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="208" fontId="8" fillId="8" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="208" fontId="7" fillId="8" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="top" wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="7" fillId="8" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center"/>
     </x:xf>
-    <x:xf numFmtId="206" fontId="8" fillId="8" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="206" fontId="7" fillId="8" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="208" fontId="8" fillId="8" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="208" fontId="7" fillId="8" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="top" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="206" fontId="7" fillId="8" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="208" fontId="7" fillId="8" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="top" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="206" fontId="7" fillId="8" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="202" fontId="10" fillId="8" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="202" fontId="1" fillId="8" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="208" fontId="7" fillId="8" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="205" fontId="10" fillId="8" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="205" fontId="1" fillId="8" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="top" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="202" fontId="8" fillId="8" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="202" fontId="7" fillId="8" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="205" fontId="8" fillId="8" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="205" fontId="7" fillId="8" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="top" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="202" fontId="8" fillId="8" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="202" fontId="7" fillId="8" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="205" fontId="8" fillId="8" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="205" fontId="7" fillId="8" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="top" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="202" fontId="7" fillId="8" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="205" fontId="7" fillId="8" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="top" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="202" fontId="7" fillId="8" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="205" fontId="1" fillId="7" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="205" fontId="1" fillId="7" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="205" fontId="1" fillId="7" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="top" wrapText="1"/>
+    <x:xf numFmtId="205" fontId="7" fillId="8" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
     </x:xf>
     <x:xf numFmtId="207" fontId="1" fillId="7" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center"/>
@@ -744,22 +766,22 @@
     <x:xf numFmtId="0" fontId="11" fillId="10" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center"/>
     </x:xf>
-    <x:xf numFmtId="204" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="200" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center"/>
     </x:xf>
     <x:xf numFmtId="201" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center"/>
     </x:xf>
-    <x:xf numFmtId="205" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="204" fontId="1" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="207" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="1" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center"/>
     </x:xf>
     <x:xf numFmtId="201" fontId="1" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center"/>
     </x:xf>
-    <x:xf numFmtId="205" fontId="1" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="207" fontId="1" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center"/>
     </x:xf>
   </x:cellXfs>
@@ -1033,7 +1055,7 @@
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="8" t="str">
-        <x:v>Meridian Industrial Corp. · student starter · $ thousands unless noted · Version 2026-07-28</x:v>
+        <x:v>Meridian Industrial Corp. · student starter · $ thousands unless noted · Version 2026-09-29</x:v>
       </x:c>
       <x:c r="B3" s="8"/>
       <x:c r="C3" s="8"/>
@@ -1499,15 +1521,49 @@
       <x:c r="G37" s="2"/>
       <x:c r="H37" s="2"/>
     </x:row>
-    <x:row r="38">
-      <x:c r="A38" s="2"/>
-      <x:c r="B38" s="2"/>
-      <x:c r="C38" s="2"/>
-      <x:c r="D38" s="2"/>
-      <x:c r="E38" s="2"/>
-      <x:c r="F38" s="2"/>
-      <x:c r="G38" s="2"/>
-      <x:c r="H38" s="2"/>
+    <x:row r="38" ht="22" customHeight="1">
+      <x:c r="A38" s="27" t="str">
+        <x:v>Canva cash-flow warm-up</x:v>
+      </x:c>
+      <x:c r="B38" s="27"/>
+      <x:c r="C38" s="27"/>
+      <x:c r="D38" s="27"/>
+      <x:c r="E38" s="27"/>
+      <x:c r="F38" s="27"/>
+      <x:c r="G38" s="27"/>
+      <x:c r="H38" s="27"/>
+    </x:row>
+    <x:row r="39" ht="25" customHeight="1">
+      <x:c r="A39" s="18" t="str">
+        <x:v>Complete the three-year bond examples at 5%, 3%, and 7% market yields before building Meridian’s ten-year bond. Keep the $1,000 face value and 5% coupon fixed; use each tab to show how discounting changes the price.</x:v>
+      </x:c>
+      <x:c r="B39" s="19"/>
+      <x:c r="C39" s="19"/>
+      <x:c r="D39" s="19"/>
+      <x:c r="E39" s="19"/>
+      <x:c r="F39" s="19"/>
+      <x:c r="G39" s="19"/>
+      <x:c r="H39" s="20"/>
+    </x:row>
+    <x:row r="40" ht="25" customHeight="1">
+      <x:c r="A40" s="21"/>
+      <x:c r="B40" s="22"/>
+      <x:c r="C40" s="22"/>
+      <x:c r="D40" s="22"/>
+      <x:c r="E40" s="22"/>
+      <x:c r="F40" s="22"/>
+      <x:c r="G40" s="22"/>
+      <x:c r="H40" s="23"/>
+    </x:row>
+    <x:row r="41" ht="25" customHeight="1">
+      <x:c r="A41" s="24"/>
+      <x:c r="B41" s="25"/>
+      <x:c r="C41" s="25"/>
+      <x:c r="D41" s="25"/>
+      <x:c r="E41" s="25"/>
+      <x:c r="F41" s="25"/>
+      <x:c r="G41" s="25"/>
+      <x:c r="H41" s="26"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -1519,12 +1575,2508 @@
     <x:mergeCell ref="A26:H26"/>
     <x:mergeCell ref="A32:H32"/>
     <x:mergeCell ref="A33:H36"/>
+    <x:mergeCell ref="A38:H38"/>
+    <x:mergeCell ref="A39:H41"/>
+  </x:mergeCells>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="38" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="19" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="19" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="19" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="14" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="16" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="45" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="30" customHeight="1">
+      <x:c r="A1" s="5" t="str">
+        <x:v>Meridian — Model Checks and Scenario Tie-Outs</x:v>
+      </x:c>
+      <x:c r="B1" s="5"/>
+      <x:c r="C1" s="5"/>
+      <x:c r="D1" s="5"/>
+      <x:c r="E1" s="5"/>
+      <x:c r="F1" s="5"/>
+      <x:c r="G1" s="5"/>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2" s="2"/>
+      <x:c r="B2" s="2"/>
+      <x:c r="C2" s="2"/>
+      <x:c r="D2" s="2"/>
+      <x:c r="E2" s="2"/>
+      <x:c r="F2" s="2"/>
+      <x:c r="G2" s="2"/>
+    </x:row>
+    <x:row r="3">
+      <x:c r="A3" s="149" t="str">
+        <x:v>MODEL STATUS</x:v>
+      </x:c>
+      <x:c r="B3" s="149" t="str">
+        <x:f>IF(COUNTIF(F7:F39,"CHECK")&gt;0,"FAIL",IF(COUNTIF(F7:F39,"COMPLETE")&gt;0,"COMPLETE MODEL","PASS"))</x:f>
+        <x:v>COMPLETE MODEL</x:v>
+      </x:c>
+      <x:c r="C3" s="149"/>
+      <x:c r="D3" s="149"/>
+      <x:c r="E3" s="2"/>
+      <x:c r="F3" s="2"/>
+      <x:c r="G3" s="2"/>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" s="2"/>
+      <x:c r="B4" s="2"/>
+      <x:c r="C4" s="2"/>
+      <x:c r="D4" s="2"/>
+      <x:c r="E4" s="2"/>
+      <x:c r="F4" s="2"/>
+      <x:c r="G4" s="2"/>
+    </x:row>
+    <x:row r="5" ht="22" customHeight="1">
+      <x:c r="A5" s="27" t="str">
+        <x:v>One assertion per row — do not proceed while a completed row says CHECK</x:v>
+      </x:c>
+      <x:c r="B5" s="27"/>
+      <x:c r="C5" s="27"/>
+      <x:c r="D5" s="27"/>
+      <x:c r="E5" s="27"/>
+      <x:c r="F5" s="27"/>
+      <x:c r="G5" s="27"/>
+    </x:row>
+    <x:row r="6" ht="27" customHeight="1">
+      <x:c r="A6" s="38" t="str">
+        <x:v>Check</x:v>
+      </x:c>
+      <x:c r="B6" s="38" t="str">
+        <x:v>Actual</x:v>
+      </x:c>
+      <x:c r="C6" s="38" t="str">
+        <x:v>Expected</x:v>
+      </x:c>
+      <x:c r="D6" s="38" t="str">
+        <x:v>Difference</x:v>
+      </x:c>
+      <x:c r="E6" s="38" t="str">
+        <x:v>Tolerance</x:v>
+      </x:c>
+      <x:c r="F6" s="38" t="str">
+        <x:v>Status</x:v>
+      </x:c>
+      <x:c r="G6" s="38" t="str">
+        <x:v>Where to fix / meaning</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="27" customHeight="1">
+      <x:c r="A7" s="2" t="str">
+        <x:v>Baseline balance sheet</x:v>
+      </x:c>
+      <x:c r="B7" s="153" t="str">
+        <x:f>IF(ISBLANK('1 Assumptions-Baseline'!B31),"",'1 Assumptions-Baseline'!B31)</x:f>
+      </x:c>
+      <x:c r="C7" s="153" t="str">
+        <x:f>IF(ISBLANK('1 Assumptions-Baseline'!F34),"",'1 Assumptions-Baseline'!F34)</x:f>
+      </x:c>
+      <x:c r="D7" s="153" t="str">
+        <x:f>IF(OR(NOT(ISNUMBER(B7)),NOT(ISNUMBER(C7))),"",B7-C7)</x:f>
+      </x:c>
+      <x:c r="E7" s="153" t="n">
+        <x:v>0.1</x:v>
+      </x:c>
+      <x:c r="F7" s="32" t="str">
+        <x:f>IF(OR(NOT(ISNUMBER(B7)),NOT(ISNUMBER(C7))),"COMPLETE",IF(ABS(D7)&lt;=E7,"OK","CHECK"))</x:f>
+        <x:v>COMPLETE</x:v>
+      </x:c>
+      <x:c r="G7" s="33" t="str">
+        <x:v>1 Assumptions-Baseline · Total Assets vs L+E</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="27" customHeight="1">
+      <x:c r="A8" s="2" t="str">
+        <x:v>Baseline tax expense sign</x:v>
+      </x:c>
+      <x:c r="B8" s="153" t="n">
+        <x:f>'1 Assumptions-Baseline'!B16</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C8" s="153" t="str">
+        <x:f>IF('1 Assumptions-Baseline'!B14="","",MAX('1 Assumptions-Baseline'!B14,0)*'1 Assumptions-Baseline'!B15)</x:f>
+      </x:c>
+      <x:c r="D8" s="153" t="str">
+        <x:f>IF(OR(NOT(ISNUMBER(B8)),NOT(ISNUMBER(C8))),"",B8-C8)</x:f>
+      </x:c>
+      <x:c r="E8" s="153" t="n">
+        <x:v>0.1</x:v>
+      </x:c>
+      <x:c r="F8" s="32" t="str">
+        <x:f>IF(OR(NOT(ISNUMBER(B8)),NOT(ISNUMBER(C8))),"COMPLETE",IF(ABS(D8)&lt;=E8,"OK","CHECK"))</x:f>
+        <x:v>COMPLETE</x:v>
+      </x:c>
+      <x:c r="G8" s="33" t="str">
+        <x:v>Tax expense must be positive</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="27" customHeight="1">
+      <x:c r="A9" s="2" t="str">
+        <x:v>Baseline net income</x:v>
+      </x:c>
+      <x:c r="B9" s="153" t="n">
+        <x:f>'1 Assumptions-Baseline'!B17</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C9" s="153" t="str">
+        <x:f>IF(OR('1 Assumptions-Baseline'!B14="",'1 Assumptions-Baseline'!B16=""),"",'1 Assumptions-Baseline'!B14-'1 Assumptions-Baseline'!B16)</x:f>
+      </x:c>
+      <x:c r="D9" s="153" t="str">
+        <x:f>IF(OR(NOT(ISNUMBER(B9)),NOT(ISNUMBER(C9))),"",B9-C9)</x:f>
+      </x:c>
+      <x:c r="E9" s="153" t="n">
+        <x:v>0.1</x:v>
+      </x:c>
+      <x:c r="F9" s="32" t="str">
+        <x:f>IF(OR(NOT(ISNUMBER(B9)),NOT(ISNUMBER(C9))),"COMPLETE",IF(ABS(D9)&lt;=E9,"OK","CHECK"))</x:f>
+        <x:v>COMPLETE</x:v>
+      </x:c>
+      <x:c r="G9" s="33" t="str">
+        <x:v>EBT − tax expense</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="27" customHeight="1">
+      <x:c r="A10" s="2" t="str">
+        <x:v>Baseline EPS</x:v>
+      </x:c>
+      <x:c r="B10" s="153" t="n">
+        <x:f>'1 Assumptions-Baseline'!B19</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C10" s="153" t="str">
+        <x:f>IF(OR('1 Assumptions-Baseline'!B17="",'1 Assumptions-Baseline'!B18=""),"",'1 Assumptions-Baseline'!B17/'1 Assumptions-Baseline'!B18)</x:f>
+      </x:c>
+      <x:c r="D10" s="153" t="str">
+        <x:f>IF(OR(NOT(ISNUMBER(B10)),NOT(ISNUMBER(C10))),"",B10-C10)</x:f>
+      </x:c>
+      <x:c r="E10" s="153" t="n">
+        <x:v>0.0001</x:v>
+      </x:c>
+      <x:c r="F10" s="32" t="str">
+        <x:f>IF(OR(NOT(ISNUMBER(B10)),NOT(ISNUMBER(C10))),"COMPLETE",IF(ABS(D10)&lt;=E10,"OK","CHECK"))</x:f>
+        <x:v>COMPLETE</x:v>
+      </x:c>
+      <x:c r="G10" s="33" t="str">
+        <x:v>Net income ÷ shares</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="27" customHeight="1">
+      <x:c r="A11" s="2" t="str">
+        <x:v>PV vs PRICE</x:v>
+      </x:c>
+      <x:c r="B11" s="153" t="str">
+        <x:f>IF(ISBLANK('2 Bond Pricing'!B24),"",'2 Bond Pricing'!B24)</x:f>
+      </x:c>
+      <x:c r="C11" s="153" t="n">
+        <x:f>0</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D11" s="153" t="str">
+        <x:f>IF(OR(NOT(ISNUMBER(B11)),NOT(ISNUMBER(C11))),"",B11-C11)</x:f>
+      </x:c>
+      <x:c r="E11" s="153" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+      <x:c r="F11" s="32" t="str">
+        <x:f>IF(OR(NOT(ISNUMBER(B11)),NOT(ISNUMBER(C11))),"COMPLETE",IF(ABS(D11)&lt;=E11,"OK","CHECK"))</x:f>
+        <x:v>COMPLETE</x:v>
+      </x:c>
+      <x:c r="G11" s="33" t="str">
+        <x:v>2 Bond Pricing · settlement is a coupon date</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="27" customHeight="1">
+      <x:c r="A12" s="2" t="str">
+        <x:v>Gross proceeds calculation</x:v>
+      </x:c>
+      <x:c r="B12" s="153" t="n">
+        <x:f>'2 Bond Pricing'!B25</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C12" s="153" t="str">
+        <x:f>IF('2 Bond Pricing'!B22="","",'2 Bond Pricing'!B22*'2 Bond Pricing'!B8/1000)</x:f>
+      </x:c>
+      <x:c r="D12" s="153" t="str">
+        <x:f>IF(OR(NOT(ISNUMBER(B12)),NOT(ISNUMBER(C12))),"",B12-C12)</x:f>
+      </x:c>
+      <x:c r="E12" s="153" t="n">
+        <x:v>0.1</x:v>
+      </x:c>
+      <x:c r="F12" s="32" t="str">
+        <x:f>IF(OR(NOT(ISNUMBER(B12)),NOT(ISNUMBER(C12))),"COMPLETE",IF(ABS(D12)&lt;=E12,"OK","CHECK"))</x:f>
+        <x:v>COMPLETE</x:v>
+      </x:c>
+      <x:c r="G12" s="33" t="str">
+        <x:v>Price × bonds ÷ 1,000</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" ht="27" customHeight="1">
+      <x:c r="A13" s="2" t="str">
+        <x:v>Scenario A sources and uses</x:v>
+      </x:c>
+      <x:c r="B13" s="153" t="str">
+        <x:f>IF(ISBLANK('3 Sources-Uses'!B14),"",'3 Sources-Uses'!B14)</x:f>
+      </x:c>
+      <x:c r="C13" s="153" t="n">
+        <x:f>0</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D13" s="153" t="str">
+        <x:f>IF(OR(NOT(ISNUMBER(B13)),NOT(ISNUMBER(C13))),"",B13-C13)</x:f>
+      </x:c>
+      <x:c r="E13" s="153" t="n">
+        <x:v>0.1</x:v>
+      </x:c>
+      <x:c r="F13" s="32" t="str">
+        <x:f>IF(OR(NOT(ISNUMBER(B13)),NOT(ISNUMBER(C13))),"COMPLETE",IF(ABS(D13)&lt;=E13,"OK","CHECK"))</x:f>
+        <x:v>COMPLETE</x:v>
+      </x:c>
+      <x:c r="G13" s="33" t="str">
+        <x:v>3 Sources-Uses</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" ht="27" customHeight="1">
+      <x:c r="A14" s="2" t="str">
+        <x:v>Scenario B sources and uses</x:v>
+      </x:c>
+      <x:c r="B14" s="153" t="str">
+        <x:f>IF(ISBLANK('3 Sources-Uses'!C14),"",'3 Sources-Uses'!C14)</x:f>
+      </x:c>
+      <x:c r="C14" s="153" t="n">
+        <x:f>0</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D14" s="153" t="str">
+        <x:f>IF(OR(NOT(ISNUMBER(B14)),NOT(ISNUMBER(C14))),"",B14-C14)</x:f>
+      </x:c>
+      <x:c r="E14" s="153" t="n">
+        <x:v>0.1</x:v>
+      </x:c>
+      <x:c r="F14" s="32" t="str">
+        <x:f>IF(OR(NOT(ISNUMBER(B14)),NOT(ISNUMBER(C14))),"COMPLETE",IF(ABS(D14)&lt;=E14,"OK","CHECK"))</x:f>
+        <x:v>COMPLETE</x:v>
+      </x:c>
+      <x:c r="G14" s="33" t="str">
+        <x:v>3 Sources-Uses</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" ht="27" customHeight="1">
+      <x:c r="A15" s="2" t="str">
+        <x:v>Scenario C sources and uses</x:v>
+      </x:c>
+      <x:c r="B15" s="153" t="str">
+        <x:f>IF(ISBLANK('3 Sources-Uses'!D14),"",'3 Sources-Uses'!D14)</x:f>
+      </x:c>
+      <x:c r="C15" s="153" t="n">
+        <x:f>0</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D15" s="153" t="str">
+        <x:f>IF(OR(NOT(ISNUMBER(B15)),NOT(ISNUMBER(C15))),"",B15-C15)</x:f>
+      </x:c>
+      <x:c r="E15" s="153" t="n">
+        <x:v>0.1</x:v>
+      </x:c>
+      <x:c r="F15" s="32" t="str">
+        <x:f>IF(OR(NOT(ISNUMBER(B15)),NOT(ISNUMBER(C15))),"COMPLETE",IF(ABS(D15)&lt;=E15,"OK","CHECK"))</x:f>
+        <x:v>COMPLETE</x:v>
+      </x:c>
+      <x:c r="G15" s="33" t="str">
+        <x:v>3 Sources-Uses</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" ht="27" customHeight="1">
+      <x:c r="A16" s="2" t="str">
+        <x:v>Scenario A net proceeds deployed</x:v>
+      </x:c>
+      <x:c r="B16" s="153" t="str">
+        <x:f>IF(ISBLANK('3 Sources-Uses'!B18),"",'3 Sources-Uses'!B18)</x:f>
+      </x:c>
+      <x:c r="C16" s="153" t="n">
+        <x:f>0</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D16" s="153" t="str">
+        <x:f>IF(OR(NOT(ISNUMBER(B16)),NOT(ISNUMBER(C16))),"",B16-C16)</x:f>
+      </x:c>
+      <x:c r="E16" s="153" t="n">
+        <x:v>0.1</x:v>
+      </x:c>
+      <x:c r="F16" s="32" t="str">
+        <x:f>IF(OR(NOT(ISNUMBER(B16)),NOT(ISNUMBER(C16))),"COMPLETE",IF(ABS(D16)&lt;=E16,"OK","CHECK"))</x:f>
+        <x:v>COMPLETE</x:v>
+      </x:c>
+      <x:c r="G16" s="33" t="str">
+        <x:v>Refi + CapEx + cash retained</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" ht="27" customHeight="1">
+      <x:c r="A17" s="2" t="str">
+        <x:v>Scenario B net proceeds deployed</x:v>
+      </x:c>
+      <x:c r="B17" s="153" t="str">
+        <x:f>IF(ISBLANK('3 Sources-Uses'!C18),"",'3 Sources-Uses'!C18)</x:f>
+      </x:c>
+      <x:c r="C17" s="153" t="n">
+        <x:f>0</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D17" s="153" t="str">
+        <x:f>IF(OR(NOT(ISNUMBER(B17)),NOT(ISNUMBER(C17))),"",B17-C17)</x:f>
+      </x:c>
+      <x:c r="E17" s="153" t="n">
+        <x:v>0.1</x:v>
+      </x:c>
+      <x:c r="F17" s="32" t="str">
+        <x:f>IF(OR(NOT(ISNUMBER(B17)),NOT(ISNUMBER(C17))),"COMPLETE",IF(ABS(D17)&lt;=E17,"OK","CHECK"))</x:f>
+        <x:v>COMPLETE</x:v>
+      </x:c>
+      <x:c r="G17" s="33" t="str">
+        <x:v>Refi + CapEx + cash retained</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" ht="27" customHeight="1">
+      <x:c r="A18" s="2" t="str">
+        <x:v>Scenario C net proceeds deployed</x:v>
+      </x:c>
+      <x:c r="B18" s="153" t="str">
+        <x:f>IF(ISBLANK('3 Sources-Uses'!D18),"",'3 Sources-Uses'!D18)</x:f>
+      </x:c>
+      <x:c r="C18" s="153" t="n">
+        <x:f>0</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D18" s="153" t="str">
+        <x:f>IF(OR(NOT(ISNUMBER(B18)),NOT(ISNUMBER(C18))),"",B18-C18)</x:f>
+      </x:c>
+      <x:c r="E18" s="153" t="n">
+        <x:v>0.1</x:v>
+      </x:c>
+      <x:c r="F18" s="32" t="str">
+        <x:f>IF(OR(NOT(ISNUMBER(B18)),NOT(ISNUMBER(C18))),"COMPLETE",IF(ABS(D18)&lt;=E18,"OK","CHECK"))</x:f>
+        <x:v>COMPLETE</x:v>
+      </x:c>
+      <x:c r="G18" s="33" t="str">
+        <x:v>Refi + CapEx + cash retained</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" ht="27" customHeight="1">
+      <x:c r="A19" s="2" t="str">
+        <x:v>Scenario A debt face/carrying bridge</x:v>
+      </x:c>
+      <x:c r="B19" s="153" t="str">
+        <x:f>IF(ISBLANK('3 Sources-Uses'!B30),"",'3 Sources-Uses'!B30)</x:f>
+      </x:c>
+      <x:c r="C19" s="153" t="n">
+        <x:f>0</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D19" s="153" t="str">
+        <x:f>IF(OR(NOT(ISNUMBER(B19)),NOT(ISNUMBER(C19))),"",B19-C19)</x:f>
+      </x:c>
+      <x:c r="E19" s="153" t="n">
+        <x:v>0.1</x:v>
+      </x:c>
+      <x:c r="F19" s="32" t="str">
+        <x:f>IF(OR(NOT(ISNUMBER(B19)),NOT(ISNUMBER(C19))),"COMPLETE",IF(ABS(D19)&lt;=E19,"OK","CHECK"))</x:f>
+        <x:v>COMPLETE</x:v>
+      </x:c>
+      <x:c r="G19" s="33" t="str">
+        <x:v>Face − carrying − contra-debt</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" ht="27" customHeight="1">
+      <x:c r="A20" s="2" t="str">
+        <x:v>Scenario B debt face/carrying bridge</x:v>
+      </x:c>
+      <x:c r="B20" s="153" t="str">
+        <x:f>IF(ISBLANK('3 Sources-Uses'!C30),"",'3 Sources-Uses'!C30)</x:f>
+      </x:c>
+      <x:c r="C20" s="153" t="n">
+        <x:f>0</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D20" s="153" t="str">
+        <x:f>IF(OR(NOT(ISNUMBER(B20)),NOT(ISNUMBER(C20))),"",B20-C20)</x:f>
+      </x:c>
+      <x:c r="E20" s="153" t="n">
+        <x:v>0.1</x:v>
+      </x:c>
+      <x:c r="F20" s="32" t="str">
+        <x:f>IF(OR(NOT(ISNUMBER(B20)),NOT(ISNUMBER(C20))),"COMPLETE",IF(ABS(D20)&lt;=E20,"OK","CHECK"))</x:f>
+        <x:v>COMPLETE</x:v>
+      </x:c>
+      <x:c r="G20" s="33" t="str">
+        <x:v>Face − carrying − contra-debt</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" ht="27" customHeight="1">
+      <x:c r="A21" s="2" t="str">
+        <x:v>Scenario C debt face/carrying bridge</x:v>
+      </x:c>
+      <x:c r="B21" s="153" t="str">
+        <x:f>IF(ISBLANK('3 Sources-Uses'!D30),"",'3 Sources-Uses'!D30)</x:f>
+      </x:c>
+      <x:c r="C21" s="153" t="n">
+        <x:f>0</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D21" s="153" t="str">
+        <x:f>IF(OR(NOT(ISNUMBER(B21)),NOT(ISNUMBER(C21))),"",B21-C21)</x:f>
+      </x:c>
+      <x:c r="E21" s="153" t="n">
+        <x:v>0.1</x:v>
+      </x:c>
+      <x:c r="F21" s="32" t="str">
+        <x:f>IF(OR(NOT(ISNUMBER(B21)),NOT(ISNUMBER(C21))),"COMPLETE",IF(ABS(D21)&lt;=E21,"OK","CHECK"))</x:f>
+        <x:v>COMPLETE</x:v>
+      </x:c>
+      <x:c r="G21" s="33" t="str">
+        <x:v>Face − carrying − contra-debt</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" ht="27" customHeight="1">
+      <x:c r="A22" s="2" t="str">
+        <x:v>Scenario A balance sheet</x:v>
+      </x:c>
+      <x:c r="B22" s="153" t="str">
+        <x:f>IF(ISBLANK('4 Scenario Impact'!C27),"",'4 Scenario Impact'!C27)</x:f>
+      </x:c>
+      <x:c r="C22" s="153" t="n">
+        <x:f>0</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D22" s="153" t="str">
+        <x:f>IF(OR(NOT(ISNUMBER(B22)),NOT(ISNUMBER(C22))),"",B22-C22)</x:f>
+      </x:c>
+      <x:c r="E22" s="153" t="n">
+        <x:v>0.1</x:v>
+      </x:c>
+      <x:c r="F22" s="32" t="str">
+        <x:f>IF(OR(NOT(ISNUMBER(B22)),NOT(ISNUMBER(C22))),"COMPLETE",IF(ABS(D22)&lt;=E22,"OK","CHECK"))</x:f>
+        <x:v>COMPLETE</x:v>
+      </x:c>
+      <x:c r="G22" s="33" t="str">
+        <x:v>4 Scenario Impact</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" ht="27" customHeight="1">
+      <x:c r="A23" s="2" t="str">
+        <x:v>Scenario B balance sheet</x:v>
+      </x:c>
+      <x:c r="B23" s="153" t="str">
+        <x:f>IF(ISBLANK('4 Scenario Impact'!D27),"",'4 Scenario Impact'!D27)</x:f>
+      </x:c>
+      <x:c r="C23" s="153" t="n">
+        <x:f>0</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D23" s="153" t="str">
+        <x:f>IF(OR(NOT(ISNUMBER(B23)),NOT(ISNUMBER(C23))),"",B23-C23)</x:f>
+      </x:c>
+      <x:c r="E23" s="153" t="n">
+        <x:v>0.1</x:v>
+      </x:c>
+      <x:c r="F23" s="32" t="str">
+        <x:f>IF(OR(NOT(ISNUMBER(B23)),NOT(ISNUMBER(C23))),"COMPLETE",IF(ABS(D23)&lt;=E23,"OK","CHECK"))</x:f>
+        <x:v>COMPLETE</x:v>
+      </x:c>
+      <x:c r="G23" s="33" t="str">
+        <x:v>4 Scenario Impact</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" ht="27" customHeight="1">
+      <x:c r="A24" s="2" t="str">
+        <x:v>Scenario C balance sheet</x:v>
+      </x:c>
+      <x:c r="B24" s="153" t="str">
+        <x:f>IF(ISBLANK('4 Scenario Impact'!E27),"",'4 Scenario Impact'!E27)</x:f>
+      </x:c>
+      <x:c r="C24" s="153" t="n">
+        <x:f>0</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D24" s="153" t="str">
+        <x:f>IF(OR(NOT(ISNUMBER(B24)),NOT(ISNUMBER(C24))),"",B24-C24)</x:f>
+      </x:c>
+      <x:c r="E24" s="153" t="n">
+        <x:v>0.1</x:v>
+      </x:c>
+      <x:c r="F24" s="32" t="str">
+        <x:f>IF(OR(NOT(ISNUMBER(B24)),NOT(ISNUMBER(C24))),"COMPLETE",IF(ABS(D24)&lt;=E24,"OK","CHECK"))</x:f>
+        <x:v>COMPLETE</x:v>
+      </x:c>
+      <x:c r="G24" s="33" t="str">
+        <x:v>4 Scenario Impact</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" ht="27" customHeight="1">
+      <x:c r="A25" s="2" t="str">
+        <x:v>Scenario A ending ST debt</x:v>
+      </x:c>
+      <x:c r="B25" s="153" t="str">
+        <x:f>IF(ISBLANK('3 Sources-Uses'!B24),"",'3 Sources-Uses'!B24)</x:f>
+      </x:c>
+      <x:c r="C25" s="153" t="str">
+        <x:f>IF(OR(ISBLANK('3 Sources-Uses'!B22),ISBLANK('3 Sources-Uses'!B23)),"",'3 Sources-Uses'!B22-'3 Sources-Uses'!B23)</x:f>
+      </x:c>
+      <x:c r="D25" s="153" t="str">
+        <x:f>IF(OR(NOT(ISNUMBER(B25)),NOT(ISNUMBER(C25))),"",B25-C25)</x:f>
+      </x:c>
+      <x:c r="E25" s="153" t="n">
+        <x:v>0.1</x:v>
+      </x:c>
+      <x:c r="F25" s="32" t="str">
+        <x:f>IF(OR(NOT(ISNUMBER(B25)),NOT(ISNUMBER(C25))),"COMPLETE",IF(ABS(D25)&lt;=E25,"OK","CHECK"))</x:f>
+        <x:v>COMPLETE</x:v>
+      </x:c>
+      <x:c r="G25" s="33" t="str">
+        <x:v>Beginning ST − refinancing</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" ht="27" customHeight="1">
+      <x:c r="A26" s="2" t="str">
+        <x:v>Scenario B ending ST debt</x:v>
+      </x:c>
+      <x:c r="B26" s="153" t="str">
+        <x:f>IF(ISBLANK('3 Sources-Uses'!C24),"",'3 Sources-Uses'!C24)</x:f>
+      </x:c>
+      <x:c r="C26" s="153" t="str">
+        <x:f>IF(OR(ISBLANK('3 Sources-Uses'!C22),ISBLANK('3 Sources-Uses'!C23)),"",'3 Sources-Uses'!C22-'3 Sources-Uses'!C23)</x:f>
+      </x:c>
+      <x:c r="D26" s="153" t="str">
+        <x:f>IF(OR(NOT(ISNUMBER(B26)),NOT(ISNUMBER(C26))),"",B26-C26)</x:f>
+      </x:c>
+      <x:c r="E26" s="153" t="n">
+        <x:v>0.1</x:v>
+      </x:c>
+      <x:c r="F26" s="32" t="str">
+        <x:f>IF(OR(NOT(ISNUMBER(B26)),NOT(ISNUMBER(C26))),"COMPLETE",IF(ABS(D26)&lt;=E26,"OK","CHECK"))</x:f>
+        <x:v>COMPLETE</x:v>
+      </x:c>
+      <x:c r="G26" s="33" t="str">
+        <x:v>Beginning ST − refinancing</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" ht="27" customHeight="1">
+      <x:c r="A27" s="2" t="str">
+        <x:v>Scenario C ending ST debt</x:v>
+      </x:c>
+      <x:c r="B27" s="153" t="str">
+        <x:f>IF(ISBLANK('3 Sources-Uses'!D24),"",'3 Sources-Uses'!D24)</x:f>
+      </x:c>
+      <x:c r="C27" s="153" t="str">
+        <x:f>IF(OR(ISBLANK('3 Sources-Uses'!D22),ISBLANK('3 Sources-Uses'!D23)),"",'3 Sources-Uses'!D22-'3 Sources-Uses'!D23)</x:f>
+      </x:c>
+      <x:c r="D27" s="153" t="str">
+        <x:f>IF(OR(NOT(ISNUMBER(B27)),NOT(ISNUMBER(C27))),"",B27-C27)</x:f>
+      </x:c>
+      <x:c r="E27" s="153" t="n">
+        <x:v>0.1</x:v>
+      </x:c>
+      <x:c r="F27" s="32" t="str">
+        <x:f>IF(OR(NOT(ISNUMBER(B27)),NOT(ISNUMBER(C27))),"COMPLETE",IF(ABS(D27)&lt;=E27,"OK","CHECK"))</x:f>
+        <x:v>COMPLETE</x:v>
+      </x:c>
+      <x:c r="G27" s="33" t="str">
+        <x:v>Beginning ST − refinancing</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" ht="27" customHeight="1">
+      <x:c r="A28" s="2" t="str">
+        <x:v>Scenario A total interest expense</x:v>
+      </x:c>
+      <x:c r="B28" s="153" t="n">
+        <x:f>'4 Scenario Impact'!C38</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C28" s="153" t="str">
+        <x:f>IF(COUNT('4 Scenario Impact'!C35:C37)&lt;3,"",SUM('4 Scenario Impact'!C35:C37))</x:f>
+      </x:c>
+      <x:c r="D28" s="153" t="str">
+        <x:f>IF(OR(NOT(ISNUMBER(B28)),NOT(ISNUMBER(C28))),"",B28-C28)</x:f>
+      </x:c>
+      <x:c r="E28" s="153" t="n">
+        <x:v>0.1</x:v>
+      </x:c>
+      <x:c r="F28" s="32" t="str">
+        <x:f>IF(OR(NOT(ISNUMBER(B28)),NOT(ISNUMBER(C28))),"COMPLETE",IF(ABS(D28)&lt;=E28,"OK","CHECK"))</x:f>
+        <x:v>COMPLETE</x:v>
+      </x:c>
+      <x:c r="G28" s="33" t="str">
+        <x:v>ST + existing LT + new bond</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" ht="27" customHeight="1">
+      <x:c r="A29" s="2" t="str">
+        <x:v>Scenario B total interest expense</x:v>
+      </x:c>
+      <x:c r="B29" s="153" t="n">
+        <x:f>'4 Scenario Impact'!D38</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C29" s="153" t="str">
+        <x:f>IF(COUNT('4 Scenario Impact'!D35:D37)&lt;3,"",SUM('4 Scenario Impact'!D35:D37))</x:f>
+      </x:c>
+      <x:c r="D29" s="153" t="str">
+        <x:f>IF(OR(NOT(ISNUMBER(B29)),NOT(ISNUMBER(C29))),"",B29-C29)</x:f>
+      </x:c>
+      <x:c r="E29" s="153" t="n">
+        <x:v>0.1</x:v>
+      </x:c>
+      <x:c r="F29" s="32" t="str">
+        <x:f>IF(OR(NOT(ISNUMBER(B29)),NOT(ISNUMBER(C29))),"COMPLETE",IF(ABS(D29)&lt;=E29,"OK","CHECK"))</x:f>
+        <x:v>COMPLETE</x:v>
+      </x:c>
+      <x:c r="G29" s="33" t="str">
+        <x:v>ST + existing LT + new bond</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" ht="27" customHeight="1">
+      <x:c r="A30" s="2" t="str">
+        <x:v>Scenario C total interest expense</x:v>
+      </x:c>
+      <x:c r="B30" s="153" t="n">
+        <x:f>'4 Scenario Impact'!E38</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C30" s="153" t="str">
+        <x:f>IF(COUNT('4 Scenario Impact'!E35:E37)&lt;3,"",SUM('4 Scenario Impact'!E35:E37))</x:f>
+      </x:c>
+      <x:c r="D30" s="153" t="str">
+        <x:f>IF(OR(NOT(ISNUMBER(B30)),NOT(ISNUMBER(C30))),"",B30-C30)</x:f>
+      </x:c>
+      <x:c r="E30" s="153" t="n">
+        <x:v>0.1</x:v>
+      </x:c>
+      <x:c r="F30" s="32" t="str">
+        <x:f>IF(OR(NOT(ISNUMBER(B30)),NOT(ISNUMBER(C30))),"COMPLETE",IF(ABS(D30)&lt;=E30,"OK","CHECK"))</x:f>
+        <x:v>COMPLETE</x:v>
+      </x:c>
+      <x:c r="G30" s="33" t="str">
+        <x:v>ST + existing LT + new bond</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" ht="27" customHeight="1">
+      <x:c r="A31" s="2" t="str">
+        <x:v>Scenario A net income</x:v>
+      </x:c>
+      <x:c r="B31" s="153" t="n">
+        <x:f>'4 Scenario Impact'!C41</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C31" s="153" t="str">
+        <x:f>IF(OR('4 Scenario Impact'!C39="",'4 Scenario Impact'!C40=""),"",'4 Scenario Impact'!C39-'4 Scenario Impact'!C40)</x:f>
+      </x:c>
+      <x:c r="D31" s="153" t="str">
+        <x:f>IF(OR(NOT(ISNUMBER(B31)),NOT(ISNUMBER(C31))),"",B31-C31)</x:f>
+      </x:c>
+      <x:c r="E31" s="153" t="n">
+        <x:v>0.1</x:v>
+      </x:c>
+      <x:c r="F31" s="32" t="str">
+        <x:f>IF(OR(NOT(ISNUMBER(B31)),NOT(ISNUMBER(C31))),"COMPLETE",IF(ABS(D31)&lt;=E31,"OK","CHECK"))</x:f>
+        <x:v>COMPLETE</x:v>
+      </x:c>
+      <x:c r="G31" s="33" t="str">
+        <x:v>EBIT − interest − positive tax expense</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" ht="27" customHeight="1">
+      <x:c r="A32" s="2" t="str">
+        <x:v>Scenario B net income</x:v>
+      </x:c>
+      <x:c r="B32" s="153" t="n">
+        <x:f>'4 Scenario Impact'!D41</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C32" s="153" t="str">
+        <x:f>IF(OR('4 Scenario Impact'!D39="",'4 Scenario Impact'!D40=""),"",'4 Scenario Impact'!D39-'4 Scenario Impact'!D40)</x:f>
+      </x:c>
+      <x:c r="D32" s="153" t="str">
+        <x:f>IF(OR(NOT(ISNUMBER(B32)),NOT(ISNUMBER(C32))),"",B32-C32)</x:f>
+      </x:c>
+      <x:c r="E32" s="153" t="n">
+        <x:v>0.1</x:v>
+      </x:c>
+      <x:c r="F32" s="32" t="str">
+        <x:f>IF(OR(NOT(ISNUMBER(B32)),NOT(ISNUMBER(C32))),"COMPLETE",IF(ABS(D32)&lt;=E32,"OK","CHECK"))</x:f>
+        <x:v>COMPLETE</x:v>
+      </x:c>
+      <x:c r="G32" s="33" t="str">
+        <x:v>EBIT − interest − positive tax expense</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" ht="27" customHeight="1">
+      <x:c r="A33" s="2" t="str">
+        <x:v>Scenario C net income</x:v>
+      </x:c>
+      <x:c r="B33" s="153" t="n">
+        <x:f>'4 Scenario Impact'!E41</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C33" s="153" t="str">
+        <x:f>IF(OR('4 Scenario Impact'!E39="",'4 Scenario Impact'!E40=""),"",'4 Scenario Impact'!E39-'4 Scenario Impact'!E40)</x:f>
+      </x:c>
+      <x:c r="D33" s="153" t="str">
+        <x:f>IF(OR(NOT(ISNUMBER(B33)),NOT(ISNUMBER(C33))),"",B33-C33)</x:f>
+      </x:c>
+      <x:c r="E33" s="153" t="n">
+        <x:v>0.1</x:v>
+      </x:c>
+      <x:c r="F33" s="32" t="str">
+        <x:f>IF(OR(NOT(ISNUMBER(B33)),NOT(ISNUMBER(C33))),"COMPLETE",IF(ABS(D33)&lt;=E33,"OK","CHECK"))</x:f>
+        <x:v>COMPLETE</x:v>
+      </x:c>
+      <x:c r="G33" s="33" t="str">
+        <x:v>EBIT − interest − positive tax expense</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" ht="27" customHeight="1">
+      <x:c r="A34" s="2" t="str">
+        <x:v>Scenario A closing equity unchanged</x:v>
+      </x:c>
+      <x:c r="B34" s="153" t="str">
+        <x:f>IF(ISBLANK('4 Scenario Impact'!C25),"",'4 Scenario Impact'!C25)</x:f>
+      </x:c>
+      <x:c r="C34" s="153" t="n">
+        <x:f>IF(ISBLANK('4 Scenario Impact'!B25),"",'4 Scenario Impact'!B25)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D34" s="153" t="str">
+        <x:f>IF(OR(NOT(ISNUMBER(B34)),NOT(ISNUMBER(C34))),"",B34-C34)</x:f>
+      </x:c>
+      <x:c r="E34" s="153" t="n">
+        <x:v>0.1</x:v>
+      </x:c>
+      <x:c r="F34" s="32" t="str">
+        <x:f>IF(OR(NOT(ISNUMBER(B34)),NOT(ISNUMBER(C34))),"COMPLETE",IF(ABS(D34)&lt;=E34,"OK","CHECK"))</x:f>
+        <x:v>COMPLETE</x:v>
+      </x:c>
+      <x:c r="G34" s="33" t="str">
+        <x:v>No equity issuance; closing timing</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35" ht="27" customHeight="1">
+      <x:c r="A35" s="2" t="str">
+        <x:v>Scenario B closing equity unchanged</x:v>
+      </x:c>
+      <x:c r="B35" s="153" t="str">
+        <x:f>IF(ISBLANK('4 Scenario Impact'!D25),"",'4 Scenario Impact'!D25)</x:f>
+      </x:c>
+      <x:c r="C35" s="153" t="n">
+        <x:f>IF(ISBLANK('4 Scenario Impact'!B25),"",'4 Scenario Impact'!B25)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D35" s="153" t="str">
+        <x:f>IF(OR(NOT(ISNUMBER(B35)),NOT(ISNUMBER(C35))),"",B35-C35)</x:f>
+      </x:c>
+      <x:c r="E35" s="153" t="n">
+        <x:v>0.1</x:v>
+      </x:c>
+      <x:c r="F35" s="32" t="str">
+        <x:f>IF(OR(NOT(ISNUMBER(B35)),NOT(ISNUMBER(C35))),"COMPLETE",IF(ABS(D35)&lt;=E35,"OK","CHECK"))</x:f>
+        <x:v>COMPLETE</x:v>
+      </x:c>
+      <x:c r="G35" s="33" t="str">
+        <x:v>No equity issuance; closing timing</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36" ht="27" customHeight="1">
+      <x:c r="A36" s="2" t="str">
+        <x:v>Scenario C closing equity unchanged</x:v>
+      </x:c>
+      <x:c r="B36" s="153" t="str">
+        <x:f>IF(ISBLANK('4 Scenario Impact'!E25),"",'4 Scenario Impact'!E25)</x:f>
+      </x:c>
+      <x:c r="C36" s="153" t="n">
+        <x:f>IF(ISBLANK('4 Scenario Impact'!B25),"",'4 Scenario Impact'!B25)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D36" s="153" t="str">
+        <x:f>IF(OR(NOT(ISNUMBER(B36)),NOT(ISNUMBER(C36))),"",B36-C36)</x:f>
+      </x:c>
+      <x:c r="E36" s="153" t="n">
+        <x:v>0.1</x:v>
+      </x:c>
+      <x:c r="F36" s="32" t="str">
+        <x:f>IF(OR(NOT(ISNUMBER(B36)),NOT(ISNUMBER(C36))),"COMPLETE",IF(ABS(D36)&lt;=E36,"OK","CHECK"))</x:f>
+        <x:v>COMPLETE</x:v>
+      </x:c>
+      <x:c r="G36" s="33" t="str">
+        <x:v>No equity issuance; closing timing</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37" ht="27" customHeight="1">
+      <x:c r="A37" s="2" t="str">
+        <x:v>YIELD vs RATE from observed price</x:v>
+      </x:c>
+      <x:c r="B37" s="154" t="str">
+        <x:f>IF(ISBLANK('2 Bond Pricing'!B31),"",'2 Bond Pricing'!B31)</x:f>
+      </x:c>
+      <x:c r="C37" s="154" t="str">
+        <x:f>IF(ISBLANK('2 Bond Pricing'!B32),"",'2 Bond Pricing'!B32)</x:f>
+      </x:c>
+      <x:c r="D37" s="154" t="str">
+        <x:f>IF(OR(NOT(ISNUMBER(B37)),NOT(ISNUMBER(C37))),"",B37-C37)</x:f>
+      </x:c>
+      <x:c r="E37" s="154" t="n">
+        <x:v>0.000001</x:v>
+      </x:c>
+      <x:c r="F37" s="32" t="str">
+        <x:f>IF(OR(NOT(ISNUMBER(B37)),NOT(ISNUMBER(C37))),"COMPLETE",IF(ABS(D37)&lt;=E37,"OK","CHECK"))</x:f>
+        <x:v>COMPLETE</x:v>
+      </x:c>
+      <x:c r="G37" s="33" t="str">
+        <x:v>2 Bond Pricing · independent reverse-yield methods</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38" ht="27" customHeight="1">
+      <x:c r="A38" s="2" t="str">
+        <x:v>Capacity sources and uses</x:v>
+      </x:c>
+      <x:c r="B38" s="153" t="str">
+        <x:f>IF(ISBLANK('5 Capacity-Decision'!B34),"",'5 Capacity-Decision'!B34)</x:f>
+      </x:c>
+      <x:c r="C38" s="153" t="n">
+        <x:f>0</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D38" s="153" t="str">
+        <x:f>IF(OR(NOT(ISNUMBER(B38)),NOT(ISNUMBER(C38))),"",B38-C38)</x:f>
+      </x:c>
+      <x:c r="E38" s="153" t="n">
+        <x:v>0.1</x:v>
+      </x:c>
+      <x:c r="F38" s="32" t="str">
+        <x:f>IF(OR(NOT(ISNUMBER(B38)),NOT(ISNUMBER(C38))),"COMPLETE",IF(ABS(D38)&lt;=E38,"OK","CHECK"))</x:f>
+        <x:v>COMPLETE</x:v>
+      </x:c>
+      <x:c r="G38" s="33" t="str">
+        <x:v>5 Capacity-Decision</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39" ht="27" customHeight="1">
+      <x:c r="A39" s="2" t="str">
+        <x:v>Capacity Debt / EBITDA</x:v>
+      </x:c>
+      <x:c r="B39" s="155" t="str">
+        <x:f>IF(ISBLANK('5 Capacity-Decision'!B35),"",'5 Capacity-Decision'!B35)</x:f>
+      </x:c>
+      <x:c r="C39" s="155" t="n">
+        <x:f>'1 Assumptions-Baseline'!F48</x:f>
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D39" s="155" t="str">
+        <x:f>IF(OR(NOT(ISNUMBER(B39)),NOT(ISNUMBER(C39))),"",B39-C39)</x:f>
+      </x:c>
+      <x:c r="E39" s="155" t="n">
+        <x:v>0.0001</x:v>
+      </x:c>
+      <x:c r="F39" s="32" t="str">
+        <x:f>IF(OR(NOT(ISNUMBER(B39)),NOT(ISNUMBER(C39))),"COMPLETE",IF(ABS(D39)&lt;=E39,"OK","CHECK"))</x:f>
+        <x:v>COMPLETE</x:v>
+      </x:c>
+      <x:c r="G39" s="33" t="str">
+        <x:v>Must equal the binding 3.00x guardrail</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40">
+      <x:c r="A40" s="2"/>
+      <x:c r="B40" s="2"/>
+      <x:c r="C40" s="2"/>
+      <x:c r="D40" s="2"/>
+      <x:c r="E40" s="2"/>
+      <x:c r="F40" s="2"/>
+      <x:c r="G40" s="2"/>
+    </x:row>
+    <x:row r="41">
+      <x:c r="A41" s="61" t="str">
+        <x:v>PASS means every required tie-out is complete within tolerance. It does not by itself prove the recommendation is economically sound; use the capacity analysis and explain the decision logic.</x:v>
+      </x:c>
+      <x:c r="B41" s="62"/>
+      <x:c r="C41" s="62"/>
+      <x:c r="D41" s="62"/>
+      <x:c r="E41" s="62"/>
+      <x:c r="F41" s="62"/>
+      <x:c r="G41" s="63"/>
+    </x:row>
+    <x:row r="42">
+      <x:c r="A42" s="64"/>
+      <x:c r="B42" s="65"/>
+      <x:c r="C42" s="65"/>
+      <x:c r="D42" s="65"/>
+      <x:c r="E42" s="65"/>
+      <x:c r="F42" s="65"/>
+      <x:c r="G42" s="66"/>
+    </x:row>
+    <x:row r="43">
+      <x:c r="A43" s="64"/>
+      <x:c r="B43" s="65"/>
+      <x:c r="C43" s="65"/>
+      <x:c r="D43" s="65"/>
+      <x:c r="E43" s="65"/>
+      <x:c r="F43" s="65"/>
+      <x:c r="G43" s="66"/>
+    </x:row>
+    <x:row r="44">
+      <x:c r="A44" s="67"/>
+      <x:c r="B44" s="68"/>
+      <x:c r="C44" s="68"/>
+      <x:c r="D44" s="68"/>
+      <x:c r="E44" s="68"/>
+      <x:c r="F44" s="68"/>
+      <x:c r="G44" s="69"/>
+    </x:row>
+  </x:sheetData>
+  <x:mergeCells>
+    <x:mergeCell ref="A1:G1"/>
+    <x:mergeCell ref="B3:D3"/>
+    <x:mergeCell ref="A5:G5"/>
+    <x:mergeCell ref="A41:G44"/>
+  </x:mergeCells>
+  <x:conditionalFormatting sqref="F7:F39">
+    <x:cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="OK"/>
+    <x:cfRule type="containsText" dxfId="1" priority="2" operator="containsText" text="CHECK"/>
+    <x:cfRule type="containsText" dxfId="2" priority="3" operator="containsText" text="COMPLETE"/>
+  </x:conditionalFormatting>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="32" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="55" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="28" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="42" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="16" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="16" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="30" customHeight="1">
+      <x:c r="A1" s="5" t="str">
+        <x:v>Bond Valuation, Interest Rates, and YTM</x:v>
+      </x:c>
+      <x:c r="B1" s="5"/>
+      <x:c r="C1" s="5"/>
+      <x:c r="D1" s="5"/>
+      <x:c r="E1" s="5"/>
+      <x:c r="F1" s="5"/>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2" s="2"/>
+      <x:c r="B2" s="2"/>
+      <x:c r="C2" s="2"/>
+      <x:c r="D2" s="2"/>
+      <x:c r="E2" s="2"/>
+      <x:c r="F2" s="2"/>
+    </x:row>
+    <x:row r="3">
+      <x:c r="A3" s="7" t="str">
+        <x:v>BUS311 · valuation-m02-l01 · display module M06 · FactSet required · student starter</x:v>
+      </x:c>
+      <x:c r="B3" s="7"/>
+      <x:c r="C3" s="7"/>
+      <x:c r="D3" s="7"/>
+      <x:c r="E3" s="7"/>
+      <x:c r="F3" s="7"/>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" s="2"/>
+      <x:c r="B4" s="2"/>
+      <x:c r="C4" s="2"/>
+      <x:c r="D4" s="2"/>
+      <x:c r="E4" s="2"/>
+      <x:c r="F4" s="2"/>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" s="38" t="str">
+        <x:v>Step</x:v>
+      </x:c>
+      <x:c r="B5" s="38" t="str">
+        <x:v>Required workflow</x:v>
+      </x:c>
+      <x:c r="C5" s="2"/>
+      <x:c r="D5" s="2"/>
+      <x:c r="E5" s="2"/>
+      <x:c r="F5" s="2"/>
+    </x:row>
+    <x:row r="6" ht="26" customHeight="1">
+      <x:c r="A6" s="32" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="B6" s="32" t="str">
+        <x:v>Read the lesson pre-reading and confirm FactSet access.</x:v>
+      </x:c>
+      <x:c r="C6" s="2"/>
+      <x:c r="D6" s="2"/>
+      <x:c r="E6" s="2"/>
+      <x:c r="F6" s="2"/>
+    </x:row>
+    <x:row r="7" ht="26" customHeight="1">
+      <x:c r="A7" s="32" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="B7" s="32" t="str">
+        <x:v>Enter or verify source values; keep units and periods consistent.</x:v>
+      </x:c>
+      <x:c r="C7" s="2"/>
+      <x:c r="D7" s="2"/>
+      <x:c r="E7" s="2"/>
+      <x:c r="F7" s="2"/>
+    </x:row>
+    <x:row r="8" ht="26" customHeight="1">
+      <x:c r="A8" s="32" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B8" s="32" t="str">
+        <x:v>Document any live FactSet field, period, units, currency, and retrieval date below.</x:v>
+      </x:c>
+      <x:c r="C8" s="2"/>
+      <x:c r="D8" s="2"/>
+      <x:c r="E8" s="2"/>
+      <x:c r="F8" s="2"/>
+    </x:row>
+    <x:row r="9" ht="26" customHeight="1">
+      <x:c r="A9" s="32" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="B9" s="32" t="str">
+        <x:v>Complete calculations with visible, auditable Excel formulas.</x:v>
+      </x:c>
+      <x:c r="C9" s="2"/>
+      <x:c r="D9" s="2"/>
+      <x:c r="E9" s="2"/>
+      <x:c r="F9" s="2"/>
+    </x:row>
+    <x:row r="10" ht="26" customHeight="1">
+      <x:c r="A10" s="32" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B10" s="32" t="str">
+        <x:v>Use the Checks sheet before stating a recommendation.</x:v>
+      </x:c>
+      <x:c r="C10" s="2"/>
+      <x:c r="D10" s="2"/>
+      <x:c r="E10" s="2"/>
+      <x:c r="F10" s="2"/>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" s="2"/>
+      <x:c r="B11" s="2"/>
+      <x:c r="C11" s="2"/>
+      <x:c r="D11" s="2"/>
+      <x:c r="E11" s="2"/>
+      <x:c r="F11" s="2"/>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" s="38" t="str">
+        <x:v>FactSet input</x:v>
+      </x:c>
+      <x:c r="B12" s="38" t="str">
+        <x:v>Field / definition</x:v>
+      </x:c>
+      <x:c r="C12" s="38" t="str">
+        <x:v>Period / units</x:v>
+      </x:c>
+      <x:c r="D12" s="38" t="str">
+        <x:v>Source note</x:v>
+      </x:c>
+      <x:c r="E12" s="2"/>
+      <x:c r="F12" s="2"/>
+    </x:row>
+    <x:row r="13" ht="28" customHeight="1">
+      <x:c r="A13" s="2" t="str">
+        <x:v>Company identifier</x:v>
+      </x:c>
+      <x:c r="B13" s="88"/>
+      <x:c r="C13" s="88"/>
+      <x:c r="D13" s="88"/>
+      <x:c r="E13" s="2"/>
+      <x:c r="F13" s="2"/>
+    </x:row>
+    <x:row r="14" ht="28" customHeight="1">
+      <x:c r="A14" s="2" t="str">
+        <x:v>Market or price input</x:v>
+      </x:c>
+      <x:c r="B14" s="88"/>
+      <x:c r="C14" s="88"/>
+      <x:c r="D14" s="88"/>
+      <x:c r="E14" s="2"/>
+      <x:c r="F14" s="2"/>
+    </x:row>
+    <x:row r="15" ht="28" customHeight="1">
+      <x:c r="A15" s="2" t="str">
+        <x:v>Financial statement input</x:v>
+      </x:c>
+      <x:c r="B15" s="88"/>
+      <x:c r="C15" s="88"/>
+      <x:c r="D15" s="88"/>
+      <x:c r="E15" s="2"/>
+      <x:c r="F15" s="2"/>
+    </x:row>
+    <x:row r="16" ht="28" customHeight="1">
+      <x:c r="A16" s="2" t="str">
+        <x:v>Risk or discount-rate input</x:v>
+      </x:c>
+      <x:c r="B16" s="88"/>
+      <x:c r="C16" s="88"/>
+      <x:c r="D16" s="88"/>
+      <x:c r="E16" s="2"/>
+      <x:c r="F16" s="2"/>
+    </x:row>
+    <x:row r="17" ht="28" customHeight="1">
+      <x:c r="A17" s="2" t="str">
+        <x:v>Comparison-company input</x:v>
+      </x:c>
+      <x:c r="B17" s="88"/>
+      <x:c r="C17" s="88"/>
+      <x:c r="D17" s="88"/>
+      <x:c r="E17" s="2"/>
+      <x:c r="F17" s="2"/>
+    </x:row>
+    <x:row r="18">
+      <x:c r="A18" s="2"/>
+      <x:c r="B18" s="2"/>
+      <x:c r="C18" s="2"/>
+      <x:c r="D18" s="2"/>
+      <x:c r="E18" s="2"/>
+      <x:c r="F18" s="2"/>
+    </x:row>
+    <x:row r="19">
+      <x:c r="A19" s="38" t="str">
+        <x:v>Decision output</x:v>
+      </x:c>
+      <x:c r="B19" s="38" t="str">
+        <x:v>Response</x:v>
+      </x:c>
+      <x:c r="C19" s="2"/>
+      <x:c r="D19" s="2"/>
+      <x:c r="E19" s="2"/>
+      <x:c r="F19" s="2"/>
+    </x:row>
+    <x:row r="20" ht="30" customHeight="1">
+      <x:c r="A20" s="2" t="str">
+        <x:v>Recommendation</x:v>
+      </x:c>
+      <x:c r="B20" s="88"/>
+      <x:c r="C20" s="2"/>
+      <x:c r="D20" s="2"/>
+      <x:c r="E20" s="2"/>
+      <x:c r="F20" s="2"/>
+    </x:row>
+    <x:row r="21" ht="30" customHeight="1">
+      <x:c r="A21" s="2" t="str">
+        <x:v>Evidence from the model</x:v>
+      </x:c>
+      <x:c r="B21" s="88"/>
+      <x:c r="C21" s="2"/>
+      <x:c r="D21" s="2"/>
+      <x:c r="E21" s="2"/>
+      <x:c r="F21" s="2"/>
+    </x:row>
+    <x:row r="22" ht="30" customHeight="1">
+      <x:c r="A22" s="2" t="str">
+        <x:v>Primary risk or limitation</x:v>
+      </x:c>
+      <x:c r="B22" s="88"/>
+      <x:c r="C22" s="2"/>
+      <x:c r="D22" s="2"/>
+      <x:c r="E22" s="2"/>
+      <x:c r="F22" s="2"/>
+    </x:row>
+    <x:row r="23" ht="30" customHeight="1">
+      <x:c r="A23" s="2" t="str">
+        <x:v>Monitoring trigger</x:v>
+      </x:c>
+      <x:c r="B23" s="88"/>
+      <x:c r="C23" s="2"/>
+      <x:c r="D23" s="2"/>
+      <x:c r="E23" s="2"/>
+      <x:c r="F23" s="2"/>
+    </x:row>
+    <x:row r="24">
+      <x:c r="A24" s="2"/>
+      <x:c r="B24" s="2"/>
+      <x:c r="C24" s="2"/>
+      <x:c r="D24" s="2"/>
+      <x:c r="E24" s="2"/>
+      <x:c r="F24" s="2"/>
+    </x:row>
+    <x:row r="25">
+      <x:c r="A25" s="2"/>
+      <x:c r="B25" s="2"/>
+      <x:c r="C25" s="2"/>
+      <x:c r="D25" s="2"/>
+      <x:c r="E25" s="2"/>
+      <x:c r="F25" s="2"/>
+    </x:row>
+  </x:sheetData>
+  <x:mergeCells>
+    <x:mergeCell ref="A1:F1"/>
+    <x:mergeCell ref="A3:F3"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="37" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="20" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="25" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="20" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="23" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="14" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="14" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="30" customHeight="1">
+      <x:c r="A1" s="5" t="str">
+        <x:v>Three-Year Bond — 5% yield</x:v>
+      </x:c>
+      <x:c r="B1" s="5"/>
+      <x:c r="C1" s="5"/>
+      <x:c r="D1" s="5"/>
+      <x:c r="E1" s="5"/>
+      <x:c r="F1" s="5"/>
+      <x:c r="G1" s="5"/>
+      <x:c r="H1" s="5"/>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2" s="2"/>
+      <x:c r="B2" s="2"/>
+      <x:c r="C2" s="2"/>
+      <x:c r="D2" s="2"/>
+      <x:c r="E2" s="2"/>
+      <x:c r="F2" s="2"/>
+      <x:c r="G2" s="2"/>
+      <x:c r="H2" s="2"/>
+    </x:row>
+    <x:row r="3">
+      <x:c r="A3" s="8" t="str">
+        <x:v>Canva M06 example · annual coupons · enter formulas in yellow cells · compare price with par</x:v>
+      </x:c>
+      <x:c r="B3" s="8"/>
+      <x:c r="C3" s="8"/>
+      <x:c r="D3" s="8"/>
+      <x:c r="E3" s="8"/>
+      <x:c r="F3" s="8"/>
+      <x:c r="G3" s="8"/>
+      <x:c r="H3" s="8"/>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" s="2"/>
+      <x:c r="B4" s="2"/>
+      <x:c r="C4" s="2"/>
+      <x:c r="D4" s="2"/>
+      <x:c r="E4" s="2"/>
+      <x:c r="F4" s="2"/>
+      <x:c r="G4" s="2"/>
+      <x:c r="H4" s="2"/>
+    </x:row>
+    <x:row r="5" ht="22" customHeight="1">
+      <x:c r="A5" s="27" t="str">
+        <x:v>Given contract and market yield</x:v>
+      </x:c>
+      <x:c r="B5" s="27"/>
+      <x:c r="C5" s="27"/>
+      <x:c r="D5" s="27"/>
+      <x:c r="E5" s="27"/>
+      <x:c r="F5" s="27"/>
+      <x:c r="G5" s="27"/>
+      <x:c r="H5" s="27"/>
+    </x:row>
+    <x:row r="6" ht="27" customHeight="1">
+      <x:c r="A6" s="71" t="str">
+        <x:v>Face value ($)</x:v>
+      </x:c>
+      <x:c r="B6" s="74" t="n">
+        <x:v>1000</x:v>
+      </x:c>
+      <x:c r="C6" s="2"/>
+      <x:c r="D6" s="18" t="str">
+        <x:v>Price the bond with Excel PV(rate, nper, pmt, fv). Use the yearly cash-flow table to check the result: calculate each promised payment, discount it at the market yield, and add its present value. Only the market yield changes across these examples.</x:v>
+      </x:c>
+      <x:c r="E6" s="19"/>
+      <x:c r="F6" s="19"/>
+      <x:c r="G6" s="19"/>
+      <x:c r="H6" s="20"/>
+    </x:row>
+    <x:row r="7" ht="27" customHeight="1">
+      <x:c r="A7" s="71" t="str">
+        <x:v>Annual coupon rate</x:v>
+      </x:c>
+      <x:c r="B7" s="75" t="n">
+        <x:v>0.05</x:v>
+      </x:c>
+      <x:c r="C7" s="2"/>
+      <x:c r="D7" s="21"/>
+      <x:c r="E7" s="22"/>
+      <x:c r="F7" s="22"/>
+      <x:c r="G7" s="22"/>
+      <x:c r="H7" s="23"/>
+    </x:row>
+    <x:row r="8" ht="27" customHeight="1">
+      <x:c r="A8" s="71" t="str">
+        <x:v>Market yield (annual)</x:v>
+      </x:c>
+      <x:c r="B8" s="75" t="n">
+        <x:v>0.05</x:v>
+      </x:c>
+      <x:c r="C8" s="2"/>
+      <x:c r="D8" s="21"/>
+      <x:c r="E8" s="22"/>
+      <x:c r="F8" s="22"/>
+      <x:c r="G8" s="22"/>
+      <x:c r="H8" s="23"/>
+    </x:row>
+    <x:row r="9" ht="27" customHeight="1">
+      <x:c r="A9" s="71" t="str">
+        <x:v>Years to maturity</x:v>
+      </x:c>
+      <x:c r="B9" s="76" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C9" s="2"/>
+      <x:c r="D9" s="21"/>
+      <x:c r="E9" s="22"/>
+      <x:c r="F9" s="22"/>
+      <x:c r="G9" s="22"/>
+      <x:c r="H9" s="23"/>
+    </x:row>
+    <x:row r="10" ht="27" customHeight="1">
+      <x:c r="A10" s="71" t="str">
+        <x:v>Coupon payments per year</x:v>
+      </x:c>
+      <x:c r="B10" s="76" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C10" s="2"/>
+      <x:c r="D10" s="24"/>
+      <x:c r="E10" s="25"/>
+      <x:c r="F10" s="25"/>
+      <x:c r="G10" s="25"/>
+      <x:c r="H10" s="26"/>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" s="2"/>
+      <x:c r="B11" s="2"/>
+      <x:c r="C11" s="2"/>
+      <x:c r="D11" s="2"/>
+      <x:c r="E11" s="2"/>
+      <x:c r="F11" s="2"/>
+      <x:c r="G11" s="2"/>
+      <x:c r="H11" s="2"/>
+    </x:row>
+    <x:row r="12" ht="22" customHeight="1">
+      <x:c r="A12" s="27" t="str">
+        <x:v>Discount each promised cash flow</x:v>
+      </x:c>
+      <x:c r="B12" s="27"/>
+      <x:c r="C12" s="27"/>
+      <x:c r="D12" s="27"/>
+      <x:c r="E12" s="27"/>
+      <x:c r="F12" s="27"/>
+      <x:c r="G12" s="27"/>
+      <x:c r="H12" s="27"/>
+    </x:row>
+    <x:row r="13" ht="30" customHeight="1">
+      <x:c r="A13" s="38" t="str">
+        <x:v>Year</x:v>
+      </x:c>
+      <x:c r="B13" s="38" t="str">
+        <x:v>Coupon ($)</x:v>
+      </x:c>
+      <x:c r="C13" s="38" t="str">
+        <x:v>Principal ($)</x:v>
+      </x:c>
+      <x:c r="D13" s="38" t="str">
+        <x:v>Total cash flow ($)</x:v>
+      </x:c>
+      <x:c r="E13" s="38" t="str">
+        <x:v>Discount factor</x:v>
+      </x:c>
+      <x:c r="F13" s="38" t="str">
+        <x:v>Present value ($)</x:v>
+      </x:c>
+      <x:c r="G13" s="2"/>
+      <x:c r="H13" s="2"/>
+    </x:row>
+    <x:row r="14" ht="30" customHeight="1">
+      <x:c r="A14" s="78" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="B14" s="82"/>
+      <x:c r="C14" s="82"/>
+      <x:c r="D14" s="82"/>
+      <x:c r="E14" s="85"/>
+      <x:c r="F14" s="82"/>
+      <x:c r="G14" s="2"/>
+      <x:c r="H14" s="2"/>
+    </x:row>
+    <x:row r="15" ht="30" customHeight="1">
+      <x:c r="A15" s="78" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="B15" s="82"/>
+      <x:c r="C15" s="82"/>
+      <x:c r="D15" s="82"/>
+      <x:c r="E15" s="85"/>
+      <x:c r="F15" s="82"/>
+      <x:c r="G15" s="2"/>
+      <x:c r="H15" s="2"/>
+    </x:row>
+    <x:row r="16" ht="30" customHeight="1">
+      <x:c r="A16" s="78" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B16" s="82"/>
+      <x:c r="C16" s="82"/>
+      <x:c r="D16" s="82"/>
+      <x:c r="E16" s="85"/>
+      <x:c r="F16" s="82"/>
+      <x:c r="G16" s="2"/>
+      <x:c r="H16" s="2"/>
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17" s="2"/>
+      <x:c r="B17" s="2"/>
+      <x:c r="C17" s="2"/>
+      <x:c r="D17" s="2"/>
+      <x:c r="E17" s="2"/>
+      <x:c r="F17" s="2"/>
+      <x:c r="G17" s="2"/>
+      <x:c r="H17" s="2"/>
+    </x:row>
+    <x:row r="18" ht="22" customHeight="1">
+      <x:c r="A18" s="27" t="str">
+        <x:v>Bond price and interpretation</x:v>
+      </x:c>
+      <x:c r="B18" s="27"/>
+      <x:c r="C18" s="27"/>
+      <x:c r="D18" s="27"/>
+      <x:c r="E18" s="27"/>
+      <x:c r="F18" s="27"/>
+      <x:c r="G18" s="27"/>
+      <x:c r="H18" s="27"/>
+    </x:row>
+    <x:row r="19" ht="28" customHeight="1">
+      <x:c r="A19" s="71" t="str">
+        <x:v>Bond price — Excel PV function</x:v>
+      </x:c>
+      <x:c r="B19" s="82"/>
+      <x:c r="C19" s="2"/>
+      <x:c r="D19" s="2"/>
+      <x:c r="E19" s="2"/>
+      <x:c r="F19" s="2"/>
+      <x:c r="G19" s="2"/>
+      <x:c r="H19" s="2"/>
+    </x:row>
+    <x:row r="20" ht="28" customHeight="1">
+      <x:c r="A20" s="71" t="str">
+        <x:v>Sum of discounted cash flows</x:v>
+      </x:c>
+      <x:c r="B20" s="82"/>
+      <x:c r="C20" s="2"/>
+      <x:c r="D20" s="2"/>
+      <x:c r="E20" s="2"/>
+      <x:c r="F20" s="2"/>
+      <x:c r="G20" s="2"/>
+      <x:c r="H20" s="2"/>
+    </x:row>
+    <x:row r="21" ht="28" customHeight="1">
+      <x:c r="A21" s="71" t="str">
+        <x:v>Difference between the methods</x:v>
+      </x:c>
+      <x:c r="B21" s="82"/>
+      <x:c r="C21" s="2"/>
+      <x:c r="D21" s="2"/>
+      <x:c r="E21" s="2"/>
+      <x:c r="F21" s="2"/>
+      <x:c r="G21" s="2"/>
+      <x:c r="H21" s="2"/>
+    </x:row>
+    <x:row r="22" ht="28" customHeight="1">
+      <x:c r="A22" s="71" t="str">
+        <x:v>Price relative to par</x:v>
+      </x:c>
+      <x:c r="B22" s="88"/>
+      <x:c r="C22" s="2"/>
+      <x:c r="D22" s="2"/>
+      <x:c r="E22" s="2"/>
+      <x:c r="F22" s="2"/>
+      <x:c r="G22" s="2"/>
+      <x:c r="H22" s="2"/>
+    </x:row>
+    <x:row r="23" ht="28" customHeight="1">
+      <x:c r="A23" s="71" t="str">
+        <x:v>Premium / (discount) dollars</x:v>
+      </x:c>
+      <x:c r="B23" s="82"/>
+      <x:c r="C23" s="2"/>
+      <x:c r="D23" s="2"/>
+      <x:c r="E23" s="2"/>
+      <x:c r="F23" s="2"/>
+      <x:c r="G23" s="2"/>
+      <x:c r="H23" s="2"/>
+    </x:row>
+    <x:row r="24">
+      <x:c r="A24" s="2"/>
+      <x:c r="B24" s="2"/>
+      <x:c r="C24" s="2"/>
+      <x:c r="D24" s="2"/>
+      <x:c r="E24" s="2"/>
+      <x:c r="F24" s="2"/>
+      <x:c r="G24" s="2"/>
+      <x:c r="H24" s="2"/>
+    </x:row>
+    <x:row r="25" ht="22" customHeight="1">
+      <x:c r="A25" s="27" t="str">
+        <x:v>Explain the price</x:v>
+      </x:c>
+      <x:c r="B25" s="27"/>
+      <x:c r="C25" s="27"/>
+      <x:c r="D25" s="27"/>
+      <x:c r="E25" s="27"/>
+      <x:c r="F25" s="27"/>
+      <x:c r="G25" s="27"/>
+      <x:c r="H25" s="27"/>
+    </x:row>
+    <x:row r="26" ht="26" customHeight="1">
+      <x:c r="A26" s="88"/>
+      <x:c r="B26" s="88"/>
+      <x:c r="C26" s="88"/>
+      <x:c r="D26" s="88"/>
+      <x:c r="E26" s="88"/>
+      <x:c r="F26" s="88"/>
+      <x:c r="G26" s="88"/>
+      <x:c r="H26" s="88"/>
+    </x:row>
+    <x:row r="27" ht="26" customHeight="1">
+      <x:c r="A27" s="88"/>
+      <x:c r="B27" s="88"/>
+      <x:c r="C27" s="88"/>
+      <x:c r="D27" s="88"/>
+      <x:c r="E27" s="88"/>
+      <x:c r="F27" s="88"/>
+      <x:c r="G27" s="88"/>
+      <x:c r="H27" s="88"/>
+    </x:row>
+    <x:row r="28" ht="26" customHeight="1">
+      <x:c r="A28" s="88"/>
+      <x:c r="B28" s="88"/>
+      <x:c r="C28" s="88"/>
+      <x:c r="D28" s="88"/>
+      <x:c r="E28" s="88"/>
+      <x:c r="F28" s="88"/>
+      <x:c r="G28" s="88"/>
+      <x:c r="H28" s="88"/>
+    </x:row>
+    <x:row r="29">
+      <x:c r="A29" s="2"/>
+      <x:c r="B29" s="2"/>
+      <x:c r="C29" s="2"/>
+      <x:c r="D29" s="2"/>
+      <x:c r="E29" s="2"/>
+      <x:c r="F29" s="2"/>
+      <x:c r="G29" s="2"/>
+      <x:c r="H29" s="2"/>
+    </x:row>
+    <x:row r="30" ht="26" customHeight="1">
+      <x:c r="A30" s="18" t="str">
+        <x:v>After all three examples: compare the coupon and principal cash flows, then compare the discount factors and prices. What stays fixed, and what moves when market yield changes?</x:v>
+      </x:c>
+      <x:c r="B30" s="19"/>
+      <x:c r="C30" s="19"/>
+      <x:c r="D30" s="19"/>
+      <x:c r="E30" s="19"/>
+      <x:c r="F30" s="19"/>
+      <x:c r="G30" s="19"/>
+      <x:c r="H30" s="20"/>
+    </x:row>
+    <x:row r="31" ht="26" customHeight="1">
+      <x:c r="A31" s="24"/>
+      <x:c r="B31" s="25"/>
+      <x:c r="C31" s="25"/>
+      <x:c r="D31" s="25"/>
+      <x:c r="E31" s="25"/>
+      <x:c r="F31" s="25"/>
+      <x:c r="G31" s="25"/>
+      <x:c r="H31" s="26"/>
+    </x:row>
+    <x:row r="32">
+      <x:c r="A32" s="2"/>
+      <x:c r="B32" s="2"/>
+      <x:c r="C32" s="2"/>
+      <x:c r="D32" s="2"/>
+      <x:c r="E32" s="2"/>
+      <x:c r="F32" s="2"/>
+      <x:c r="G32" s="2"/>
+      <x:c r="H32" s="2"/>
+    </x:row>
+  </x:sheetData>
+  <x:mergeCells>
+    <x:mergeCell ref="A1:H1"/>
+    <x:mergeCell ref="A3:H3"/>
+    <x:mergeCell ref="A5:H5"/>
+    <x:mergeCell ref="D6:H10"/>
+    <x:mergeCell ref="A12:H12"/>
+    <x:mergeCell ref="A18:H18"/>
+    <x:mergeCell ref="A25:H25"/>
+    <x:mergeCell ref="A26:H28"/>
+    <x:mergeCell ref="A30:H31"/>
+  </x:mergeCells>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="37" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="20" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="25" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="20" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="23" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="14" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="14" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="30" customHeight="1">
+      <x:c r="A1" s="5" t="str">
+        <x:v>Three-Year Bond — 3% yield</x:v>
+      </x:c>
+      <x:c r="B1" s="5"/>
+      <x:c r="C1" s="5"/>
+      <x:c r="D1" s="5"/>
+      <x:c r="E1" s="5"/>
+      <x:c r="F1" s="5"/>
+      <x:c r="G1" s="5"/>
+      <x:c r="H1" s="5"/>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2" s="2"/>
+      <x:c r="B2" s="2"/>
+      <x:c r="C2" s="2"/>
+      <x:c r="D2" s="2"/>
+      <x:c r="E2" s="2"/>
+      <x:c r="F2" s="2"/>
+      <x:c r="G2" s="2"/>
+      <x:c r="H2" s="2"/>
+    </x:row>
+    <x:row r="3">
+      <x:c r="A3" s="8" t="str">
+        <x:v>Canva M06 example · annual coupons · enter formulas in yellow cells · compare price with par</x:v>
+      </x:c>
+      <x:c r="B3" s="8"/>
+      <x:c r="C3" s="8"/>
+      <x:c r="D3" s="8"/>
+      <x:c r="E3" s="8"/>
+      <x:c r="F3" s="8"/>
+      <x:c r="G3" s="8"/>
+      <x:c r="H3" s="8"/>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" s="2"/>
+      <x:c r="B4" s="2"/>
+      <x:c r="C4" s="2"/>
+      <x:c r="D4" s="2"/>
+      <x:c r="E4" s="2"/>
+      <x:c r="F4" s="2"/>
+      <x:c r="G4" s="2"/>
+      <x:c r="H4" s="2"/>
+    </x:row>
+    <x:row r="5" ht="22" customHeight="1">
+      <x:c r="A5" s="27" t="str">
+        <x:v>Given contract and market yield</x:v>
+      </x:c>
+      <x:c r="B5" s="27"/>
+      <x:c r="C5" s="27"/>
+      <x:c r="D5" s="27"/>
+      <x:c r="E5" s="27"/>
+      <x:c r="F5" s="27"/>
+      <x:c r="G5" s="27"/>
+      <x:c r="H5" s="27"/>
+    </x:row>
+    <x:row r="6" ht="27" customHeight="1">
+      <x:c r="A6" s="71" t="str">
+        <x:v>Face value ($)</x:v>
+      </x:c>
+      <x:c r="B6" s="74" t="n">
+        <x:v>1000</x:v>
+      </x:c>
+      <x:c r="C6" s="2"/>
+      <x:c r="D6" s="18" t="str">
+        <x:v>Price the bond with Excel PV(rate, nper, pmt, fv). Use the yearly cash-flow table to check the result: calculate each promised payment, discount it at the market yield, and add its present value. Only the market yield changes across these examples.</x:v>
+      </x:c>
+      <x:c r="E6" s="19"/>
+      <x:c r="F6" s="19"/>
+      <x:c r="G6" s="19"/>
+      <x:c r="H6" s="20"/>
+    </x:row>
+    <x:row r="7" ht="27" customHeight="1">
+      <x:c r="A7" s="71" t="str">
+        <x:v>Annual coupon rate</x:v>
+      </x:c>
+      <x:c r="B7" s="75" t="n">
+        <x:v>0.05</x:v>
+      </x:c>
+      <x:c r="C7" s="2"/>
+      <x:c r="D7" s="21"/>
+      <x:c r="E7" s="22"/>
+      <x:c r="F7" s="22"/>
+      <x:c r="G7" s="22"/>
+      <x:c r="H7" s="23"/>
+    </x:row>
+    <x:row r="8" ht="27" customHeight="1">
+      <x:c r="A8" s="71" t="str">
+        <x:v>Market yield (annual)</x:v>
+      </x:c>
+      <x:c r="B8" s="75" t="n">
+        <x:v>0.03</x:v>
+      </x:c>
+      <x:c r="C8" s="2"/>
+      <x:c r="D8" s="21"/>
+      <x:c r="E8" s="22"/>
+      <x:c r="F8" s="22"/>
+      <x:c r="G8" s="22"/>
+      <x:c r="H8" s="23"/>
+    </x:row>
+    <x:row r="9" ht="27" customHeight="1">
+      <x:c r="A9" s="71" t="str">
+        <x:v>Years to maturity</x:v>
+      </x:c>
+      <x:c r="B9" s="76" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C9" s="2"/>
+      <x:c r="D9" s="21"/>
+      <x:c r="E9" s="22"/>
+      <x:c r="F9" s="22"/>
+      <x:c r="G9" s="22"/>
+      <x:c r="H9" s="23"/>
+    </x:row>
+    <x:row r="10" ht="27" customHeight="1">
+      <x:c r="A10" s="71" t="str">
+        <x:v>Coupon payments per year</x:v>
+      </x:c>
+      <x:c r="B10" s="76" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C10" s="2"/>
+      <x:c r="D10" s="24"/>
+      <x:c r="E10" s="25"/>
+      <x:c r="F10" s="25"/>
+      <x:c r="G10" s="25"/>
+      <x:c r="H10" s="26"/>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" s="2"/>
+      <x:c r="B11" s="2"/>
+      <x:c r="C11" s="2"/>
+      <x:c r="D11" s="2"/>
+      <x:c r="E11" s="2"/>
+      <x:c r="F11" s="2"/>
+      <x:c r="G11" s="2"/>
+      <x:c r="H11" s="2"/>
+    </x:row>
+    <x:row r="12" ht="22" customHeight="1">
+      <x:c r="A12" s="27" t="str">
+        <x:v>Discount each promised cash flow</x:v>
+      </x:c>
+      <x:c r="B12" s="27"/>
+      <x:c r="C12" s="27"/>
+      <x:c r="D12" s="27"/>
+      <x:c r="E12" s="27"/>
+      <x:c r="F12" s="27"/>
+      <x:c r="G12" s="27"/>
+      <x:c r="H12" s="27"/>
+    </x:row>
+    <x:row r="13" ht="30" customHeight="1">
+      <x:c r="A13" s="38" t="str">
+        <x:v>Year</x:v>
+      </x:c>
+      <x:c r="B13" s="38" t="str">
+        <x:v>Coupon ($)</x:v>
+      </x:c>
+      <x:c r="C13" s="38" t="str">
+        <x:v>Principal ($)</x:v>
+      </x:c>
+      <x:c r="D13" s="38" t="str">
+        <x:v>Total cash flow ($)</x:v>
+      </x:c>
+      <x:c r="E13" s="38" t="str">
+        <x:v>Discount factor</x:v>
+      </x:c>
+      <x:c r="F13" s="38" t="str">
+        <x:v>Present value ($)</x:v>
+      </x:c>
+      <x:c r="G13" s="2"/>
+      <x:c r="H13" s="2"/>
+    </x:row>
+    <x:row r="14" ht="30" customHeight="1">
+      <x:c r="A14" s="78" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="B14" s="82"/>
+      <x:c r="C14" s="82"/>
+      <x:c r="D14" s="82"/>
+      <x:c r="E14" s="85"/>
+      <x:c r="F14" s="82"/>
+      <x:c r="G14" s="2"/>
+      <x:c r="H14" s="2"/>
+    </x:row>
+    <x:row r="15" ht="30" customHeight="1">
+      <x:c r="A15" s="78" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="B15" s="82"/>
+      <x:c r="C15" s="82"/>
+      <x:c r="D15" s="82"/>
+      <x:c r="E15" s="85"/>
+      <x:c r="F15" s="82"/>
+      <x:c r="G15" s="2"/>
+      <x:c r="H15" s="2"/>
+    </x:row>
+    <x:row r="16" ht="30" customHeight="1">
+      <x:c r="A16" s="78" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B16" s="82"/>
+      <x:c r="C16" s="82"/>
+      <x:c r="D16" s="82"/>
+      <x:c r="E16" s="85"/>
+      <x:c r="F16" s="82"/>
+      <x:c r="G16" s="2"/>
+      <x:c r="H16" s="2"/>
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17" s="2"/>
+      <x:c r="B17" s="2"/>
+      <x:c r="C17" s="2"/>
+      <x:c r="D17" s="2"/>
+      <x:c r="E17" s="2"/>
+      <x:c r="F17" s="2"/>
+      <x:c r="G17" s="2"/>
+      <x:c r="H17" s="2"/>
+    </x:row>
+    <x:row r="18" ht="22" customHeight="1">
+      <x:c r="A18" s="27" t="str">
+        <x:v>Bond price and interpretation</x:v>
+      </x:c>
+      <x:c r="B18" s="27"/>
+      <x:c r="C18" s="27"/>
+      <x:c r="D18" s="27"/>
+      <x:c r="E18" s="27"/>
+      <x:c r="F18" s="27"/>
+      <x:c r="G18" s="27"/>
+      <x:c r="H18" s="27"/>
+    </x:row>
+    <x:row r="19" ht="28" customHeight="1">
+      <x:c r="A19" s="71" t="str">
+        <x:v>Bond price — Excel PV function</x:v>
+      </x:c>
+      <x:c r="B19" s="82"/>
+      <x:c r="C19" s="2"/>
+      <x:c r="D19" s="2"/>
+      <x:c r="E19" s="2"/>
+      <x:c r="F19" s="2"/>
+      <x:c r="G19" s="2"/>
+      <x:c r="H19" s="2"/>
+    </x:row>
+    <x:row r="20" ht="28" customHeight="1">
+      <x:c r="A20" s="71" t="str">
+        <x:v>Sum of discounted cash flows</x:v>
+      </x:c>
+      <x:c r="B20" s="82"/>
+      <x:c r="C20" s="2"/>
+      <x:c r="D20" s="2"/>
+      <x:c r="E20" s="2"/>
+      <x:c r="F20" s="2"/>
+      <x:c r="G20" s="2"/>
+      <x:c r="H20" s="2"/>
+    </x:row>
+    <x:row r="21" ht="28" customHeight="1">
+      <x:c r="A21" s="71" t="str">
+        <x:v>Difference between the methods</x:v>
+      </x:c>
+      <x:c r="B21" s="82"/>
+      <x:c r="C21" s="2"/>
+      <x:c r="D21" s="2"/>
+      <x:c r="E21" s="2"/>
+      <x:c r="F21" s="2"/>
+      <x:c r="G21" s="2"/>
+      <x:c r="H21" s="2"/>
+    </x:row>
+    <x:row r="22" ht="28" customHeight="1">
+      <x:c r="A22" s="71" t="str">
+        <x:v>Price relative to par</x:v>
+      </x:c>
+      <x:c r="B22" s="88"/>
+      <x:c r="C22" s="2"/>
+      <x:c r="D22" s="2"/>
+      <x:c r="E22" s="2"/>
+      <x:c r="F22" s="2"/>
+      <x:c r="G22" s="2"/>
+      <x:c r="H22" s="2"/>
+    </x:row>
+    <x:row r="23" ht="28" customHeight="1">
+      <x:c r="A23" s="71" t="str">
+        <x:v>Premium / (discount) dollars</x:v>
+      </x:c>
+      <x:c r="B23" s="82"/>
+      <x:c r="C23" s="2"/>
+      <x:c r="D23" s="2"/>
+      <x:c r="E23" s="2"/>
+      <x:c r="F23" s="2"/>
+      <x:c r="G23" s="2"/>
+      <x:c r="H23" s="2"/>
+    </x:row>
+    <x:row r="24">
+      <x:c r="A24" s="2"/>
+      <x:c r="B24" s="2"/>
+      <x:c r="C24" s="2"/>
+      <x:c r="D24" s="2"/>
+      <x:c r="E24" s="2"/>
+      <x:c r="F24" s="2"/>
+      <x:c r="G24" s="2"/>
+      <x:c r="H24" s="2"/>
+    </x:row>
+    <x:row r="25" ht="22" customHeight="1">
+      <x:c r="A25" s="27" t="str">
+        <x:v>Explain the price</x:v>
+      </x:c>
+      <x:c r="B25" s="27"/>
+      <x:c r="C25" s="27"/>
+      <x:c r="D25" s="27"/>
+      <x:c r="E25" s="27"/>
+      <x:c r="F25" s="27"/>
+      <x:c r="G25" s="27"/>
+      <x:c r="H25" s="27"/>
+    </x:row>
+    <x:row r="26" ht="26" customHeight="1">
+      <x:c r="A26" s="88"/>
+      <x:c r="B26" s="88"/>
+      <x:c r="C26" s="88"/>
+      <x:c r="D26" s="88"/>
+      <x:c r="E26" s="88"/>
+      <x:c r="F26" s="88"/>
+      <x:c r="G26" s="88"/>
+      <x:c r="H26" s="88"/>
+    </x:row>
+    <x:row r="27" ht="26" customHeight="1">
+      <x:c r="A27" s="88"/>
+      <x:c r="B27" s="88"/>
+      <x:c r="C27" s="88"/>
+      <x:c r="D27" s="88"/>
+      <x:c r="E27" s="88"/>
+      <x:c r="F27" s="88"/>
+      <x:c r="G27" s="88"/>
+      <x:c r="H27" s="88"/>
+    </x:row>
+    <x:row r="28" ht="26" customHeight="1">
+      <x:c r="A28" s="88"/>
+      <x:c r="B28" s="88"/>
+      <x:c r="C28" s="88"/>
+      <x:c r="D28" s="88"/>
+      <x:c r="E28" s="88"/>
+      <x:c r="F28" s="88"/>
+      <x:c r="G28" s="88"/>
+      <x:c r="H28" s="88"/>
+    </x:row>
+    <x:row r="29">
+      <x:c r="A29" s="2"/>
+      <x:c r="B29" s="2"/>
+      <x:c r="C29" s="2"/>
+      <x:c r="D29" s="2"/>
+      <x:c r="E29" s="2"/>
+      <x:c r="F29" s="2"/>
+      <x:c r="G29" s="2"/>
+      <x:c r="H29" s="2"/>
+    </x:row>
+    <x:row r="30" ht="26" customHeight="1">
+      <x:c r="A30" s="18" t="str">
+        <x:v>After all three examples: compare the coupon and principal cash flows, then compare the discount factors and prices. What stays fixed, and what moves when market yield changes?</x:v>
+      </x:c>
+      <x:c r="B30" s="19"/>
+      <x:c r="C30" s="19"/>
+      <x:c r="D30" s="19"/>
+      <x:c r="E30" s="19"/>
+      <x:c r="F30" s="19"/>
+      <x:c r="G30" s="19"/>
+      <x:c r="H30" s="20"/>
+    </x:row>
+    <x:row r="31" ht="26" customHeight="1">
+      <x:c r="A31" s="24"/>
+      <x:c r="B31" s="25"/>
+      <x:c r="C31" s="25"/>
+      <x:c r="D31" s="25"/>
+      <x:c r="E31" s="25"/>
+      <x:c r="F31" s="25"/>
+      <x:c r="G31" s="25"/>
+      <x:c r="H31" s="26"/>
+    </x:row>
+    <x:row r="32">
+      <x:c r="A32" s="2"/>
+      <x:c r="B32" s="2"/>
+      <x:c r="C32" s="2"/>
+      <x:c r="D32" s="2"/>
+      <x:c r="E32" s="2"/>
+      <x:c r="F32" s="2"/>
+      <x:c r="G32" s="2"/>
+      <x:c r="H32" s="2"/>
+    </x:row>
+  </x:sheetData>
+  <x:mergeCells>
+    <x:mergeCell ref="A1:H1"/>
+    <x:mergeCell ref="A3:H3"/>
+    <x:mergeCell ref="A5:H5"/>
+    <x:mergeCell ref="D6:H10"/>
+    <x:mergeCell ref="A12:H12"/>
+    <x:mergeCell ref="A18:H18"/>
+    <x:mergeCell ref="A25:H25"/>
+    <x:mergeCell ref="A26:H28"/>
+    <x:mergeCell ref="A30:H31"/>
+  </x:mergeCells>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="37" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="20" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="25" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="20" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="23" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="14" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="14" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="30" customHeight="1">
+      <x:c r="A1" s="5" t="str">
+        <x:v>Three-Year Bond — 7% yield</x:v>
+      </x:c>
+      <x:c r="B1" s="5"/>
+      <x:c r="C1" s="5"/>
+      <x:c r="D1" s="5"/>
+      <x:c r="E1" s="5"/>
+      <x:c r="F1" s="5"/>
+      <x:c r="G1" s="5"/>
+      <x:c r="H1" s="5"/>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2" s="2"/>
+      <x:c r="B2" s="2"/>
+      <x:c r="C2" s="2"/>
+      <x:c r="D2" s="2"/>
+      <x:c r="E2" s="2"/>
+      <x:c r="F2" s="2"/>
+      <x:c r="G2" s="2"/>
+      <x:c r="H2" s="2"/>
+    </x:row>
+    <x:row r="3">
+      <x:c r="A3" s="8" t="str">
+        <x:v>Canva M06 example · annual coupons · enter formulas in yellow cells · compare price with par</x:v>
+      </x:c>
+      <x:c r="B3" s="8"/>
+      <x:c r="C3" s="8"/>
+      <x:c r="D3" s="8"/>
+      <x:c r="E3" s="8"/>
+      <x:c r="F3" s="8"/>
+      <x:c r="G3" s="8"/>
+      <x:c r="H3" s="8"/>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" s="2"/>
+      <x:c r="B4" s="2"/>
+      <x:c r="C4" s="2"/>
+      <x:c r="D4" s="2"/>
+      <x:c r="E4" s="2"/>
+      <x:c r="F4" s="2"/>
+      <x:c r="G4" s="2"/>
+      <x:c r="H4" s="2"/>
+    </x:row>
+    <x:row r="5" ht="22" customHeight="1">
+      <x:c r="A5" s="27" t="str">
+        <x:v>Given contract and market yield</x:v>
+      </x:c>
+      <x:c r="B5" s="27"/>
+      <x:c r="C5" s="27"/>
+      <x:c r="D5" s="27"/>
+      <x:c r="E5" s="27"/>
+      <x:c r="F5" s="27"/>
+      <x:c r="G5" s="27"/>
+      <x:c r="H5" s="27"/>
+    </x:row>
+    <x:row r="6" ht="27" customHeight="1">
+      <x:c r="A6" s="71" t="str">
+        <x:v>Face value ($)</x:v>
+      </x:c>
+      <x:c r="B6" s="74" t="n">
+        <x:v>1000</x:v>
+      </x:c>
+      <x:c r="C6" s="2"/>
+      <x:c r="D6" s="18" t="str">
+        <x:v>Price the bond with Excel PV(rate, nper, pmt, fv). Use the yearly cash-flow table to check the result: calculate each promised payment, discount it at the market yield, and add its present value. Only the market yield changes across these examples.</x:v>
+      </x:c>
+      <x:c r="E6" s="19"/>
+      <x:c r="F6" s="19"/>
+      <x:c r="G6" s="19"/>
+      <x:c r="H6" s="20"/>
+    </x:row>
+    <x:row r="7" ht="27" customHeight="1">
+      <x:c r="A7" s="71" t="str">
+        <x:v>Annual coupon rate</x:v>
+      </x:c>
+      <x:c r="B7" s="75" t="n">
+        <x:v>0.05</x:v>
+      </x:c>
+      <x:c r="C7" s="2"/>
+      <x:c r="D7" s="21"/>
+      <x:c r="E7" s="22"/>
+      <x:c r="F7" s="22"/>
+      <x:c r="G7" s="22"/>
+      <x:c r="H7" s="23"/>
+    </x:row>
+    <x:row r="8" ht="27" customHeight="1">
+      <x:c r="A8" s="71" t="str">
+        <x:v>Market yield (annual)</x:v>
+      </x:c>
+      <x:c r="B8" s="75" t="n">
+        <x:v>0.07</x:v>
+      </x:c>
+      <x:c r="C8" s="2"/>
+      <x:c r="D8" s="21"/>
+      <x:c r="E8" s="22"/>
+      <x:c r="F8" s="22"/>
+      <x:c r="G8" s="22"/>
+      <x:c r="H8" s="23"/>
+    </x:row>
+    <x:row r="9" ht="27" customHeight="1">
+      <x:c r="A9" s="71" t="str">
+        <x:v>Years to maturity</x:v>
+      </x:c>
+      <x:c r="B9" s="76" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C9" s="2"/>
+      <x:c r="D9" s="21"/>
+      <x:c r="E9" s="22"/>
+      <x:c r="F9" s="22"/>
+      <x:c r="G9" s="22"/>
+      <x:c r="H9" s="23"/>
+    </x:row>
+    <x:row r="10" ht="27" customHeight="1">
+      <x:c r="A10" s="71" t="str">
+        <x:v>Coupon payments per year</x:v>
+      </x:c>
+      <x:c r="B10" s="76" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C10" s="2"/>
+      <x:c r="D10" s="24"/>
+      <x:c r="E10" s="25"/>
+      <x:c r="F10" s="25"/>
+      <x:c r="G10" s="25"/>
+      <x:c r="H10" s="26"/>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" s="2"/>
+      <x:c r="B11" s="2"/>
+      <x:c r="C11" s="2"/>
+      <x:c r="D11" s="2"/>
+      <x:c r="E11" s="2"/>
+      <x:c r="F11" s="2"/>
+      <x:c r="G11" s="2"/>
+      <x:c r="H11" s="2"/>
+    </x:row>
+    <x:row r="12" ht="22" customHeight="1">
+      <x:c r="A12" s="27" t="str">
+        <x:v>Discount each promised cash flow</x:v>
+      </x:c>
+      <x:c r="B12" s="27"/>
+      <x:c r="C12" s="27"/>
+      <x:c r="D12" s="27"/>
+      <x:c r="E12" s="27"/>
+      <x:c r="F12" s="27"/>
+      <x:c r="G12" s="27"/>
+      <x:c r="H12" s="27"/>
+    </x:row>
+    <x:row r="13" ht="30" customHeight="1">
+      <x:c r="A13" s="38" t="str">
+        <x:v>Year</x:v>
+      </x:c>
+      <x:c r="B13" s="38" t="str">
+        <x:v>Coupon ($)</x:v>
+      </x:c>
+      <x:c r="C13" s="38" t="str">
+        <x:v>Principal ($)</x:v>
+      </x:c>
+      <x:c r="D13" s="38" t="str">
+        <x:v>Total cash flow ($)</x:v>
+      </x:c>
+      <x:c r="E13" s="38" t="str">
+        <x:v>Discount factor</x:v>
+      </x:c>
+      <x:c r="F13" s="38" t="str">
+        <x:v>Present value ($)</x:v>
+      </x:c>
+      <x:c r="G13" s="2"/>
+      <x:c r="H13" s="2"/>
+    </x:row>
+    <x:row r="14" ht="30" customHeight="1">
+      <x:c r="A14" s="78" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="B14" s="82"/>
+      <x:c r="C14" s="82"/>
+      <x:c r="D14" s="82"/>
+      <x:c r="E14" s="85"/>
+      <x:c r="F14" s="82"/>
+      <x:c r="G14" s="2"/>
+      <x:c r="H14" s="2"/>
+    </x:row>
+    <x:row r="15" ht="30" customHeight="1">
+      <x:c r="A15" s="78" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="B15" s="82"/>
+      <x:c r="C15" s="82"/>
+      <x:c r="D15" s="82"/>
+      <x:c r="E15" s="85"/>
+      <x:c r="F15" s="82"/>
+      <x:c r="G15" s="2"/>
+      <x:c r="H15" s="2"/>
+    </x:row>
+    <x:row r="16" ht="30" customHeight="1">
+      <x:c r="A16" s="78" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B16" s="82"/>
+      <x:c r="C16" s="82"/>
+      <x:c r="D16" s="82"/>
+      <x:c r="E16" s="85"/>
+      <x:c r="F16" s="82"/>
+      <x:c r="G16" s="2"/>
+      <x:c r="H16" s="2"/>
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17" s="2"/>
+      <x:c r="B17" s="2"/>
+      <x:c r="C17" s="2"/>
+      <x:c r="D17" s="2"/>
+      <x:c r="E17" s="2"/>
+      <x:c r="F17" s="2"/>
+      <x:c r="G17" s="2"/>
+      <x:c r="H17" s="2"/>
+    </x:row>
+    <x:row r="18" ht="22" customHeight="1">
+      <x:c r="A18" s="27" t="str">
+        <x:v>Bond price and interpretation</x:v>
+      </x:c>
+      <x:c r="B18" s="27"/>
+      <x:c r="C18" s="27"/>
+      <x:c r="D18" s="27"/>
+      <x:c r="E18" s="27"/>
+      <x:c r="F18" s="27"/>
+      <x:c r="G18" s="27"/>
+      <x:c r="H18" s="27"/>
+    </x:row>
+    <x:row r="19" ht="28" customHeight="1">
+      <x:c r="A19" s="71" t="str">
+        <x:v>Bond price — Excel PV function</x:v>
+      </x:c>
+      <x:c r="B19" s="82"/>
+      <x:c r="C19" s="2"/>
+      <x:c r="D19" s="2"/>
+      <x:c r="E19" s="2"/>
+      <x:c r="F19" s="2"/>
+      <x:c r="G19" s="2"/>
+      <x:c r="H19" s="2"/>
+    </x:row>
+    <x:row r="20" ht="28" customHeight="1">
+      <x:c r="A20" s="71" t="str">
+        <x:v>Sum of discounted cash flows</x:v>
+      </x:c>
+      <x:c r="B20" s="82"/>
+      <x:c r="C20" s="2"/>
+      <x:c r="D20" s="2"/>
+      <x:c r="E20" s="2"/>
+      <x:c r="F20" s="2"/>
+      <x:c r="G20" s="2"/>
+      <x:c r="H20" s="2"/>
+    </x:row>
+    <x:row r="21" ht="28" customHeight="1">
+      <x:c r="A21" s="71" t="str">
+        <x:v>Difference between the methods</x:v>
+      </x:c>
+      <x:c r="B21" s="82"/>
+      <x:c r="C21" s="2"/>
+      <x:c r="D21" s="2"/>
+      <x:c r="E21" s="2"/>
+      <x:c r="F21" s="2"/>
+      <x:c r="G21" s="2"/>
+      <x:c r="H21" s="2"/>
+    </x:row>
+    <x:row r="22" ht="28" customHeight="1">
+      <x:c r="A22" s="71" t="str">
+        <x:v>Price relative to par</x:v>
+      </x:c>
+      <x:c r="B22" s="88"/>
+      <x:c r="C22" s="2"/>
+      <x:c r="D22" s="2"/>
+      <x:c r="E22" s="2"/>
+      <x:c r="F22" s="2"/>
+      <x:c r="G22" s="2"/>
+      <x:c r="H22" s="2"/>
+    </x:row>
+    <x:row r="23" ht="28" customHeight="1">
+      <x:c r="A23" s="71" t="str">
+        <x:v>Premium / (discount) dollars</x:v>
+      </x:c>
+      <x:c r="B23" s="82"/>
+      <x:c r="C23" s="2"/>
+      <x:c r="D23" s="2"/>
+      <x:c r="E23" s="2"/>
+      <x:c r="F23" s="2"/>
+      <x:c r="G23" s="2"/>
+      <x:c r="H23" s="2"/>
+    </x:row>
+    <x:row r="24">
+      <x:c r="A24" s="2"/>
+      <x:c r="B24" s="2"/>
+      <x:c r="C24" s="2"/>
+      <x:c r="D24" s="2"/>
+      <x:c r="E24" s="2"/>
+      <x:c r="F24" s="2"/>
+      <x:c r="G24" s="2"/>
+      <x:c r="H24" s="2"/>
+    </x:row>
+    <x:row r="25" ht="22" customHeight="1">
+      <x:c r="A25" s="27" t="str">
+        <x:v>Explain the price</x:v>
+      </x:c>
+      <x:c r="B25" s="27"/>
+      <x:c r="C25" s="27"/>
+      <x:c r="D25" s="27"/>
+      <x:c r="E25" s="27"/>
+      <x:c r="F25" s="27"/>
+      <x:c r="G25" s="27"/>
+      <x:c r="H25" s="27"/>
+    </x:row>
+    <x:row r="26" ht="26" customHeight="1">
+      <x:c r="A26" s="88"/>
+      <x:c r="B26" s="88"/>
+      <x:c r="C26" s="88"/>
+      <x:c r="D26" s="88"/>
+      <x:c r="E26" s="88"/>
+      <x:c r="F26" s="88"/>
+      <x:c r="G26" s="88"/>
+      <x:c r="H26" s="88"/>
+    </x:row>
+    <x:row r="27" ht="26" customHeight="1">
+      <x:c r="A27" s="88"/>
+      <x:c r="B27" s="88"/>
+      <x:c r="C27" s="88"/>
+      <x:c r="D27" s="88"/>
+      <x:c r="E27" s="88"/>
+      <x:c r="F27" s="88"/>
+      <x:c r="G27" s="88"/>
+      <x:c r="H27" s="88"/>
+    </x:row>
+    <x:row r="28" ht="26" customHeight="1">
+      <x:c r="A28" s="88"/>
+      <x:c r="B28" s="88"/>
+      <x:c r="C28" s="88"/>
+      <x:c r="D28" s="88"/>
+      <x:c r="E28" s="88"/>
+      <x:c r="F28" s="88"/>
+      <x:c r="G28" s="88"/>
+      <x:c r="H28" s="88"/>
+    </x:row>
+    <x:row r="29">
+      <x:c r="A29" s="2"/>
+      <x:c r="B29" s="2"/>
+      <x:c r="C29" s="2"/>
+      <x:c r="D29" s="2"/>
+      <x:c r="E29" s="2"/>
+      <x:c r="F29" s="2"/>
+      <x:c r="G29" s="2"/>
+      <x:c r="H29" s="2"/>
+    </x:row>
+    <x:row r="30" ht="26" customHeight="1">
+      <x:c r="A30" s="18" t="str">
+        <x:v>After all three examples: compare the coupon and principal cash flows, then compare the discount factors and prices. What stays fixed, and what moves when market yield changes?</x:v>
+      </x:c>
+      <x:c r="B30" s="19"/>
+      <x:c r="C30" s="19"/>
+      <x:c r="D30" s="19"/>
+      <x:c r="E30" s="19"/>
+      <x:c r="F30" s="19"/>
+      <x:c r="G30" s="19"/>
+      <x:c r="H30" s="20"/>
+    </x:row>
+    <x:row r="31" ht="26" customHeight="1">
+      <x:c r="A31" s="24"/>
+      <x:c r="B31" s="25"/>
+      <x:c r="C31" s="25"/>
+      <x:c r="D31" s="25"/>
+      <x:c r="E31" s="25"/>
+      <x:c r="F31" s="25"/>
+      <x:c r="G31" s="25"/>
+      <x:c r="H31" s="26"/>
+    </x:row>
+    <x:row r="32">
+      <x:c r="A32" s="2"/>
+      <x:c r="B32" s="2"/>
+      <x:c r="C32" s="2"/>
+      <x:c r="D32" s="2"/>
+      <x:c r="E32" s="2"/>
+      <x:c r="F32" s="2"/>
+      <x:c r="G32" s="2"/>
+      <x:c r="H32" s="2"/>
+    </x:row>
+  </x:sheetData>
+  <x:mergeCells>
+    <x:mergeCell ref="A1:H1"/>
+    <x:mergeCell ref="A3:H3"/>
+    <x:mergeCell ref="A5:H5"/>
+    <x:mergeCell ref="D6:H10"/>
+    <x:mergeCell ref="A12:H12"/>
+    <x:mergeCell ref="A18:H18"/>
+    <x:mergeCell ref="A25:H25"/>
+    <x:mergeCell ref="A26:H28"/>
+    <x:mergeCell ref="A30:H31"/>
+  </x:mergeCells>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
@@ -1616,7 +4168,7 @@
       <x:c r="A7" s="2" t="str">
         <x:v>Revenue</x:v>
       </x:c>
-      <x:c r="B7" s="72" t="n">
+      <x:c r="B7" s="76" t="n">
         <x:v>425000</x:v>
       </x:c>
       <x:c r="C7" s="33" t="str">
@@ -1634,7 +4186,7 @@
       <x:c r="A8" s="2" t="str">
         <x:v>Cost of Goods Sold</x:v>
       </x:c>
-      <x:c r="B8" s="72" t="n">
+      <x:c r="B8" s="76" t="n">
         <x:v>272000</x:v>
       </x:c>
       <x:c r="C8" s="33" t="str">
@@ -1652,7 +4204,7 @@
       <x:c r="A9" s="2" t="str">
         <x:v>Gross Profit</x:v>
       </x:c>
-      <x:c r="B9" s="77"/>
+      <x:c r="B9" s="91"/>
       <x:c r="C9" s="33" t="str">
         <x:v>Revenue − COGS</x:v>
       </x:c>
@@ -1668,7 +4220,7 @@
       <x:c r="A10" s="2" t="str">
         <x:v>Selling, General &amp; Admin</x:v>
       </x:c>
-      <x:c r="B10" s="72" t="n">
+      <x:c r="B10" s="76" t="n">
         <x:v>61000</x:v>
       </x:c>
       <x:c r="C10" s="33" t="str">
@@ -1686,7 +4238,7 @@
       <x:c r="A11" s="2" t="str">
         <x:v>Depreciation &amp; Amortization</x:v>
       </x:c>
-      <x:c r="B11" s="72" t="n">
+      <x:c r="B11" s="76" t="n">
         <x:v>18500</x:v>
       </x:c>
       <x:c r="C11" s="33" t="str">
@@ -1704,7 +4256,7 @@
       <x:c r="A12" s="2" t="str">
         <x:v>EBIT (Operating Income)</x:v>
       </x:c>
-      <x:c r="B12" s="77"/>
+      <x:c r="B12" s="91"/>
       <x:c r="C12" s="33" t="str">
         <x:v>Gross Profit − SG&amp;A − D&amp;A</x:v>
       </x:c>
@@ -1720,7 +4272,7 @@
       <x:c r="A13" s="2" t="str">
         <x:v>Interest Expense</x:v>
       </x:c>
-      <x:c r="B13" s="72" t="n">
+      <x:c r="B13" s="76" t="n">
         <x:v>9800</x:v>
       </x:c>
       <x:c r="C13" s="33" t="str">
@@ -1738,7 +4290,7 @@
       <x:c r="A14" s="2" t="str">
         <x:v>EBT</x:v>
       </x:c>
-      <x:c r="B14" s="77"/>
+      <x:c r="B14" s="91"/>
       <x:c r="C14" s="33" t="str">
         <x:v>EBIT − Interest Expense</x:v>
       </x:c>
@@ -1754,7 +4306,7 @@
       <x:c r="A15" s="2" t="str">
         <x:v>Income Tax Rate</x:v>
       </x:c>
-      <x:c r="B15" s="73" t="n">
+      <x:c r="B15" s="75" t="n">
         <x:v>0.25</x:v>
       </x:c>
       <x:c r="C15" s="33" t="str">
@@ -1772,7 +4324,7 @@
       <x:c r="A16" s="2" t="str">
         <x:v>Income Tax Expense</x:v>
       </x:c>
-      <x:c r="B16" s="77"/>
+      <x:c r="B16" s="91"/>
       <x:c r="C16" s="33" t="str">
         <x:v>Positive expense = MAX(EBT,0) × tax rate</x:v>
       </x:c>
@@ -1788,7 +4340,7 @@
       <x:c r="A17" s="2" t="str">
         <x:v>Net Income</x:v>
       </x:c>
-      <x:c r="B17" s="77"/>
+      <x:c r="B17" s="91"/>
       <x:c r="C17" s="33" t="str">
         <x:v>EBT − Income Tax Expense</x:v>
       </x:c>
@@ -1804,7 +4356,7 @@
       <x:c r="A18" s="2" t="str">
         <x:v>Diluted Shares Outstanding (000s)</x:v>
       </x:c>
-      <x:c r="B18" s="72" t="n">
+      <x:c r="B18" s="76" t="n">
         <x:v>50000</x:v>
       </x:c>
       <x:c r="C18" s="33" t="str">
@@ -1822,7 +4374,7 @@
       <x:c r="A19" s="2" t="str">
         <x:v>EPS</x:v>
       </x:c>
-      <x:c r="B19" s="80"/>
+      <x:c r="B19" s="94"/>
       <x:c r="C19" s="33" t="str">
         <x:v>Net Income ÷ diluted shares</x:v>
       </x:c>
@@ -1886,7 +4438,7 @@
       <x:c r="A23" s="2" t="str">
         <x:v>Cash &amp; Cash Equivalents</x:v>
       </x:c>
-      <x:c r="B23" s="72" t="n">
+      <x:c r="B23" s="76" t="n">
         <x:v>32500</x:v>
       </x:c>
       <x:c r="C23" s="33" t="str">
@@ -1898,7 +4450,7 @@
       <x:c r="E23" s="2" t="str">
         <x:v>Accounts Payable</x:v>
       </x:c>
-      <x:c r="F23" s="72" t="n">
+      <x:c r="F23" s="76" t="n">
         <x:v>29400</x:v>
       </x:c>
       <x:c r="G23" s="33" t="str">
@@ -1912,7 +4464,7 @@
       <x:c r="A24" s="2" t="str">
         <x:v>Accounts Receivable</x:v>
       </x:c>
-      <x:c r="B24" s="72" t="n">
+      <x:c r="B24" s="76" t="n">
         <x:v>58000</x:v>
       </x:c>
       <x:c r="C24" s="33" t="str">
@@ -1924,7 +4476,7 @@
       <x:c r="E24" s="2" t="str">
         <x:v>Short-Term Debt</x:v>
       </x:c>
-      <x:c r="F24" s="72" t="n">
+      <x:c r="F24" s="76" t="n">
         <x:v>45000</x:v>
       </x:c>
       <x:c r="G24" s="33" t="str">
@@ -1938,7 +4490,7 @@
       <x:c r="A25" s="2" t="str">
         <x:v>Inventory</x:v>
       </x:c>
-      <x:c r="B25" s="72" t="n">
+      <x:c r="B25" s="76" t="n">
         <x:v>44200</x:v>
       </x:c>
       <x:c r="C25" s="33" t="str">
@@ -1950,7 +4502,7 @@
       <x:c r="E25" s="2" t="str">
         <x:v>Other Current Liabilities</x:v>
       </x:c>
-      <x:c r="F25" s="72" t="n">
+      <x:c r="F25" s="76" t="n">
         <x:v>13100</x:v>
       </x:c>
       <x:c r="G25" s="33" t="str">
@@ -1964,7 +4516,7 @@
       <x:c r="A26" s="2" t="str">
         <x:v>Other Current Assets</x:v>
       </x:c>
-      <x:c r="B26" s="72" t="n">
+      <x:c r="B26" s="76" t="n">
         <x:v>8300</x:v>
       </x:c>
       <x:c r="C26" s="33" t="str">
@@ -1976,7 +4528,7 @@
       <x:c r="E26" s="2" t="str">
         <x:v>Total Current Liabilities</x:v>
       </x:c>
-      <x:c r="F26" s="77"/>
+      <x:c r="F26" s="91"/>
       <x:c r="G26" s="33" t="str">
         <x:v>Sum current liabilities</x:v>
       </x:c>
@@ -1988,7 +4540,7 @@
       <x:c r="A27" s="2" t="str">
         <x:v>Total Current Assets</x:v>
       </x:c>
-      <x:c r="B27" s="77"/>
+      <x:c r="B27" s="91"/>
       <x:c r="C27" s="33" t="str">
         <x:v>Sum current assets</x:v>
       </x:c>
@@ -1998,7 +4550,7 @@
       <x:c r="E27" s="2" t="str">
         <x:v>Existing Long-Term Debt</x:v>
       </x:c>
-      <x:c r="F27" s="72" t="n">
+      <x:c r="F27" s="76" t="n">
         <x:v>110000</x:v>
       </x:c>
       <x:c r="G27" s="33" t="str">
@@ -2012,7 +4564,7 @@
       <x:c r="A28" s="2" t="str">
         <x:v>Property, Plant &amp; Equipment (net)</x:v>
       </x:c>
-      <x:c r="B28" s="72" t="n">
+      <x:c r="B28" s="76" t="n">
         <x:v>312000</x:v>
       </x:c>
       <x:c r="C28" s="33" t="str">
@@ -2024,7 +4576,7 @@
       <x:c r="E28" s="2" t="str">
         <x:v>Deferred Tax Liability</x:v>
       </x:c>
-      <x:c r="F28" s="72" t="n">
+      <x:c r="F28" s="76" t="n">
         <x:v>7200</x:v>
       </x:c>
       <x:c r="G28" s="33" t="str">
@@ -2038,7 +4590,7 @@
       <x:c r="A29" s="2" t="str">
         <x:v>Intangible Assets</x:v>
       </x:c>
-      <x:c r="B29" s="72" t="n">
+      <x:c r="B29" s="76" t="n">
         <x:v>22000</x:v>
       </x:c>
       <x:c r="C29" s="33" t="str">
@@ -2050,7 +4602,7 @@
       <x:c r="E29" s="2" t="str">
         <x:v>Other Long-Term Operating Liabilities</x:v>
       </x:c>
-      <x:c r="F29" s="72" t="n">
+      <x:c r="F29" s="76" t="n">
         <x:v>61000</x:v>
       </x:c>
       <x:c r="G29" s="33" t="str">
@@ -2064,7 +4616,7 @@
       <x:c r="A30" s="2" t="str">
         <x:v>Other Long-Term Assets</x:v>
       </x:c>
-      <x:c r="B30" s="72" t="n">
+      <x:c r="B30" s="76" t="n">
         <x:v>9500</x:v>
       </x:c>
       <x:c r="C30" s="33" t="str">
@@ -2076,7 +4628,7 @@
       <x:c r="E30" s="2" t="str">
         <x:v>Total Liabilities</x:v>
       </x:c>
-      <x:c r="F30" s="77"/>
+      <x:c r="F30" s="91"/>
       <x:c r="G30" s="33" t="str">
         <x:v>Current + all long-term liabilities</x:v>
       </x:c>
@@ -2088,7 +4640,7 @@
       <x:c r="A31" s="2" t="str">
         <x:v>Total Assets</x:v>
       </x:c>
-      <x:c r="B31" s="77"/>
+      <x:c r="B31" s="91"/>
       <x:c r="C31" s="33" t="str">
         <x:v>Current assets + all long-term assets</x:v>
       </x:c>
@@ -2098,7 +4650,7 @@
       <x:c r="E31" s="2" t="str">
         <x:v>Common Stock &amp; APIC</x:v>
       </x:c>
-      <x:c r="F31" s="72" t="n">
+      <x:c r="F31" s="76" t="n">
         <x:v>85000</x:v>
       </x:c>
       <x:c r="G31" s="33" t="str">
@@ -2116,7 +4668,7 @@
       <x:c r="E32" s="2" t="str">
         <x:v>Retained Earnings</x:v>
       </x:c>
-      <x:c r="F32" s="72" t="n">
+      <x:c r="F32" s="76" t="n">
         <x:v>135800</x:v>
       </x:c>
       <x:c r="G32" s="33" t="str">
@@ -2134,7 +4686,7 @@
       <x:c r="E33" s="2" t="str">
         <x:v>Total Equity</x:v>
       </x:c>
-      <x:c r="F33" s="77"/>
+      <x:c r="F33" s="91"/>
       <x:c r="G33" s="33" t="str">
         <x:v>Common Stock &amp; APIC + Retained Earnings</x:v>
       </x:c>
@@ -2150,7 +4702,7 @@
       <x:c r="E34" s="2" t="str">
         <x:v>Total Liabilities &amp; Equity</x:v>
       </x:c>
-      <x:c r="F34" s="77"/>
+      <x:c r="F34" s="91"/>
       <x:c r="G34" s="33" t="str">
         <x:v>Total Liabilities + Total Equity</x:v>
       </x:c>
@@ -2210,7 +4762,7 @@
       <x:c r="A38" s="2" t="str">
         <x:v>Par Value per Bond</x:v>
       </x:c>
-      <x:c r="B38" s="72" t="n">
+      <x:c r="B38" s="76" t="n">
         <x:v>1000</x:v>
       </x:c>
       <x:c r="C38" s="33" t="str">
@@ -2222,13 +4774,13 @@
       <x:c r="E38" s="33" t="str">
         <x:v>Refinancing Target ($000s)</x:v>
       </x:c>
-      <x:c r="F38" s="72" t="n">
+      <x:c r="F38" s="76" t="n">
         <x:v>45000</x:v>
       </x:c>
-      <x:c r="G38" s="72" t="n">
+      <x:c r="G38" s="76" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H38" s="72" t="n">
+      <x:c r="H38" s="76" t="n">
         <x:v>45000</x:v>
       </x:c>
     </x:row>
@@ -2236,7 +4788,7 @@
       <x:c r="A39" s="2" t="str">
         <x:v>Number of Bonds Issued</x:v>
       </x:c>
-      <x:c r="B39" s="72" t="n">
+      <x:c r="B39" s="76" t="n">
         <x:v>200000</x:v>
       </x:c>
       <x:c r="C39" s="33" t="str">
@@ -2248,13 +4800,13 @@
       <x:c r="E39" s="33" t="str">
         <x:v>Fixed CapEx Target ($000s)</x:v>
       </x:c>
-      <x:c r="F39" s="72" t="n">
+      <x:c r="F39" s="76" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G39" s="72" t="n">
+      <x:c r="G39" s="76" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H39" s="72" t="n">
+      <x:c r="H39" s="76" t="n">
         <x:v>100000</x:v>
       </x:c>
     </x:row>
@@ -2262,7 +4814,7 @@
       <x:c r="A40" s="2" t="str">
         <x:v>Annual Coupon Rate</x:v>
       </x:c>
-      <x:c r="B40" s="73" t="n">
+      <x:c r="B40" s="75" t="n">
         <x:v>0.055</x:v>
       </x:c>
       <x:c r="C40" s="33" t="str">
@@ -2274,13 +4826,13 @@
       <x:c r="E40" s="33" t="str">
         <x:v>Allocate Residual Net Proceeds to CapEx?</x:v>
       </x:c>
-      <x:c r="F40" s="72" t="n">
+      <x:c r="F40" s="76" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G40" s="72" t="n">
+      <x:c r="G40" s="76" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="H40" s="72" t="n">
+      <x:c r="H40" s="76" t="n">
         <x:v>0</x:v>
       </x:c>
     </x:row>
@@ -2288,7 +4840,7 @@
       <x:c r="A41" s="2" t="str">
         <x:v>Market YTM</x:v>
       </x:c>
-      <x:c r="B41" s="73" t="n">
+      <x:c r="B41" s="75" t="n">
         <x:v>0.058</x:v>
       </x:c>
       <x:c r="C41" s="33" t="str">
@@ -2300,13 +4852,13 @@
       <x:c r="E41" s="33" t="str">
         <x:v>Revenue Growth</x:v>
       </x:c>
-      <x:c r="F41" s="73" t="n">
+      <x:c r="F41" s="75" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G41" s="73" t="n">
+      <x:c r="G41" s="75" t="n">
         <x:v>0.025</x:v>
       </x:c>
-      <x:c r="H41" s="73" t="n">
+      <x:c r="H41" s="75" t="n">
         <x:v>0.015</x:v>
       </x:c>
     </x:row>
@@ -2314,7 +4866,7 @@
       <x:c r="A42" s="2" t="str">
         <x:v>Settlement Date</x:v>
       </x:c>
-      <x:c r="B42" s="81" t="n">
+      <x:c r="B42" s="95" t="n">
         <x:v>46266</x:v>
       </x:c>
       <x:c r="C42" s="33" t="str">
@@ -2326,13 +4878,13 @@
       <x:c r="E42" s="33" t="str">
         <x:v>EBIT Growth</x:v>
       </x:c>
-      <x:c r="F42" s="73" t="n">
+      <x:c r="F42" s="75" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G42" s="73" t="n">
+      <x:c r="G42" s="75" t="n">
         <x:v>0.025</x:v>
       </x:c>
-      <x:c r="H42" s="73" t="n">
+      <x:c r="H42" s="75" t="n">
         <x:v>0.012</x:v>
       </x:c>
     </x:row>
@@ -2340,7 +4892,7 @@
       <x:c r="A43" s="2" t="str">
         <x:v>Maturity Date</x:v>
       </x:c>
-      <x:c r="B43" s="81" t="n">
+      <x:c r="B43" s="95" t="n">
         <x:v>49919</x:v>
       </x:c>
       <x:c r="C43" s="33" t="str">
@@ -2352,13 +4904,13 @@
       <x:c r="E43" s="33" t="str">
         <x:v>Incremental D&amp;A ($000s)</x:v>
       </x:c>
-      <x:c r="F43" s="72" t="n">
+      <x:c r="F43" s="76" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G43" s="72" t="n">
+      <x:c r="G43" s="76" t="n">
         <x:v>10000</x:v>
       </x:c>
-      <x:c r="H43" s="72" t="n">
+      <x:c r="H43" s="76" t="n">
         <x:v>5000</x:v>
       </x:c>
     </x:row>
@@ -2366,7 +4918,7 @@
       <x:c r="A44" s="2" t="str">
         <x:v>Payment Frequency</x:v>
       </x:c>
-      <x:c r="B44" s="72" t="n">
+      <x:c r="B44" s="76" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="C44" s="33" t="str">
@@ -2378,13 +4930,13 @@
       <x:c r="E44" s="33" t="str">
         <x:v>Cash Retained Rule</x:v>
       </x:c>
-      <x:c r="F44" s="86" t="str">
+      <x:c r="F44" s="99" t="str">
         <x:v>Residual</x:v>
       </x:c>
-      <x:c r="G44" s="86" t="str">
+      <x:c r="G44" s="99" t="str">
         <x:v>None</x:v>
       </x:c>
-      <x:c r="H44" s="86" t="str">
+      <x:c r="H44" s="99" t="str">
         <x:v>Residual</x:v>
       </x:c>
     </x:row>
@@ -2392,7 +4944,7 @@
       <x:c r="A45" s="2" t="str">
         <x:v>Day-Count Basis</x:v>
       </x:c>
-      <x:c r="B45" s="72" t="n">
+      <x:c r="B45" s="76" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="C45" s="33" t="str">
@@ -2410,7 +4962,7 @@
       <x:c r="A46" s="2" t="str">
         <x:v>Issuance Cost Rate</x:v>
       </x:c>
-      <x:c r="B46" s="73" t="n">
+      <x:c r="B46" s="75" t="n">
         <x:v>0.01</x:v>
       </x:c>
       <x:c r="C46" s="33" t="str">
@@ -2436,7 +4988,7 @@
       <x:c r="A47" s="2" t="str">
         <x:v>Observed Clean Price</x:v>
       </x:c>
-      <x:c r="B47" s="82" t="n">
+      <x:c r="B47" s="74" t="n">
         <x:v>96.5</x:v>
       </x:c>
       <x:c r="C47" s="33" t="str">
@@ -2448,7 +5000,7 @@
       <x:c r="E47" s="32" t="str">
         <x:v>Debt / Equity</x:v>
       </x:c>
-      <x:c r="F47" s="87" t="n">
+      <x:c r="F47" s="100" t="n">
         <x:v>1.5</x:v>
       </x:c>
       <x:c r="G47" s="32" t="str">
@@ -2462,7 +5014,7 @@
       <x:c r="A48" s="2" t="str">
         <x:v>Short-Term Debt Rate</x:v>
       </x:c>
-      <x:c r="B48" s="73" t="n">
+      <x:c r="B48" s="75" t="n">
         <x:v>0.085</x:v>
       </x:c>
       <x:c r="C48" s="33" t="str">
@@ -2474,7 +5026,7 @@
       <x:c r="E48" s="32" t="str">
         <x:v>Debt / EBITDA</x:v>
       </x:c>
-      <x:c r="F48" s="87" t="n">
+      <x:c r="F48" s="100" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="G48" s="32" t="str">
@@ -2488,7 +5040,7 @@
       <x:c r="A49" s="2" t="str">
         <x:v>Implied Existing LT Debt Rate</x:v>
       </x:c>
-      <x:c r="B49" s="85"/>
+      <x:c r="B49" s="98"/>
       <x:c r="C49" s="33" t="str">
         <x:v>(Baseline interest − ST interest) ÷ existing LT debt</x:v>
       </x:c>
@@ -2498,7 +5050,7 @@
       <x:c r="E49" s="32" t="str">
         <x:v>Interest Coverage</x:v>
       </x:c>
-      <x:c r="F49" s="87" t="n">
+      <x:c r="F49" s="100" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="G49" s="32" t="str">
@@ -2516,7 +5068,7 @@
       <x:c r="E50" s="32" t="str">
         <x:v>Net Debt / EBITDA</x:v>
       </x:c>
-      <x:c r="F50" s="87" t="n">
+      <x:c r="F50" s="100" t="n">
         <x:v>2.5</x:v>
       </x:c>
       <x:c r="G50" s="32" t="str">
@@ -2534,7 +5086,7 @@
       <x:c r="E51" s="32" t="str">
         <x:v>Current Ratio</x:v>
       </x:c>
-      <x:c r="F51" s="87" t="n">
+      <x:c r="F51" s="100" t="n">
         <x:v>1.5</x:v>
       </x:c>
       <x:c r="G51" s="32" t="str">
@@ -2567,10 +5119,10 @@
       <x:c r="H53" s="2"/>
     </x:row>
     <x:row r="54">
-      <x:c r="A54" s="89" t="str">
+      <x:c r="A54" s="102" t="str">
         <x:v>Rates Fall</x:v>
       </x:c>
-      <x:c r="B54" s="73" t="n">
+      <x:c r="B54" s="75" t="n">
         <x:v>0.045</x:v>
       </x:c>
       <x:c r="C54" s="2"/>
@@ -2581,10 +5133,10 @@
       <x:c r="H54" s="2"/>
     </x:row>
     <x:row r="55">
-      <x:c r="A55" s="89" t="str">
+      <x:c r="A55" s="102" t="str">
         <x:v>Par / Flat</x:v>
       </x:c>
-      <x:c r="B55" s="73" t="n">
+      <x:c r="B55" s="75" t="n">
         <x:v>0.055</x:v>
       </x:c>
       <x:c r="C55" s="2"/>
@@ -2595,10 +5147,10 @@
       <x:c r="H55" s="2"/>
     </x:row>
     <x:row r="56">
-      <x:c r="A56" s="89" t="str">
+      <x:c r="A56" s="102" t="str">
         <x:v>Base Case</x:v>
       </x:c>
-      <x:c r="B56" s="73" t="n">
+      <x:c r="B56" s="75" t="n">
         <x:v>0.058</x:v>
       </x:c>
       <x:c r="C56" s="2"/>
@@ -2609,10 +5161,10 @@
       <x:c r="H56" s="2"/>
     </x:row>
     <x:row r="57">
-      <x:c r="A57" s="89" t="str">
+      <x:c r="A57" s="102" t="str">
         <x:v>Rates Rise</x:v>
       </x:c>
-      <x:c r="B57" s="73" t="n">
+      <x:c r="B57" s="75" t="n">
         <x:v>0.065</x:v>
       </x:c>
       <x:c r="C57" s="2"/>
@@ -2623,10 +5175,10 @@
       <x:c r="H57" s="2"/>
     </x:row>
     <x:row r="58">
-      <x:c r="A58" s="89" t="str">
+      <x:c r="A58" s="102" t="str">
         <x:v>Stress Case</x:v>
       </x:c>
-      <x:c r="B58" s="73" t="n">
+      <x:c r="B58" s="75" t="n">
         <x:v>0.075</x:v>
       </x:c>
       <x:c r="C58" s="2"/>
@@ -2659,7 +5211,7 @@
 </x:worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
@@ -2696,16 +5248,16 @@
       <x:c r="H2" s="2"/>
     </x:row>
     <x:row r="3">
-      <x:c r="A3" s="93" t="str">
+      <x:c r="A3" s="106" t="str">
         <x:v>Use investor signs for valuation: price today is a cash outflow; coupons and principal are future inflows. Use issuer signs for proceeds and interest expense.</x:v>
       </x:c>
-      <x:c r="B3" s="94"/>
-      <x:c r="C3" s="94"/>
-      <x:c r="D3" s="94"/>
-      <x:c r="E3" s="94"/>
-      <x:c r="F3" s="94"/>
-      <x:c r="G3" s="94"/>
-      <x:c r="H3" s="95"/>
+      <x:c r="B3" s="107"/>
+      <x:c r="C3" s="107"/>
+      <x:c r="D3" s="107"/>
+      <x:c r="E3" s="107"/>
+      <x:c r="F3" s="107"/>
+      <x:c r="G3" s="107"/>
+      <x:c r="H3" s="108"/>
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="2"/>
@@ -2749,7 +5301,7 @@
       <x:c r="A7" s="32" t="str">
         <x:v>Par Value per Bond</x:v>
       </x:c>
-      <x:c r="B7" s="98" t="n">
+      <x:c r="B7" s="111" t="n">
         <x:f>'1 Assumptions-Baseline'!B38</x:f>
         <x:v>1000</x:v>
       </x:c>
@@ -2766,7 +5318,7 @@
       <x:c r="A8" s="32" t="str">
         <x:v>Number of Bonds</x:v>
       </x:c>
-      <x:c r="B8" s="98" t="n">
+      <x:c r="B8" s="111" t="n">
         <x:f>'1 Assumptions-Baseline'!B39</x:f>
         <x:v>200000</x:v>
       </x:c>
@@ -2783,7 +5335,7 @@
       <x:c r="A9" s="32" t="str">
         <x:v>Annual Coupon Rate</x:v>
       </x:c>
-      <x:c r="B9" s="99" t="n">
+      <x:c r="B9" s="112" t="n">
         <x:f>'1 Assumptions-Baseline'!B40</x:f>
         <x:v>0.055</x:v>
       </x:c>
@@ -2800,7 +5352,7 @@
       <x:c r="A10" s="32" t="str">
         <x:v>Market YTM</x:v>
       </x:c>
-      <x:c r="B10" s="99" t="n">
+      <x:c r="B10" s="112" t="n">
         <x:f>'1 Assumptions-Baseline'!B41</x:f>
         <x:v>0.058</x:v>
       </x:c>
@@ -2817,7 +5369,7 @@
       <x:c r="A11" s="32" t="str">
         <x:v>Settlement Date</x:v>
       </x:c>
-      <x:c r="B11" s="100" t="n">
+      <x:c r="B11" s="113" t="n">
         <x:f>'1 Assumptions-Baseline'!B42</x:f>
         <x:v>46266</x:v>
       </x:c>
@@ -2834,7 +5386,7 @@
       <x:c r="A12" s="32" t="str">
         <x:v>Maturity Date</x:v>
       </x:c>
-      <x:c r="B12" s="100" t="n">
+      <x:c r="B12" s="113" t="n">
         <x:f>'1 Assumptions-Baseline'!B43</x:f>
         <x:v>49919</x:v>
       </x:c>
@@ -2851,7 +5403,7 @@
       <x:c r="A13" s="32" t="str">
         <x:v>Payment Frequency</x:v>
       </x:c>
-      <x:c r="B13" s="98" t="n">
+      <x:c r="B13" s="111" t="n">
         <x:f>'1 Assumptions-Baseline'!B44</x:f>
         <x:v>2</x:v>
       </x:c>
@@ -2868,7 +5420,7 @@
       <x:c r="A14" s="32" t="str">
         <x:v>Day-Count Basis</x:v>
       </x:c>
-      <x:c r="B14" s="98" t="n">
+      <x:c r="B14" s="111" t="n">
         <x:f>'1 Assumptions-Baseline'!B45</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -2885,7 +5437,7 @@
       <x:c r="A15" s="32" t="str">
         <x:v>Issuance Cost Rate</x:v>
       </x:c>
-      <x:c r="B15" s="99" t="n">
+      <x:c r="B15" s="112" t="n">
         <x:f>'1 Assumptions-Baseline'!B46</x:f>
         <x:v>0.01</x:v>
       </x:c>
@@ -2942,7 +5494,7 @@
       <x:c r="A19" s="2" t="str">
         <x:v>Coupon per Period ($ / bond)</x:v>
       </x:c>
-      <x:c r="B19" s="103"/>
+      <x:c r="B19" s="82"/>
       <x:c r="C19" s="33" t="str">
         <x:v>Par × coupon rate ÷ frequency</x:v>
       </x:c>
@@ -2958,7 +5510,7 @@
       <x:c r="A20" s="2" t="str">
         <x:v>Market Yield per Period</x:v>
       </x:c>
-      <x:c r="B20" s="85"/>
+      <x:c r="B20" s="98"/>
       <x:c r="C20" s="33" t="str">
         <x:v>YTM ÷ frequency</x:v>
       </x:c>
@@ -2974,7 +5526,7 @@
       <x:c r="A21" s="2" t="str">
         <x:v>Total Coupon Periods</x:v>
       </x:c>
-      <x:c r="B21" s="77"/>
+      <x:c r="B21" s="91"/>
       <x:c r="C21" s="33" t="str">
         <x:v>Years × frequency, or dated equivalent</x:v>
       </x:c>
@@ -2990,7 +5542,7 @@
       <x:c r="A22" s="2" t="str">
         <x:v>Price per Bond — PV</x:v>
       </x:c>
-      <x:c r="B22" s="103"/>
+      <x:c r="B22" s="82"/>
       <x:c r="C22" s="33" t="str">
         <x:v>Negative PV of investor inflows</x:v>
       </x:c>
@@ -3006,7 +5558,7 @@
       <x:c r="A23" s="2" t="str">
         <x:v>Price per Bond — PRICE</x:v>
       </x:c>
-      <x:c r="B23" s="103"/>
+      <x:c r="B23" s="82"/>
       <x:c r="C23" s="33" t="str">
         <x:v>PRICE × par ÷ 100</x:v>
       </x:c>
@@ -3022,7 +5574,7 @@
       <x:c r="A24" s="2" t="str">
         <x:v>PV vs PRICE Difference</x:v>
       </x:c>
-      <x:c r="B24" s="103"/>
+      <x:c r="B24" s="82"/>
       <x:c r="C24" s="33" t="str">
         <x:v>PV price − PRICE price</x:v>
       </x:c>
@@ -3038,7 +5590,7 @@
       <x:c r="A25" s="2" t="str">
         <x:v>Gross Offering Proceeds ($000s)</x:v>
       </x:c>
-      <x:c r="B25" s="106"/>
+      <x:c r="B25" s="116"/>
       <x:c r="C25" s="33" t="str">
         <x:v>Price × bonds ÷ 1,000</x:v>
       </x:c>
@@ -3054,7 +5606,7 @@
       <x:c r="A26" s="2" t="str">
         <x:v>Issuance Costs ($000s)</x:v>
       </x:c>
-      <x:c r="B26" s="106"/>
+      <x:c r="B26" s="116"/>
       <x:c r="C26" s="33" t="str">
         <x:v>Gross proceeds × issuance cost rate</x:v>
       </x:c>
@@ -3070,7 +5622,7 @@
       <x:c r="A27" s="2" t="str">
         <x:v>Net Proceeds / Initial Carrying Amount ($000s)</x:v>
       </x:c>
-      <x:c r="B27" s="106"/>
+      <x:c r="B27" s="116"/>
       <x:c r="C27" s="33" t="str">
         <x:v>Gross proceeds − issuance costs</x:v>
       </x:c>
@@ -3086,7 +5638,7 @@
       <x:c r="A28" s="2" t="str">
         <x:v>Face Discount + Issuance Costs ($000s)</x:v>
       </x:c>
-      <x:c r="B28" s="106"/>
+      <x:c r="B28" s="116"/>
       <x:c r="C28" s="33" t="str">
         <x:v>Face amount − initial carrying amount</x:v>
       </x:c>
@@ -3102,7 +5654,7 @@
       <x:c r="A29" s="2" t="str">
         <x:v>Annual Cash Coupon ($000s)</x:v>
       </x:c>
-      <x:c r="B29" s="106"/>
+      <x:c r="B29" s="116"/>
       <x:c r="C29" s="33" t="str">
         <x:v>Face amount × coupon rate</x:v>
       </x:c>
@@ -3118,7 +5670,7 @@
       <x:c r="A30" s="2" t="str">
         <x:v>Observed Clean Price ($ per $100)</x:v>
       </x:c>
-      <x:c r="B30" s="103"/>
+      <x:c r="B30" s="82"/>
       <x:c r="C30" s="33" t="str">
         <x:v>Link the separate observed quote</x:v>
       </x:c>
@@ -3134,7 +5686,7 @@
       <x:c r="A31" s="2" t="str">
         <x:v>YIELD from Observed Price</x:v>
       </x:c>
-      <x:c r="B31" s="85"/>
+      <x:c r="B31" s="98"/>
       <x:c r="C31" s="33" t="str">
         <x:v>YIELD using dated terms</x:v>
       </x:c>
@@ -3150,7 +5702,7 @@
       <x:c r="A32" s="2" t="str">
         <x:v>RATE from Observed Price</x:v>
       </x:c>
-      <x:c r="B32" s="85"/>
+      <x:c r="B32" s="98"/>
       <x:c r="C32" s="33" t="str">
         <x:v>RATE periodic result × frequency</x:v>
       </x:c>
@@ -3166,7 +5718,7 @@
       <x:c r="A33" s="2" t="str">
         <x:v>Issuer EIR per Period</x:v>
       </x:c>
-      <x:c r="B33" s="85"/>
+      <x:c r="B33" s="98"/>
       <x:c r="C33" s="33" t="str">
         <x:v>RATE using net proceeds as PV</x:v>
       </x:c>
@@ -3182,7 +5734,7 @@
       <x:c r="A34" s="2" t="str">
         <x:v>Issuer Nominal Annual EIR</x:v>
       </x:c>
-      <x:c r="B34" s="85"/>
+      <x:c r="B34" s="98"/>
       <x:c r="C34" s="33" t="str">
         <x:v>Periodic issuer EIR × frequency</x:v>
       </x:c>
@@ -3198,7 +5750,7 @@
       <x:c r="A35" s="2" t="str">
         <x:v>Period 1 Interest Expense ($000s)</x:v>
       </x:c>
-      <x:c r="B35" s="106"/>
+      <x:c r="B35" s="116"/>
       <x:c r="C35" s="33" t="str">
         <x:v>Opening carrying value × periodic EIR</x:v>
       </x:c>
@@ -3214,7 +5766,7 @@
       <x:c r="A36" s="2" t="str">
         <x:v>Ending Carrying Value — Period 1</x:v>
       </x:c>
-      <x:c r="B36" s="106"/>
+      <x:c r="B36" s="116"/>
       <x:c r="C36" s="33" t="str">
         <x:v>Opening carry + interest expense − cash coupon</x:v>
       </x:c>
@@ -3230,7 +5782,7 @@
       <x:c r="A37" s="2" t="str">
         <x:v>Period 2 Interest Expense ($000s)</x:v>
       </x:c>
-      <x:c r="B37" s="106"/>
+      <x:c r="B37" s="116"/>
       <x:c r="C37" s="33" t="str">
         <x:v>Period 1 ending carry × periodic EIR</x:v>
       </x:c>
@@ -3246,7 +5798,7 @@
       <x:c r="A38" s="2" t="str">
         <x:v>Year 1 New-Bond Interest Expense ($000s)</x:v>
       </x:c>
-      <x:c r="B38" s="106"/>
+      <x:c r="B38" s="116"/>
       <x:c r="C38" s="33" t="str">
         <x:v>Period 1 + Period 2 expense</x:v>
       </x:c>
@@ -3262,7 +5814,7 @@
       <x:c r="A39" s="2" t="str">
         <x:v>Ending Carrying Value — Year 1</x:v>
       </x:c>
-      <x:c r="B39" s="106"/>
+      <x:c r="B39" s="116"/>
       <x:c r="C39" s="33" t="str">
         <x:v>Period 1 ending carry + period 2 expense − cash coupon</x:v>
       </x:c>
@@ -3332,14 +5884,14 @@
       <x:c r="A44" s="2" t="str">
         <x:v>Rates Fall</x:v>
       </x:c>
-      <x:c r="B44" s="99" t="n">
+      <x:c r="B44" s="112" t="n">
         <x:f>'1 Assumptions-Baseline'!B54</x:f>
         <x:v>0.045</x:v>
       </x:c>
-      <x:c r="C44" s="103"/>
-      <x:c r="D44" s="103"/>
-      <x:c r="E44" s="103"/>
-      <x:c r="F44" s="108" t="str">
+      <x:c r="C44" s="82"/>
+      <x:c r="D44" s="82"/>
+      <x:c r="E44" s="82"/>
+      <x:c r="F44" s="117" t="str">
         <x:v>Coupon exceeds market yield → premium</x:v>
       </x:c>
       <x:c r="G44" s="2"/>
@@ -3349,14 +5901,14 @@
       <x:c r="A45" s="2" t="str">
         <x:v>Par / Flat</x:v>
       </x:c>
-      <x:c r="B45" s="99" t="n">
+      <x:c r="B45" s="112" t="n">
         <x:f>'1 Assumptions-Baseline'!B55</x:f>
         <x:v>0.055</x:v>
       </x:c>
-      <x:c r="C45" s="103"/>
-      <x:c r="D45" s="103"/>
-      <x:c r="E45" s="103"/>
-      <x:c r="F45" s="108" t="str">
+      <x:c r="C45" s="82"/>
+      <x:c r="D45" s="82"/>
+      <x:c r="E45" s="82"/>
+      <x:c r="F45" s="117" t="str">
         <x:v>Coupon equals market yield → par</x:v>
       </x:c>
       <x:c r="G45" s="2"/>
@@ -3366,14 +5918,14 @@
       <x:c r="A46" s="2" t="str">
         <x:v>Base Case</x:v>
       </x:c>
-      <x:c r="B46" s="99" t="n">
+      <x:c r="B46" s="112" t="n">
         <x:f>'1 Assumptions-Baseline'!B56</x:f>
         <x:v>0.058</x:v>
       </x:c>
-      <x:c r="C46" s="103"/>
-      <x:c r="D46" s="103"/>
-      <x:c r="E46" s="103"/>
-      <x:c r="F46" s="108" t="str">
+      <x:c r="C46" s="82"/>
+      <x:c r="D46" s="82"/>
+      <x:c r="E46" s="82"/>
+      <x:c r="F46" s="117" t="str">
         <x:v>Market yield exceeds coupon → discount</x:v>
       </x:c>
       <x:c r="G46" s="2"/>
@@ -3383,14 +5935,14 @@
       <x:c r="A47" s="2" t="str">
         <x:v>Rates Rise</x:v>
       </x:c>
-      <x:c r="B47" s="99" t="n">
+      <x:c r="B47" s="112" t="n">
         <x:f>'1 Assumptions-Baseline'!B57</x:f>
         <x:v>0.065</x:v>
       </x:c>
-      <x:c r="C47" s="103"/>
-      <x:c r="D47" s="103"/>
-      <x:c r="E47" s="103"/>
-      <x:c r="F47" s="108" t="str">
+      <x:c r="C47" s="82"/>
+      <x:c r="D47" s="82"/>
+      <x:c r="E47" s="82"/>
+      <x:c r="F47" s="117" t="str">
         <x:v>Discount widens</x:v>
       </x:c>
       <x:c r="G47" s="2"/>
@@ -3400,14 +5952,14 @@
       <x:c r="A48" s="2" t="str">
         <x:v>Stress Case</x:v>
       </x:c>
-      <x:c r="B48" s="99" t="n">
+      <x:c r="B48" s="112" t="n">
         <x:f>'1 Assumptions-Baseline'!B58</x:f>
         <x:v>0.075</x:v>
       </x:c>
-      <x:c r="C48" s="103"/>
-      <x:c r="D48" s="103"/>
-      <x:c r="E48" s="103"/>
-      <x:c r="F48" s="108" t="str">
+      <x:c r="C48" s="82"/>
+      <x:c r="D48" s="82"/>
+      <x:c r="E48" s="82"/>
+      <x:c r="F48" s="117" t="str">
         <x:v>Deep discount; funding shortfall grows</x:v>
       </x:c>
       <x:c r="G48" s="2"/>
@@ -3468,7 +6020,7 @@
 </x:worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
@@ -3505,16 +6057,16 @@
       <x:c r="H2" s="2"/>
     </x:row>
     <x:row r="3">
-      <x:c r="A3" s="93" t="str">
+      <x:c r="A3" s="106" t="str">
         <x:v>Every dollar of gross proceeds must be assigned exactly once. Discount and fees reduce cash received but do not reduce the promised face amount used in credit ratios.</x:v>
       </x:c>
-      <x:c r="B3" s="94"/>
-      <x:c r="C3" s="94"/>
-      <x:c r="D3" s="94"/>
-      <x:c r="E3" s="94"/>
-      <x:c r="F3" s="94"/>
-      <x:c r="G3" s="94"/>
-      <x:c r="H3" s="95"/>
+      <x:c r="B3" s="107"/>
+      <x:c r="C3" s="107"/>
+      <x:c r="D3" s="107"/>
+      <x:c r="E3" s="107"/>
+      <x:c r="F3" s="107"/>
+      <x:c r="G3" s="107"/>
+      <x:c r="H3" s="108"/>
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="2"/>
@@ -3557,18 +6109,18 @@
       <x:c r="H6" s="2"/>
     </x:row>
     <x:row r="7" ht="28" customHeight="1">
-      <x:c r="A7" s="111" t="str">
+      <x:c r="A7" s="120" t="str">
         <x:v>Gross Bond Proceeds</x:v>
       </x:c>
-      <x:c r="B7" s="109" t="n">
+      <x:c r="B7" s="118" t="n">
         <x:f>'2 Bond Pricing'!$B$25</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="C7" s="109" t="n">
+      <x:c r="C7" s="118" t="n">
         <x:f>'2 Bond Pricing'!$B$25</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="D7" s="109" t="n">
+      <x:c r="D7" s="118" t="n">
         <x:f>'2 Bond Pricing'!$B$25</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -3578,7 +6130,7 @@
       <x:c r="H7" s="2"/>
     </x:row>
     <x:row r="8" ht="28" customHeight="1">
-      <x:c r="A8" s="111" t="str"/>
+      <x:c r="A8" s="120" t="str"/>
       <x:c r="B8" s="2"/>
       <x:c r="C8" s="2"/>
       <x:c r="D8" s="2"/>
@@ -3588,79 +6140,79 @@
       <x:c r="H8" s="2"/>
     </x:row>
     <x:row r="9" ht="28" customHeight="1">
-      <x:c r="A9" s="111" t="str">
+      <x:c r="A9" s="120" t="str">
         <x:v>Issuance Costs</x:v>
       </x:c>
-      <x:c r="B9" s="106"/>
-      <x:c r="C9" s="106"/>
-      <x:c r="D9" s="106"/>
+      <x:c r="B9" s="116"/>
+      <x:c r="C9" s="116"/>
+      <x:c r="D9" s="116"/>
       <x:c r="E9" s="2"/>
       <x:c r="F9" s="2"/>
       <x:c r="G9" s="2"/>
       <x:c r="H9" s="2"/>
     </x:row>
     <x:row r="10" ht="28" customHeight="1">
-      <x:c r="A10" s="111" t="str">
+      <x:c r="A10" s="120" t="str">
         <x:v>Refinance Short-Term Debt</x:v>
       </x:c>
-      <x:c r="B10" s="106"/>
-      <x:c r="C10" s="106"/>
-      <x:c r="D10" s="106"/>
+      <x:c r="B10" s="116"/>
+      <x:c r="C10" s="116"/>
+      <x:c r="D10" s="116"/>
       <x:c r="E10" s="2"/>
       <x:c r="F10" s="2"/>
       <x:c r="G10" s="2"/>
       <x:c r="H10" s="2"/>
     </x:row>
     <x:row r="11" ht="28" customHeight="1">
-      <x:c r="A11" s="111" t="str">
+      <x:c r="A11" s="120" t="str">
         <x:v>Capital Expenditure</x:v>
       </x:c>
-      <x:c r="B11" s="106"/>
-      <x:c r="C11" s="106"/>
-      <x:c r="D11" s="106"/>
+      <x:c r="B11" s="116"/>
+      <x:c r="C11" s="116"/>
+      <x:c r="D11" s="116"/>
       <x:c r="E11" s="2"/>
       <x:c r="F11" s="2"/>
       <x:c r="G11" s="2"/>
       <x:c r="H11" s="2"/>
     </x:row>
     <x:row r="12" ht="28" customHeight="1">
-      <x:c r="A12" s="111" t="str">
+      <x:c r="A12" s="120" t="str">
         <x:v>Cash Retained</x:v>
       </x:c>
-      <x:c r="B12" s="106"/>
-      <x:c r="C12" s="106"/>
-      <x:c r="D12" s="106"/>
+      <x:c r="B12" s="116"/>
+      <x:c r="C12" s="116"/>
+      <x:c r="D12" s="116"/>
       <x:c r="E12" s="2"/>
       <x:c r="F12" s="2"/>
       <x:c r="G12" s="2"/>
       <x:c r="H12" s="2"/>
     </x:row>
     <x:row r="13" ht="28" customHeight="1">
-      <x:c r="A13" s="111" t="str">
+      <x:c r="A13" s="120" t="str">
         <x:v>Total Uses</x:v>
       </x:c>
-      <x:c r="B13" s="106"/>
-      <x:c r="C13" s="106"/>
-      <x:c r="D13" s="106"/>
+      <x:c r="B13" s="116"/>
+      <x:c r="C13" s="116"/>
+      <x:c r="D13" s="116"/>
       <x:c r="E13" s="2"/>
       <x:c r="F13" s="2"/>
       <x:c r="G13" s="2"/>
       <x:c r="H13" s="2"/>
     </x:row>
     <x:row r="14" ht="28" customHeight="1">
-      <x:c r="A14" s="111" t="str">
+      <x:c r="A14" s="120" t="str">
         <x:v>Sources − Uses Check</x:v>
       </x:c>
-      <x:c r="B14" s="106"/>
-      <x:c r="C14" s="106"/>
-      <x:c r="D14" s="106"/>
+      <x:c r="B14" s="116"/>
+      <x:c r="C14" s="116"/>
+      <x:c r="D14" s="116"/>
       <x:c r="E14" s="2"/>
       <x:c r="F14" s="2"/>
       <x:c r="G14" s="2"/>
       <x:c r="H14" s="2"/>
     </x:row>
     <x:row r="15" ht="28" customHeight="1">
-      <x:c r="A15" s="111" t="str"/>
+      <x:c r="A15" s="120" t="str"/>
       <x:c r="B15" s="2"/>
       <x:c r="C15" s="2"/>
       <x:c r="D15" s="2"/>
@@ -3670,18 +6222,18 @@
       <x:c r="H15" s="2"/>
     </x:row>
     <x:row r="16" ht="28" customHeight="1">
-      <x:c r="A16" s="111" t="str">
+      <x:c r="A16" s="120" t="str">
         <x:v>Net Proceeds</x:v>
       </x:c>
-      <x:c r="B16" s="109" t="n">
+      <x:c r="B16" s="118" t="n">
         <x:f>'2 Bond Pricing'!$B$27</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="C16" s="109" t="n">
+      <x:c r="C16" s="118" t="n">
         <x:f>'2 Bond Pricing'!$B$27</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="D16" s="109" t="n">
+      <x:c r="D16" s="118" t="n">
         <x:f>'2 Bond Pricing'!$B$27</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -3691,24 +6243,24 @@
       <x:c r="H16" s="2"/>
     </x:row>
     <x:row r="17" ht="28" customHeight="1">
-      <x:c r="A17" s="111" t="str">
+      <x:c r="A17" s="120" t="str">
         <x:v>Refi + CapEx + Cash Retained</x:v>
       </x:c>
-      <x:c r="B17" s="106"/>
-      <x:c r="C17" s="106"/>
-      <x:c r="D17" s="106"/>
+      <x:c r="B17" s="116"/>
+      <x:c r="C17" s="116"/>
+      <x:c r="D17" s="116"/>
       <x:c r="E17" s="2"/>
       <x:c r="F17" s="2"/>
       <x:c r="G17" s="2"/>
       <x:c r="H17" s="2"/>
     </x:row>
     <x:row r="18" ht="28" customHeight="1">
-      <x:c r="A18" s="111" t="str">
+      <x:c r="A18" s="120" t="str">
         <x:v>Net Proceeds − Deployment Check</x:v>
       </x:c>
-      <x:c r="B18" s="106"/>
-      <x:c r="C18" s="106"/>
-      <x:c r="D18" s="106"/>
+      <x:c r="B18" s="116"/>
+      <x:c r="C18" s="116"/>
+      <x:c r="D18" s="116"/>
       <x:c r="E18" s="2"/>
       <x:c r="F18" s="2"/>
       <x:c r="G18" s="2"/>
@@ -3755,18 +6307,18 @@
       <x:c r="H21" s="2"/>
     </x:row>
     <x:row r="22" ht="28" customHeight="1">
-      <x:c r="A22" s="111" t="str">
+      <x:c r="A22" s="120" t="str">
         <x:v>Beginning Short-Term Debt</x:v>
       </x:c>
-      <x:c r="B22" s="109" t="n">
+      <x:c r="B22" s="118" t="n">
         <x:f>'1 Assumptions-Baseline'!$F$24</x:f>
         <x:v>45000</x:v>
       </x:c>
-      <x:c r="C22" s="109" t="n">
+      <x:c r="C22" s="118" t="n">
         <x:f>'1 Assumptions-Baseline'!$F$24</x:f>
         <x:v>45000</x:v>
       </x:c>
-      <x:c r="D22" s="109" t="n">
+      <x:c r="D22" s="118" t="n">
         <x:f>'1 Assumptions-Baseline'!$F$24</x:f>
         <x:v>45000</x:v>
       </x:c>
@@ -3776,42 +6328,42 @@
       <x:c r="H22" s="2"/>
     </x:row>
     <x:row r="23" ht="28" customHeight="1">
-      <x:c r="A23" s="111" t="str">
+      <x:c r="A23" s="120" t="str">
         <x:v>Refinancing Repayment</x:v>
       </x:c>
-      <x:c r="B23" s="106"/>
-      <x:c r="C23" s="106"/>
-      <x:c r="D23" s="106"/>
+      <x:c r="B23" s="116"/>
+      <x:c r="C23" s="116"/>
+      <x:c r="D23" s="116"/>
       <x:c r="E23" s="2"/>
       <x:c r="F23" s="2"/>
       <x:c r="G23" s="2"/>
       <x:c r="H23" s="2"/>
     </x:row>
     <x:row r="24" ht="28" customHeight="1">
-      <x:c r="A24" s="111" t="str">
+      <x:c r="A24" s="120" t="str">
         <x:v>Ending Short-Term Debt</x:v>
       </x:c>
-      <x:c r="B24" s="106"/>
-      <x:c r="C24" s="106"/>
-      <x:c r="D24" s="106"/>
+      <x:c r="B24" s="116"/>
+      <x:c r="C24" s="116"/>
+      <x:c r="D24" s="116"/>
       <x:c r="E24" s="2"/>
       <x:c r="F24" s="2"/>
       <x:c r="G24" s="2"/>
       <x:c r="H24" s="2"/>
     </x:row>
     <x:row r="25" ht="28" customHeight="1">
-      <x:c r="A25" s="111" t="str">
+      <x:c r="A25" s="120" t="str">
         <x:v>Beginning Existing LT Debt — Face</x:v>
       </x:c>
-      <x:c r="B25" s="109" t="n">
+      <x:c r="B25" s="118" t="n">
         <x:f>'1 Assumptions-Baseline'!$F$27</x:f>
         <x:v>110000</x:v>
       </x:c>
-      <x:c r="C25" s="109" t="n">
+      <x:c r="C25" s="118" t="n">
         <x:f>'1 Assumptions-Baseline'!$F$27</x:f>
         <x:v>110000</x:v>
       </x:c>
-      <x:c r="D25" s="109" t="n">
+      <x:c r="D25" s="118" t="n">
         <x:f>'1 Assumptions-Baseline'!$F$27</x:f>
         <x:v>110000</x:v>
       </x:c>
@@ -3821,60 +6373,60 @@
       <x:c r="H25" s="2"/>
     </x:row>
     <x:row r="26" ht="28" customHeight="1">
-      <x:c r="A26" s="111" t="str">
+      <x:c r="A26" s="120" t="str">
         <x:v>New Bond — Face</x:v>
       </x:c>
-      <x:c r="B26" s="106"/>
-      <x:c r="C26" s="106"/>
-      <x:c r="D26" s="106"/>
+      <x:c r="B26" s="116"/>
+      <x:c r="C26" s="116"/>
+      <x:c r="D26" s="116"/>
       <x:c r="E26" s="2"/>
       <x:c r="F26" s="2"/>
       <x:c r="G26" s="2"/>
       <x:c r="H26" s="2"/>
     </x:row>
     <x:row r="27" ht="28" customHeight="1">
-      <x:c r="A27" s="111" t="str">
+      <x:c r="A27" s="120" t="str">
         <x:v>Ending Gross Face Debt</x:v>
       </x:c>
-      <x:c r="B27" s="106"/>
-      <x:c r="C27" s="106"/>
-      <x:c r="D27" s="106"/>
+      <x:c r="B27" s="116"/>
+      <x:c r="C27" s="116"/>
+      <x:c r="D27" s="116"/>
       <x:c r="E27" s="2"/>
       <x:c r="F27" s="2"/>
       <x:c r="G27" s="2"/>
       <x:c r="H27" s="2"/>
     </x:row>
     <x:row r="28" ht="28" customHeight="1">
-      <x:c r="A28" s="111" t="str">
+      <x:c r="A28" s="120" t="str">
         <x:v>New Bond — Initial Carrying Value</x:v>
       </x:c>
-      <x:c r="B28" s="106"/>
-      <x:c r="C28" s="106"/>
-      <x:c r="D28" s="106"/>
+      <x:c r="B28" s="116"/>
+      <x:c r="C28" s="116"/>
+      <x:c r="D28" s="116"/>
       <x:c r="E28" s="2"/>
       <x:c r="F28" s="2"/>
       <x:c r="G28" s="2"/>
       <x:c r="H28" s="2"/>
     </x:row>
     <x:row r="29" ht="28" customHeight="1">
-      <x:c r="A29" s="111" t="str">
+      <x:c r="A29" s="120" t="str">
         <x:v>Contra-Debt: Discount + Issuance Costs</x:v>
       </x:c>
-      <x:c r="B29" s="106"/>
-      <x:c r="C29" s="106"/>
-      <x:c r="D29" s="106"/>
+      <x:c r="B29" s="116"/>
+      <x:c r="C29" s="116"/>
+      <x:c r="D29" s="116"/>
       <x:c r="E29" s="2"/>
       <x:c r="F29" s="2"/>
       <x:c r="G29" s="2"/>
       <x:c r="H29" s="2"/>
     </x:row>
     <x:row r="30" ht="28" customHeight="1">
-      <x:c r="A30" s="111" t="str">
+      <x:c r="A30" s="120" t="str">
         <x:v>New Bond Face − Carrying − Contra Check</x:v>
       </x:c>
-      <x:c r="B30" s="106"/>
-      <x:c r="C30" s="106"/>
-      <x:c r="D30" s="106"/>
+      <x:c r="B30" s="116"/>
+      <x:c r="C30" s="116"/>
+      <x:c r="D30" s="116"/>
       <x:c r="E30" s="2"/>
       <x:c r="F30" s="2"/>
       <x:c r="G30" s="2"/>
@@ -3954,7 +6506,7 @@
 </x:worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
@@ -3991,16 +6543,16 @@
       <x:c r="H2" s="2"/>
     </x:row>
     <x:row r="3">
-      <x:c r="A3" s="93" t="str">
+      <x:c r="A3" s="106" t="str">
         <x:v>Timing discipline: the balance sheet is measured immediately after closing; the income statement and EPS show the first full year after closing. Closing equity is unchanged because no shares are issued and year-1 earnings have not yet accumulated.</x:v>
       </x:c>
-      <x:c r="B3" s="94"/>
-      <x:c r="C3" s="94"/>
-      <x:c r="D3" s="94"/>
-      <x:c r="E3" s="94"/>
-      <x:c r="F3" s="94"/>
-      <x:c r="G3" s="94"/>
-      <x:c r="H3" s="95"/>
+      <x:c r="B3" s="107"/>
+      <x:c r="C3" s="107"/>
+      <x:c r="D3" s="107"/>
+      <x:c r="E3" s="107"/>
+      <x:c r="F3" s="107"/>
+      <x:c r="G3" s="107"/>
+      <x:c r="H3" s="108"/>
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="2"/>
@@ -4048,13 +6600,13 @@
       <x:c r="A7" s="2" t="str">
         <x:v>Cash &amp; Cash Equivalents</x:v>
       </x:c>
-      <x:c r="B7" s="109" t="n">
+      <x:c r="B7" s="118" t="n">
         <x:f>'1 Assumptions-Baseline'!B23</x:f>
         <x:v>32500</x:v>
       </x:c>
-      <x:c r="C7" s="106"/>
-      <x:c r="D7" s="106"/>
-      <x:c r="E7" s="106"/>
+      <x:c r="C7" s="116"/>
+      <x:c r="D7" s="116"/>
+      <x:c r="E7" s="116"/>
       <x:c r="F7" s="2"/>
       <x:c r="G7" s="2"/>
       <x:c r="H7" s="2"/>
@@ -4063,13 +6615,13 @@
       <x:c r="A8" s="2" t="str">
         <x:v>Total Current Assets</x:v>
       </x:c>
-      <x:c r="B8" s="109" t="n">
+      <x:c r="B8" s="118" t="n">
         <x:f>'1 Assumptions-Baseline'!B27</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="C8" s="106"/>
-      <x:c r="D8" s="106"/>
-      <x:c r="E8" s="106"/>
+      <x:c r="C8" s="116"/>
+      <x:c r="D8" s="116"/>
+      <x:c r="E8" s="116"/>
       <x:c r="F8" s="2"/>
       <x:c r="G8" s="2"/>
       <x:c r="H8" s="2"/>
@@ -4078,13 +6630,13 @@
       <x:c r="A9" s="2" t="str">
         <x:v>PP&amp;E (net)</x:v>
       </x:c>
-      <x:c r="B9" s="109" t="n">
+      <x:c r="B9" s="118" t="n">
         <x:f>'1 Assumptions-Baseline'!B28</x:f>
         <x:v>312000</x:v>
       </x:c>
-      <x:c r="C9" s="106"/>
-      <x:c r="D9" s="106"/>
-      <x:c r="E9" s="106"/>
+      <x:c r="C9" s="116"/>
+      <x:c r="D9" s="116"/>
+      <x:c r="E9" s="116"/>
       <x:c r="F9" s="2"/>
       <x:c r="G9" s="2"/>
       <x:c r="H9" s="2"/>
@@ -4093,13 +6645,13 @@
       <x:c r="A10" s="2" t="str">
         <x:v>Intangible Assets</x:v>
       </x:c>
-      <x:c r="B10" s="109" t="n">
+      <x:c r="B10" s="118" t="n">
         <x:f>'1 Assumptions-Baseline'!B29</x:f>
         <x:v>22000</x:v>
       </x:c>
-      <x:c r="C10" s="106"/>
-      <x:c r="D10" s="106"/>
-      <x:c r="E10" s="106"/>
+      <x:c r="C10" s="116"/>
+      <x:c r="D10" s="116"/>
+      <x:c r="E10" s="116"/>
       <x:c r="F10" s="2"/>
       <x:c r="G10" s="2"/>
       <x:c r="H10" s="2"/>
@@ -4108,38 +6660,38 @@
       <x:c r="A11" s="2" t="str">
         <x:v>Other Long-Term Assets</x:v>
       </x:c>
-      <x:c r="B11" s="109" t="n">
+      <x:c r="B11" s="118" t="n">
         <x:f>'1 Assumptions-Baseline'!B30</x:f>
         <x:v>9500</x:v>
       </x:c>
-      <x:c r="C11" s="106"/>
-      <x:c r="D11" s="106"/>
-      <x:c r="E11" s="106"/>
+      <x:c r="C11" s="116"/>
+      <x:c r="D11" s="116"/>
+      <x:c r="E11" s="116"/>
       <x:c r="F11" s="2"/>
       <x:c r="G11" s="2"/>
       <x:c r="H11" s="2"/>
     </x:row>
     <x:row r="12" ht="27" customHeight="1">
-      <x:c r="A12" s="119" t="str">
+      <x:c r="A12" s="128" t="str">
         <x:v>Total Assets</x:v>
       </x:c>
-      <x:c r="B12" s="116" t="n">
+      <x:c r="B12" s="125" t="n">
         <x:f>'1 Assumptions-Baseline'!B31</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="C12" s="117"/>
-      <x:c r="D12" s="117"/>
-      <x:c r="E12" s="118"/>
+      <x:c r="C12" s="126"/>
+      <x:c r="D12" s="126"/>
+      <x:c r="E12" s="127"/>
       <x:c r="F12" s="2"/>
       <x:c r="G12" s="2"/>
       <x:c r="H12" s="2"/>
     </x:row>
     <x:row r="13" ht="27" customHeight="1">
       <x:c r="A13" s="2" t="str"/>
-      <x:c r="B13" s="109"/>
-      <x:c r="C13" s="106"/>
-      <x:c r="D13" s="106"/>
-      <x:c r="E13" s="106"/>
+      <x:c r="B13" s="118"/>
+      <x:c r="C13" s="116"/>
+      <x:c r="D13" s="116"/>
+      <x:c r="E13" s="116"/>
       <x:c r="F13" s="2"/>
       <x:c r="G13" s="2"/>
       <x:c r="H13" s="2"/>
@@ -4148,13 +6700,13 @@
       <x:c r="A14" s="2" t="str">
         <x:v>Accounts Payable</x:v>
       </x:c>
-      <x:c r="B14" s="109" t="n">
+      <x:c r="B14" s="118" t="n">
         <x:f>'1 Assumptions-Baseline'!F23</x:f>
         <x:v>29400</x:v>
       </x:c>
-      <x:c r="C14" s="106"/>
-      <x:c r="D14" s="106"/>
-      <x:c r="E14" s="106"/>
+      <x:c r="C14" s="116"/>
+      <x:c r="D14" s="116"/>
+      <x:c r="E14" s="116"/>
       <x:c r="F14" s="2"/>
       <x:c r="G14" s="2"/>
       <x:c r="H14" s="2"/>
@@ -4163,13 +6715,13 @@
       <x:c r="A15" s="2" t="str">
         <x:v>Short-Term Debt</x:v>
       </x:c>
-      <x:c r="B15" s="109" t="n">
+      <x:c r="B15" s="118" t="n">
         <x:f>'1 Assumptions-Baseline'!F24</x:f>
         <x:v>45000</x:v>
       </x:c>
-      <x:c r="C15" s="106"/>
-      <x:c r="D15" s="106"/>
-      <x:c r="E15" s="106"/>
+      <x:c r="C15" s="116"/>
+      <x:c r="D15" s="116"/>
+      <x:c r="E15" s="116"/>
       <x:c r="F15" s="2"/>
       <x:c r="G15" s="2"/>
       <x:c r="H15" s="2"/>
@@ -4178,13 +6730,13 @@
       <x:c r="A16" s="2" t="str">
         <x:v>Other Current Liabilities</x:v>
       </x:c>
-      <x:c r="B16" s="109" t="n">
+      <x:c r="B16" s="118" t="n">
         <x:f>'1 Assumptions-Baseline'!F25</x:f>
         <x:v>13100</x:v>
       </x:c>
-      <x:c r="C16" s="106"/>
-      <x:c r="D16" s="106"/>
-      <x:c r="E16" s="106"/>
+      <x:c r="C16" s="116"/>
+      <x:c r="D16" s="116"/>
+      <x:c r="E16" s="116"/>
       <x:c r="F16" s="2"/>
       <x:c r="G16" s="2"/>
       <x:c r="H16" s="2"/>
@@ -4193,13 +6745,13 @@
       <x:c r="A17" s="2" t="str">
         <x:v>Total Current Liabilities</x:v>
       </x:c>
-      <x:c r="B17" s="109" t="n">
+      <x:c r="B17" s="118" t="n">
         <x:f>'1 Assumptions-Baseline'!F26</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="C17" s="106"/>
-      <x:c r="D17" s="106"/>
-      <x:c r="E17" s="106"/>
+      <x:c r="C17" s="116"/>
+      <x:c r="D17" s="116"/>
+      <x:c r="E17" s="116"/>
       <x:c r="F17" s="2"/>
       <x:c r="G17" s="2"/>
       <x:c r="H17" s="2"/>
@@ -4208,13 +6760,13 @@
       <x:c r="A18" s="2" t="str">
         <x:v>Existing Long-Term Debt</x:v>
       </x:c>
-      <x:c r="B18" s="109" t="n">
+      <x:c r="B18" s="118" t="n">
         <x:f>'1 Assumptions-Baseline'!F27</x:f>
         <x:v>110000</x:v>
       </x:c>
-      <x:c r="C18" s="106"/>
-      <x:c r="D18" s="106"/>
-      <x:c r="E18" s="106"/>
+      <x:c r="C18" s="116"/>
+      <x:c r="D18" s="116"/>
+      <x:c r="E18" s="116"/>
       <x:c r="F18" s="2"/>
       <x:c r="G18" s="2"/>
       <x:c r="H18" s="2"/>
@@ -4223,12 +6775,12 @@
       <x:c r="A19" s="2" t="str">
         <x:v>New Bond — Carrying Value</x:v>
       </x:c>
-      <x:c r="B19" s="109" t="n">
+      <x:c r="B19" s="118" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="C19" s="106"/>
-      <x:c r="D19" s="106"/>
-      <x:c r="E19" s="106"/>
+      <x:c r="C19" s="116"/>
+      <x:c r="D19" s="116"/>
+      <x:c r="E19" s="116"/>
       <x:c r="F19" s="2"/>
       <x:c r="G19" s="2"/>
       <x:c r="H19" s="2"/>
@@ -4237,13 +6789,13 @@
       <x:c r="A20" s="2" t="str">
         <x:v>Deferred Tax Liability</x:v>
       </x:c>
-      <x:c r="B20" s="109" t="n">
+      <x:c r="B20" s="118" t="n">
         <x:f>'1 Assumptions-Baseline'!F28</x:f>
         <x:v>7200</x:v>
       </x:c>
-      <x:c r="C20" s="106"/>
-      <x:c r="D20" s="106"/>
-      <x:c r="E20" s="106"/>
+      <x:c r="C20" s="116"/>
+      <x:c r="D20" s="116"/>
+      <x:c r="E20" s="116"/>
       <x:c r="F20" s="2"/>
       <x:c r="G20" s="2"/>
       <x:c r="H20" s="2"/>
@@ -4252,28 +6804,28 @@
       <x:c r="A21" s="2" t="str">
         <x:v>Other Long-Term Operating Liabilities</x:v>
       </x:c>
-      <x:c r="B21" s="109" t="n">
+      <x:c r="B21" s="118" t="n">
         <x:f>'1 Assumptions-Baseline'!F29</x:f>
         <x:v>61000</x:v>
       </x:c>
-      <x:c r="C21" s="106"/>
-      <x:c r="D21" s="106"/>
-      <x:c r="E21" s="106"/>
+      <x:c r="C21" s="116"/>
+      <x:c r="D21" s="116"/>
+      <x:c r="E21" s="116"/>
       <x:c r="F21" s="2"/>
       <x:c r="G21" s="2"/>
       <x:c r="H21" s="2"/>
     </x:row>
     <x:row r="22" ht="27" customHeight="1">
-      <x:c r="A22" s="119" t="str">
+      <x:c r="A22" s="128" t="str">
         <x:v>Total Liabilities</x:v>
       </x:c>
-      <x:c r="B22" s="116" t="n">
+      <x:c r="B22" s="125" t="n">
         <x:f>'1 Assumptions-Baseline'!F30</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="C22" s="117"/>
-      <x:c r="D22" s="117"/>
-      <x:c r="E22" s="118"/>
+      <x:c r="C22" s="126"/>
+      <x:c r="D22" s="126"/>
+      <x:c r="E22" s="127"/>
       <x:c r="F22" s="2"/>
       <x:c r="G22" s="2"/>
       <x:c r="H22" s="2"/>
@@ -4282,13 +6834,13 @@
       <x:c r="A23" s="2" t="str">
         <x:v>Common Stock &amp; APIC</x:v>
       </x:c>
-      <x:c r="B23" s="109" t="n">
+      <x:c r="B23" s="118" t="n">
         <x:f>'1 Assumptions-Baseline'!F31</x:f>
         <x:v>85000</x:v>
       </x:c>
-      <x:c r="C23" s="106"/>
-      <x:c r="D23" s="106"/>
-      <x:c r="E23" s="106"/>
+      <x:c r="C23" s="116"/>
+      <x:c r="D23" s="116"/>
+      <x:c r="E23" s="116"/>
       <x:c r="F23" s="2"/>
       <x:c r="G23" s="2"/>
       <x:c r="H23" s="2"/>
@@ -4297,55 +6849,55 @@
       <x:c r="A24" s="2" t="str">
         <x:v>Retained Earnings</x:v>
       </x:c>
-      <x:c r="B24" s="109" t="n">
+      <x:c r="B24" s="118" t="n">
         <x:f>'1 Assumptions-Baseline'!F32</x:f>
         <x:v>135800</x:v>
       </x:c>
-      <x:c r="C24" s="106"/>
-      <x:c r="D24" s="106"/>
-      <x:c r="E24" s="106"/>
+      <x:c r="C24" s="116"/>
+      <x:c r="D24" s="116"/>
+      <x:c r="E24" s="116"/>
       <x:c r="F24" s="2"/>
       <x:c r="G24" s="2"/>
       <x:c r="H24" s="2"/>
     </x:row>
     <x:row r="25" ht="27" customHeight="1">
-      <x:c r="A25" s="119" t="str">
+      <x:c r="A25" s="128" t="str">
         <x:v>Total Equity at Closing</x:v>
       </x:c>
-      <x:c r="B25" s="116" t="n">
+      <x:c r="B25" s="125" t="n">
         <x:f>'1 Assumptions-Baseline'!F33</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="C25" s="117"/>
-      <x:c r="D25" s="117"/>
-      <x:c r="E25" s="118"/>
+      <x:c r="C25" s="126"/>
+      <x:c r="D25" s="126"/>
+      <x:c r="E25" s="127"/>
       <x:c r="F25" s="2"/>
       <x:c r="G25" s="2"/>
       <x:c r="H25" s="2"/>
     </x:row>
     <x:row r="26" ht="27" customHeight="1">
-      <x:c r="A26" s="119" t="str">
+      <x:c r="A26" s="128" t="str">
         <x:v>Total Liabilities &amp; Equity</x:v>
       </x:c>
-      <x:c r="B26" s="116" t="n">
+      <x:c r="B26" s="125" t="n">
         <x:f>'1 Assumptions-Baseline'!F34</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="C26" s="117"/>
-      <x:c r="D26" s="117"/>
-      <x:c r="E26" s="118"/>
+      <x:c r="C26" s="126"/>
+      <x:c r="D26" s="126"/>
+      <x:c r="E26" s="127"/>
       <x:c r="F26" s="2"/>
       <x:c r="G26" s="2"/>
       <x:c r="H26" s="2"/>
     </x:row>
     <x:row r="27" ht="27" customHeight="1">
-      <x:c r="A27" s="119" t="str">
+      <x:c r="A27" s="128" t="str">
         <x:v>Balance Sheet Check</x:v>
       </x:c>
-      <x:c r="B27" s="119"/>
-      <x:c r="C27" s="117"/>
-      <x:c r="D27" s="117"/>
-      <x:c r="E27" s="118"/>
+      <x:c r="B27" s="128"/>
+      <x:c r="C27" s="126"/>
+      <x:c r="D27" s="126"/>
+      <x:c r="E27" s="127"/>
       <x:c r="F27" s="2"/>
       <x:c r="G27" s="2"/>
       <x:c r="H27" s="2"/>
@@ -4396,13 +6948,13 @@
       <x:c r="A31" s="2" t="str">
         <x:v>Revenue</x:v>
       </x:c>
-      <x:c r="B31" s="109" t="n">
+      <x:c r="B31" s="118" t="n">
         <x:f>'1 Assumptions-Baseline'!B7</x:f>
         <x:v>425000</x:v>
       </x:c>
-      <x:c r="C31" s="106"/>
-      <x:c r="D31" s="106"/>
-      <x:c r="E31" s="106"/>
+      <x:c r="C31" s="116"/>
+      <x:c r="D31" s="116"/>
+      <x:c r="E31" s="116"/>
       <x:c r="F31" s="2"/>
       <x:c r="G31" s="2"/>
       <x:c r="H31" s="2"/>
@@ -4411,13 +6963,13 @@
       <x:c r="A32" s="2" t="str">
         <x:v>EBIT</x:v>
       </x:c>
-      <x:c r="B32" s="109" t="n">
+      <x:c r="B32" s="118" t="n">
         <x:f>'1 Assumptions-Baseline'!B12</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="C32" s="106"/>
-      <x:c r="D32" s="106"/>
-      <x:c r="E32" s="106"/>
+      <x:c r="C32" s="116"/>
+      <x:c r="D32" s="116"/>
+      <x:c r="E32" s="116"/>
       <x:c r="F32" s="2"/>
       <x:c r="G32" s="2"/>
       <x:c r="H32" s="2"/>
@@ -4426,27 +6978,27 @@
       <x:c r="A33" s="2" t="str">
         <x:v>D&amp;A</x:v>
       </x:c>
-      <x:c r="B33" s="109" t="n">
+      <x:c r="B33" s="118" t="n">
         <x:f>'1 Assumptions-Baseline'!B11</x:f>
         <x:v>18500</x:v>
       </x:c>
-      <x:c r="C33" s="106"/>
-      <x:c r="D33" s="106"/>
-      <x:c r="E33" s="106"/>
+      <x:c r="C33" s="116"/>
+      <x:c r="D33" s="116"/>
+      <x:c r="E33" s="116"/>
       <x:c r="F33" s="2"/>
       <x:c r="G33" s="2"/>
       <x:c r="H33" s="2"/>
     </x:row>
     <x:row r="34" ht="27" customHeight="1">
-      <x:c r="A34" s="119" t="str">
+      <x:c r="A34" s="128" t="str">
         <x:v>EBITDA</x:v>
       </x:c>
-      <x:c r="B34" s="116" t="str">
+      <x:c r="B34" s="125" t="str">
         <x:f>IF(ISBLANK('1 Assumptions-Baseline'!B12),"",'1 Assumptions-Baseline'!B12+'1 Assumptions-Baseline'!B11)</x:f>
       </x:c>
-      <x:c r="C34" s="117"/>
-      <x:c r="D34" s="117"/>
-      <x:c r="E34" s="118"/>
+      <x:c r="C34" s="126"/>
+      <x:c r="D34" s="126"/>
+      <x:c r="E34" s="127"/>
       <x:c r="F34" s="2"/>
       <x:c r="G34" s="2"/>
       <x:c r="H34" s="2"/>
@@ -4455,13 +7007,13 @@
       <x:c r="A35" s="2" t="str">
         <x:v>Short-Term Debt Interest Expense</x:v>
       </x:c>
-      <x:c r="B35" s="109" t="n">
+      <x:c r="B35" s="118" t="n">
         <x:f>'1 Assumptions-Baseline'!F24*'1 Assumptions-Baseline'!B48</x:f>
         <x:v>3825.0000000000005</x:v>
       </x:c>
-      <x:c r="C35" s="106"/>
-      <x:c r="D35" s="106"/>
-      <x:c r="E35" s="106"/>
+      <x:c r="C35" s="116"/>
+      <x:c r="D35" s="116"/>
+      <x:c r="E35" s="116"/>
       <x:c r="F35" s="2"/>
       <x:c r="G35" s="2"/>
       <x:c r="H35" s="2"/>
@@ -4470,12 +7022,12 @@
       <x:c r="A36" s="2" t="str">
         <x:v>Existing LT Debt Interest Expense</x:v>
       </x:c>
-      <x:c r="B36" s="109" t="str">
+      <x:c r="B36" s="118" t="str">
         <x:f>IF(ISBLANK('1 Assumptions-Baseline'!B49),"",'1 Assumptions-Baseline'!F27*'1 Assumptions-Baseline'!B49)</x:f>
       </x:c>
-      <x:c r="C36" s="106"/>
-      <x:c r="D36" s="106"/>
-      <x:c r="E36" s="106"/>
+      <x:c r="C36" s="116"/>
+      <x:c r="D36" s="116"/>
+      <x:c r="E36" s="116"/>
       <x:c r="F36" s="2"/>
       <x:c r="G36" s="2"/>
       <x:c r="H36" s="2"/>
@@ -4484,26 +7036,26 @@
       <x:c r="A37" s="2" t="str">
         <x:v>New Bond Year-1 Interest Expense</x:v>
       </x:c>
-      <x:c r="B37" s="109" t="n">
+      <x:c r="B37" s="118" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="C37" s="106"/>
-      <x:c r="D37" s="106"/>
-      <x:c r="E37" s="106"/>
+      <x:c r="C37" s="116"/>
+      <x:c r="D37" s="116"/>
+      <x:c r="E37" s="116"/>
       <x:c r="F37" s="2"/>
       <x:c r="G37" s="2"/>
       <x:c r="H37" s="2"/>
     </x:row>
     <x:row r="38" ht="27" customHeight="1">
-      <x:c r="A38" s="119" t="str">
+      <x:c r="A38" s="128" t="str">
         <x:v>Total Interest Expense</x:v>
       </x:c>
-      <x:c r="B38" s="116" t="str">
+      <x:c r="B38" s="125" t="str">
         <x:f>IF(COUNT(B35:B37)&lt;3,"",SUM(B35:B37))</x:f>
       </x:c>
-      <x:c r="C38" s="117"/>
-      <x:c r="D38" s="117"/>
-      <x:c r="E38" s="118"/>
+      <x:c r="C38" s="126"/>
+      <x:c r="D38" s="126"/>
+      <x:c r="E38" s="127"/>
       <x:c r="F38" s="2"/>
       <x:c r="G38" s="2"/>
       <x:c r="H38" s="2"/>
@@ -4512,13 +7064,13 @@
       <x:c r="A39" s="2" t="str">
         <x:v>EBT</x:v>
       </x:c>
-      <x:c r="B39" s="109" t="n">
+      <x:c r="B39" s="118" t="n">
         <x:f>'1 Assumptions-Baseline'!B14</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="C39" s="106"/>
-      <x:c r="D39" s="106"/>
-      <x:c r="E39" s="106"/>
+      <x:c r="C39" s="116"/>
+      <x:c r="D39" s="116"/>
+      <x:c r="E39" s="116"/>
       <x:c r="F39" s="2"/>
       <x:c r="G39" s="2"/>
       <x:c r="H39" s="2"/>
@@ -4527,28 +7079,28 @@
       <x:c r="A40" s="2" t="str">
         <x:v>Income Tax Expense</x:v>
       </x:c>
-      <x:c r="B40" s="109" t="n">
+      <x:c r="B40" s="118" t="n">
         <x:f>'1 Assumptions-Baseline'!B16</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="C40" s="106"/>
-      <x:c r="D40" s="106"/>
-      <x:c r="E40" s="106"/>
+      <x:c r="C40" s="116"/>
+      <x:c r="D40" s="116"/>
+      <x:c r="E40" s="116"/>
       <x:c r="F40" s="2"/>
       <x:c r="G40" s="2"/>
       <x:c r="H40" s="2"/>
     </x:row>
     <x:row r="41" ht="27" customHeight="1">
-      <x:c r="A41" s="119" t="str">
+      <x:c r="A41" s="128" t="str">
         <x:v>Net Income</x:v>
       </x:c>
-      <x:c r="B41" s="116" t="n">
+      <x:c r="B41" s="125" t="n">
         <x:f>'1 Assumptions-Baseline'!B17</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="C41" s="117"/>
-      <x:c r="D41" s="117"/>
-      <x:c r="E41" s="118"/>
+      <x:c r="C41" s="126"/>
+      <x:c r="D41" s="126"/>
+      <x:c r="E41" s="127"/>
       <x:c r="F41" s="2"/>
       <x:c r="G41" s="2"/>
       <x:c r="H41" s="2"/>
@@ -4557,28 +7109,28 @@
       <x:c r="A42" s="2" t="str">
         <x:v>Diluted Shares Outstanding (000s)</x:v>
       </x:c>
-      <x:c r="B42" s="109" t="n">
+      <x:c r="B42" s="118" t="n">
         <x:f>'1 Assumptions-Baseline'!B18</x:f>
         <x:v>50000</x:v>
       </x:c>
-      <x:c r="C42" s="77"/>
-      <x:c r="D42" s="77"/>
-      <x:c r="E42" s="77"/>
+      <x:c r="C42" s="91"/>
+      <x:c r="D42" s="91"/>
+      <x:c r="E42" s="91"/>
       <x:c r="F42" s="2"/>
       <x:c r="G42" s="2"/>
       <x:c r="H42" s="2"/>
     </x:row>
     <x:row r="43" ht="27" customHeight="1">
-      <x:c r="A43" s="127" t="str">
+      <x:c r="A43" s="136" t="str">
         <x:v>EPS</x:v>
       </x:c>
-      <x:c r="B43" s="124" t="n">
+      <x:c r="B43" s="133" t="n">
         <x:f>'1 Assumptions-Baseline'!B19</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="C43" s="125"/>
-      <x:c r="D43" s="125"/>
-      <x:c r="E43" s="126"/>
+      <x:c r="C43" s="134"/>
+      <x:c r="D43" s="134"/>
+      <x:c r="E43" s="135"/>
       <x:c r="F43" s="2"/>
       <x:c r="G43" s="2"/>
       <x:c r="H43" s="2"/>
@@ -4643,14 +7195,14 @@
       <x:c r="A48" s="2" t="str">
         <x:v>Gross Face Debt ($000s)</x:v>
       </x:c>
-      <x:c r="B48" s="106"/>
-      <x:c r="C48" s="106"/>
-      <x:c r="D48" s="106"/>
-      <x:c r="E48" s="106"/>
-      <x:c r="F48" s="108" t="str">
+      <x:c r="B48" s="116"/>
+      <x:c r="C48" s="116"/>
+      <x:c r="D48" s="116"/>
+      <x:c r="E48" s="116"/>
+      <x:c r="F48" s="117" t="str">
         <x:v>n/a</x:v>
       </x:c>
-      <x:c r="G48" s="108" t="str">
+      <x:c r="G48" s="117" t="str">
         <x:v>Uses promised debt, not carrying value</x:v>
       </x:c>
       <x:c r="H48" s="2"/>
@@ -4659,14 +7211,14 @@
       <x:c r="A49" s="2" t="str">
         <x:v>Debt / Equity</x:v>
       </x:c>
-      <x:c r="B49" s="130"/>
-      <x:c r="C49" s="130"/>
-      <x:c r="D49" s="130"/>
-      <x:c r="E49" s="130"/>
-      <x:c r="F49" s="108" t="str">
+      <x:c r="B49" s="139"/>
+      <x:c r="C49" s="139"/>
+      <x:c r="D49" s="139"/>
+      <x:c r="E49" s="139"/>
+      <x:c r="F49" s="117" t="str">
         <x:v>≤ 1.50x</x:v>
       </x:c>
-      <x:c r="G49" s="108" t="str">
+      <x:c r="G49" s="117" t="str">
         <x:v>Lower is stronger</x:v>
       </x:c>
       <x:c r="H49" s="2"/>
@@ -4675,14 +7227,14 @@
       <x:c r="A50" s="2" t="str">
         <x:v>Debt / EBITDA</x:v>
       </x:c>
-      <x:c r="B50" s="130"/>
-      <x:c r="C50" s="130"/>
-      <x:c r="D50" s="130"/>
-      <x:c r="E50" s="130"/>
-      <x:c r="F50" s="108" t="str">
+      <x:c r="B50" s="139"/>
+      <x:c r="C50" s="139"/>
+      <x:c r="D50" s="139"/>
+      <x:c r="E50" s="139"/>
+      <x:c r="F50" s="117" t="str">
         <x:v>≤ 3.00x</x:v>
       </x:c>
-      <x:c r="G50" s="108" t="str">
+      <x:c r="G50" s="117" t="str">
         <x:v>Primary capacity constraint</x:v>
       </x:c>
       <x:c r="H50" s="2"/>
@@ -4691,14 +7243,14 @@
       <x:c r="A51" s="2" t="str">
         <x:v>Interest Coverage</x:v>
       </x:c>
-      <x:c r="B51" s="130"/>
-      <x:c r="C51" s="130"/>
-      <x:c r="D51" s="130"/>
-      <x:c r="E51" s="130"/>
-      <x:c r="F51" s="108" t="str">
+      <x:c r="B51" s="139"/>
+      <x:c r="C51" s="139"/>
+      <x:c r="D51" s="139"/>
+      <x:c r="E51" s="139"/>
+      <x:c r="F51" s="117" t="str">
         <x:v>≥ 3.00x</x:v>
       </x:c>
-      <x:c r="G51" s="108" t="str">
+      <x:c r="G51" s="117" t="str">
         <x:v>EBIT ÷ positive interest expense</x:v>
       </x:c>
       <x:c r="H51" s="2"/>
@@ -4707,14 +7259,14 @@
       <x:c r="A52" s="2" t="str">
         <x:v>Net Debt / EBITDA</x:v>
       </x:c>
-      <x:c r="B52" s="130"/>
-      <x:c r="C52" s="130"/>
-      <x:c r="D52" s="130"/>
-      <x:c r="E52" s="130"/>
-      <x:c r="F52" s="108" t="str">
+      <x:c r="B52" s="139"/>
+      <x:c r="C52" s="139"/>
+      <x:c r="D52" s="139"/>
+      <x:c r="E52" s="139"/>
+      <x:c r="F52" s="117" t="str">
         <x:v>≤ 2.50x</x:v>
       </x:c>
-      <x:c r="G52" s="108" t="str">
+      <x:c r="G52" s="117" t="str">
         <x:v>Cash retained reduces net debt</x:v>
       </x:c>
       <x:c r="H52" s="2"/>
@@ -4723,14 +7275,14 @@
       <x:c r="A53" s="2" t="str">
         <x:v>Current Ratio</x:v>
       </x:c>
-      <x:c r="B53" s="130"/>
-      <x:c r="C53" s="130"/>
-      <x:c r="D53" s="130"/>
-      <x:c r="E53" s="130"/>
-      <x:c r="F53" s="108" t="str">
+      <x:c r="B53" s="139"/>
+      <x:c r="C53" s="139"/>
+      <x:c r="D53" s="139"/>
+      <x:c r="E53" s="139"/>
+      <x:c r="F53" s="117" t="str">
         <x:v>≥ 1.50x</x:v>
       </x:c>
-      <x:c r="G53" s="108" t="str">
+      <x:c r="G53" s="117" t="str">
         <x:v>Closing current assets ÷ current liabilities</x:v>
       </x:c>
       <x:c r="H53" s="2"/>
@@ -4800,7 +7352,7 @@
 </x:worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
@@ -4837,16 +7389,16 @@
       <x:c r="H2" s="2"/>
     </x:row>
     <x:row r="3">
-      <x:c r="A3" s="93" t="str">
+      <x:c r="A3" s="106" t="str">
         <x:v>First identify the strongest full-size use of proceeds. Then calculate whether the $200M face amount is supportable under the stated guardrails.</x:v>
       </x:c>
-      <x:c r="B3" s="94"/>
-      <x:c r="C3" s="94"/>
-      <x:c r="D3" s="94"/>
-      <x:c r="E3" s="94"/>
-      <x:c r="F3" s="94"/>
-      <x:c r="G3" s="94"/>
-      <x:c r="H3" s="95"/>
+      <x:c r="B3" s="107"/>
+      <x:c r="C3" s="107"/>
+      <x:c r="D3" s="107"/>
+      <x:c r="E3" s="107"/>
+      <x:c r="F3" s="107"/>
+      <x:c r="G3" s="107"/>
+      <x:c r="H3" s="108"/>
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="2"/>
@@ -4894,10 +7446,10 @@
       <x:c r="A7" s="2" t="str">
         <x:v>Debt / Equity</x:v>
       </x:c>
-      <x:c r="B7" s="130"/>
-      <x:c r="C7" s="130"/>
-      <x:c r="D7" s="130"/>
-      <x:c r="E7" s="133"/>
+      <x:c r="B7" s="139"/>
+      <x:c r="C7" s="139"/>
+      <x:c r="D7" s="139"/>
+      <x:c r="E7" s="88"/>
       <x:c r="F7" s="2"/>
       <x:c r="G7" s="2"/>
       <x:c r="H7" s="2"/>
@@ -4906,10 +7458,10 @@
       <x:c r="A8" s="2" t="str">
         <x:v>Debt / EBITDA</x:v>
       </x:c>
-      <x:c r="B8" s="130"/>
-      <x:c r="C8" s="130"/>
-      <x:c r="D8" s="130"/>
-      <x:c r="E8" s="133"/>
+      <x:c r="B8" s="139"/>
+      <x:c r="C8" s="139"/>
+      <x:c r="D8" s="139"/>
+      <x:c r="E8" s="88"/>
       <x:c r="F8" s="2"/>
       <x:c r="G8" s="2"/>
       <x:c r="H8" s="2"/>
@@ -4918,10 +7470,10 @@
       <x:c r="A9" s="2" t="str">
         <x:v>Interest Coverage</x:v>
       </x:c>
-      <x:c r="B9" s="130"/>
-      <x:c r="C9" s="130"/>
-      <x:c r="D9" s="130"/>
-      <x:c r="E9" s="133"/>
+      <x:c r="B9" s="139"/>
+      <x:c r="C9" s="139"/>
+      <x:c r="D9" s="139"/>
+      <x:c r="E9" s="88"/>
       <x:c r="F9" s="2"/>
       <x:c r="G9" s="2"/>
       <x:c r="H9" s="2"/>
@@ -4930,10 +7482,10 @@
       <x:c r="A10" s="2" t="str">
         <x:v>Net Debt / EBITDA</x:v>
       </x:c>
-      <x:c r="B10" s="130"/>
-      <x:c r="C10" s="130"/>
-      <x:c r="D10" s="130"/>
-      <x:c r="E10" s="133"/>
+      <x:c r="B10" s="139"/>
+      <x:c r="C10" s="139"/>
+      <x:c r="D10" s="139"/>
+      <x:c r="E10" s="88"/>
       <x:c r="F10" s="2"/>
       <x:c r="G10" s="2"/>
       <x:c r="H10" s="2"/>
@@ -4942,10 +7494,10 @@
       <x:c r="A11" s="2" t="str">
         <x:v>Current Ratio</x:v>
       </x:c>
-      <x:c r="B11" s="130"/>
-      <x:c r="C11" s="130"/>
-      <x:c r="D11" s="130"/>
-      <x:c r="E11" s="133"/>
+      <x:c r="B11" s="139"/>
+      <x:c r="C11" s="139"/>
+      <x:c r="D11" s="139"/>
+      <x:c r="E11" s="88"/>
       <x:c r="F11" s="2"/>
       <x:c r="G11" s="2"/>
       <x:c r="H11" s="2"/>
@@ -4954,10 +7506,10 @@
       <x:c r="A12" s="2" t="str">
         <x:v>EPS</x:v>
       </x:c>
-      <x:c r="B12" s="80"/>
-      <x:c r="C12" s="80"/>
-      <x:c r="D12" s="80"/>
-      <x:c r="E12" s="133"/>
+      <x:c r="B12" s="94"/>
+      <x:c r="C12" s="94"/>
+      <x:c r="D12" s="94"/>
+      <x:c r="E12" s="88"/>
       <x:c r="F12" s="2"/>
       <x:c r="G12" s="2"/>
       <x:c r="H12" s="2"/>
@@ -5013,10 +7565,10 @@
       <x:c r="H16" s="2"/>
     </x:row>
     <x:row r="17" ht="28" customHeight="1">
-      <x:c r="A17" s="111" t="str">
+      <x:c r="A17" s="120" t="str">
         <x:v>Scenario C EBITDA</x:v>
       </x:c>
-      <x:c r="B17" s="106"/>
+      <x:c r="B17" s="116"/>
       <x:c r="C17" s="33" t="str">
         <x:v>$000s</x:v>
       </x:c>
@@ -5029,10 +7581,10 @@
       <x:c r="H17" s="2"/>
     </x:row>
     <x:row r="18" ht="28" customHeight="1">
-      <x:c r="A18" s="111" t="str">
+      <x:c r="A18" s="120" t="str">
         <x:v>Scenario C EBIT</x:v>
       </x:c>
-      <x:c r="B18" s="106"/>
+      <x:c r="B18" s="116"/>
       <x:c r="C18" s="33" t="str">
         <x:v>$000s</x:v>
       </x:c>
@@ -5045,10 +7597,10 @@
       <x:c r="H18" s="2"/>
     </x:row>
     <x:row r="19" ht="28" customHeight="1">
-      <x:c r="A19" s="111" t="str">
+      <x:c r="A19" s="120" t="str">
         <x:v>Closing Equity</x:v>
       </x:c>
-      <x:c r="B19" s="106"/>
+      <x:c r="B19" s="116"/>
       <x:c r="C19" s="33" t="str">
         <x:v>$000s</x:v>
       </x:c>
@@ -5061,10 +7613,10 @@
       <x:c r="H19" s="2"/>
     </x:row>
     <x:row r="20" ht="28" customHeight="1">
-      <x:c r="A20" s="111" t="str">
+      <x:c r="A20" s="120" t="str">
         <x:v>Remaining Pre-Existing Face Debt after Refi</x:v>
       </x:c>
-      <x:c r="B20" s="106"/>
+      <x:c r="B20" s="116"/>
       <x:c r="C20" s="33" t="str">
         <x:v>$000s</x:v>
       </x:c>
@@ -5077,8 +7629,8 @@
       <x:c r="H20" s="2"/>
     </x:row>
     <x:row r="21" ht="28" customHeight="1">
-      <x:c r="A21" s="111" t="str"/>
-      <x:c r="B21" s="106"/>
+      <x:c r="A21" s="120" t="str"/>
+      <x:c r="B21" s="116"/>
       <x:c r="C21" s="33" t="str"/>
       <x:c r="D21" s="33" t="str"/>
       <x:c r="E21" s="2"/>
@@ -5087,10 +7639,10 @@
       <x:c r="H21" s="2"/>
     </x:row>
     <x:row r="22" ht="28" customHeight="1">
-      <x:c r="A22" s="111" t="str">
+      <x:c r="A22" s="120" t="str">
         <x:v>New Face Capacity — Debt / Equity</x:v>
       </x:c>
-      <x:c r="B22" s="106"/>
+      <x:c r="B22" s="116"/>
       <x:c r="C22" s="33" t="str">
         <x:v>$000s</x:v>
       </x:c>
@@ -5103,10 +7655,10 @@
       <x:c r="H22" s="2"/>
     </x:row>
     <x:row r="23" ht="28" customHeight="1">
-      <x:c r="A23" s="111" t="str">
+      <x:c r="A23" s="120" t="str">
         <x:v>New Face Capacity — Debt / EBITDA</x:v>
       </x:c>
-      <x:c r="B23" s="106"/>
+      <x:c r="B23" s="116"/>
       <x:c r="C23" s="33" t="str">
         <x:v>$000s</x:v>
       </x:c>
@@ -5119,10 +7671,10 @@
       <x:c r="H23" s="2"/>
     </x:row>
     <x:row r="24" ht="28" customHeight="1">
-      <x:c r="A24" s="111" t="str">
+      <x:c r="A24" s="120" t="str">
         <x:v>New Face Capacity — Interest Coverage</x:v>
       </x:c>
-      <x:c r="B24" s="106"/>
+      <x:c r="B24" s="116"/>
       <x:c r="C24" s="33" t="str">
         <x:v>$000s</x:v>
       </x:c>
@@ -5135,10 +7687,10 @@
       <x:c r="H24" s="2"/>
     </x:row>
     <x:row r="25" ht="28" customHeight="1">
-      <x:c r="A25" s="111" t="str">
+      <x:c r="A25" s="120" t="str">
         <x:v>Recommended Maximum New Face Amount</x:v>
       </x:c>
-      <x:c r="B25" s="106"/>
+      <x:c r="B25" s="116"/>
       <x:c r="C25" s="33" t="str">
         <x:v>$000s</x:v>
       </x:c>
@@ -5151,8 +7703,8 @@
       <x:c r="H25" s="2"/>
     </x:row>
     <x:row r="26" ht="28" customHeight="1">
-      <x:c r="A26" s="111" t="str"/>
-      <x:c r="B26" s="106"/>
+      <x:c r="A26" s="120" t="str"/>
+      <x:c r="B26" s="116"/>
       <x:c r="C26" s="33" t="str"/>
       <x:c r="D26" s="33" t="str"/>
       <x:c r="E26" s="2"/>
@@ -5161,10 +7713,10 @@
       <x:c r="H26" s="2"/>
     </x:row>
     <x:row r="27" ht="28" customHeight="1">
-      <x:c r="A27" s="111" t="str">
+      <x:c r="A27" s="120" t="str">
         <x:v>Gross Proceeds at Capacity</x:v>
       </x:c>
-      <x:c r="B27" s="106"/>
+      <x:c r="B27" s="116"/>
       <x:c r="C27" s="33" t="str">
         <x:v>$000s</x:v>
       </x:c>
@@ -5177,10 +7729,10 @@
       <x:c r="H27" s="2"/>
     </x:row>
     <x:row r="28" ht="28" customHeight="1">
-      <x:c r="A28" s="111" t="str">
+      <x:c r="A28" s="120" t="str">
         <x:v>Issuance Costs at Capacity</x:v>
       </x:c>
-      <x:c r="B28" s="106"/>
+      <x:c r="B28" s="116"/>
       <x:c r="C28" s="33" t="str">
         <x:v>$000s</x:v>
       </x:c>
@@ -5193,10 +7745,10 @@
       <x:c r="H28" s="2"/>
     </x:row>
     <x:row r="29" ht="28" customHeight="1">
-      <x:c r="A29" s="111" t="str">
+      <x:c r="A29" s="120" t="str">
         <x:v>Net Proceeds at Capacity</x:v>
       </x:c>
-      <x:c r="B29" s="106"/>
+      <x:c r="B29" s="116"/>
       <x:c r="C29" s="33" t="str">
         <x:v>$000s</x:v>
       </x:c>
@@ -5209,10 +7761,10 @@
       <x:c r="H29" s="2"/>
     </x:row>
     <x:row r="30" ht="28" customHeight="1">
-      <x:c r="A30" s="111" t="str">
+      <x:c r="A30" s="120" t="str">
         <x:v>Refinance Short-Term Debt</x:v>
       </x:c>
-      <x:c r="B30" s="106"/>
+      <x:c r="B30" s="116"/>
       <x:c r="C30" s="33" t="str">
         <x:v>$000s</x:v>
       </x:c>
@@ -5225,10 +7777,10 @@
       <x:c r="H30" s="2"/>
     </x:row>
     <x:row r="31" ht="28" customHeight="1">
-      <x:c r="A31" s="111" t="str">
+      <x:c r="A31" s="120" t="str">
         <x:v>Staged CapEx</x:v>
       </x:c>
-      <x:c r="B31" s="106"/>
+      <x:c r="B31" s="116"/>
       <x:c r="C31" s="33" t="str">
         <x:v>$000s</x:v>
       </x:c>
@@ -5241,10 +7793,10 @@
       <x:c r="H31" s="2"/>
     </x:row>
     <x:row r="32" ht="28" customHeight="1">
-      <x:c r="A32" s="111" t="str">
+      <x:c r="A32" s="120" t="str">
         <x:v>Cash Retained</x:v>
       </x:c>
-      <x:c r="B32" s="106"/>
+      <x:c r="B32" s="116"/>
       <x:c r="C32" s="33" t="str">
         <x:v>$000s</x:v>
       </x:c>
@@ -5257,10 +7809,10 @@
       <x:c r="H32" s="2"/>
     </x:row>
     <x:row r="33" ht="28" customHeight="1">
-      <x:c r="A33" s="111" t="str">
+      <x:c r="A33" s="120" t="str">
         <x:v>Total Uses</x:v>
       </x:c>
-      <x:c r="B33" s="106"/>
+      <x:c r="B33" s="116"/>
       <x:c r="C33" s="33" t="str">
         <x:v>$000s</x:v>
       </x:c>
@@ -5273,10 +7825,10 @@
       <x:c r="H33" s="2"/>
     </x:row>
     <x:row r="34" ht="28" customHeight="1">
-      <x:c r="A34" s="111" t="str">
+      <x:c r="A34" s="120" t="str">
         <x:v>Capacity Sources − Uses Check</x:v>
       </x:c>
-      <x:c r="B34" s="106"/>
+      <x:c r="B34" s="116"/>
       <x:c r="C34" s="33" t="str">
         <x:v>$000s</x:v>
       </x:c>
@@ -5289,10 +7841,10 @@
       <x:c r="H34" s="2"/>
     </x:row>
     <x:row r="35" ht="28" customHeight="1">
-      <x:c r="A35" s="111" t="str">
+      <x:c r="A35" s="120" t="str">
         <x:v>Debt / EBITDA at Capacity</x:v>
       </x:c>
-      <x:c r="B35" s="130"/>
+      <x:c r="B35" s="139"/>
       <x:c r="C35" s="33" t="str">
         <x:v>x</x:v>
       </x:c>
@@ -5337,36 +7889,36 @@
       <x:c r="H38" s="27"/>
     </x:row>
     <x:row r="39" ht="26" customHeight="1">
-      <x:c r="A39" s="137" t="str">
+      <x:c r="A39" s="143" t="str">
         <x:v>Recommendation: Choose the best full-size comparison, state whether the issue should be resized, and name the staged uses.</x:v>
       </x:c>
-      <x:c r="B39" s="138"/>
-      <x:c r="C39" s="138"/>
-      <x:c r="D39" s="138"/>
-      <x:c r="E39" s="138"/>
-      <x:c r="F39" s="138"/>
-      <x:c r="G39" s="138"/>
-      <x:c r="H39" s="139"/>
+      <x:c r="B39" s="144"/>
+      <x:c r="C39" s="144"/>
+      <x:c r="D39" s="144"/>
+      <x:c r="E39" s="144"/>
+      <x:c r="F39" s="144"/>
+      <x:c r="G39" s="144"/>
+      <x:c r="H39" s="145"/>
     </x:row>
     <x:row r="40" ht="28" customHeight="1">
-      <x:c r="A40" s="133"/>
-      <x:c r="B40" s="133"/>
-      <x:c r="C40" s="133"/>
-      <x:c r="D40" s="133"/>
-      <x:c r="E40" s="133"/>
-      <x:c r="F40" s="133"/>
-      <x:c r="G40" s="133"/>
-      <x:c r="H40" s="133"/>
+      <x:c r="A40" s="88"/>
+      <x:c r="B40" s="88"/>
+      <x:c r="C40" s="88"/>
+      <x:c r="D40" s="88"/>
+      <x:c r="E40" s="88"/>
+      <x:c r="F40" s="88"/>
+      <x:c r="G40" s="88"/>
+      <x:c r="H40" s="88"/>
     </x:row>
     <x:row r="41" ht="28" customHeight="1">
-      <x:c r="A41" s="133"/>
-      <x:c r="B41" s="133"/>
-      <x:c r="C41" s="133"/>
-      <x:c r="D41" s="133"/>
-      <x:c r="E41" s="133"/>
-      <x:c r="F41" s="133"/>
-      <x:c r="G41" s="133"/>
-      <x:c r="H41" s="133"/>
+      <x:c r="A41" s="88"/>
+      <x:c r="B41" s="88"/>
+      <x:c r="C41" s="88"/>
+      <x:c r="D41" s="88"/>
+      <x:c r="E41" s="88"/>
+      <x:c r="F41" s="88"/>
+      <x:c r="G41" s="88"/>
+      <x:c r="H41" s="88"/>
     </x:row>
     <x:row r="42">
       <x:c r="A42" s="2"/>
@@ -5379,36 +7931,36 @@
       <x:c r="H42" s="2"/>
     </x:row>
     <x:row r="43" ht="26" customHeight="1">
-      <x:c r="A43" s="137" t="str">
+      <x:c r="A43" s="143" t="str">
         <x:v>Evidence: Cite bond price / proceeds, two ratios, the capacity amount, and one tie-out.</x:v>
       </x:c>
-      <x:c r="B43" s="138"/>
-      <x:c r="C43" s="138"/>
-      <x:c r="D43" s="138"/>
-      <x:c r="E43" s="138"/>
-      <x:c r="F43" s="138"/>
-      <x:c r="G43" s="138"/>
-      <x:c r="H43" s="139"/>
+      <x:c r="B43" s="144"/>
+      <x:c r="C43" s="144"/>
+      <x:c r="D43" s="144"/>
+      <x:c r="E43" s="144"/>
+      <x:c r="F43" s="144"/>
+      <x:c r="G43" s="144"/>
+      <x:c r="H43" s="145"/>
     </x:row>
     <x:row r="44" ht="28" customHeight="1">
-      <x:c r="A44" s="133"/>
-      <x:c r="B44" s="133"/>
-      <x:c r="C44" s="133"/>
-      <x:c r="D44" s="133"/>
-      <x:c r="E44" s="133"/>
-      <x:c r="F44" s="133"/>
-      <x:c r="G44" s="133"/>
-      <x:c r="H44" s="133"/>
+      <x:c r="A44" s="88"/>
+      <x:c r="B44" s="88"/>
+      <x:c r="C44" s="88"/>
+      <x:c r="D44" s="88"/>
+      <x:c r="E44" s="88"/>
+      <x:c r="F44" s="88"/>
+      <x:c r="G44" s="88"/>
+      <x:c r="H44" s="88"/>
     </x:row>
     <x:row r="45" ht="28" customHeight="1">
-      <x:c r="A45" s="133"/>
-      <x:c r="B45" s="133"/>
-      <x:c r="C45" s="133"/>
-      <x:c r="D45" s="133"/>
-      <x:c r="E45" s="133"/>
-      <x:c r="F45" s="133"/>
-      <x:c r="G45" s="133"/>
-      <x:c r="H45" s="133"/>
+      <x:c r="A45" s="88"/>
+      <x:c r="B45" s="88"/>
+      <x:c r="C45" s="88"/>
+      <x:c r="D45" s="88"/>
+      <x:c r="E45" s="88"/>
+      <x:c r="F45" s="88"/>
+      <x:c r="G45" s="88"/>
+      <x:c r="H45" s="88"/>
     </x:row>
     <x:row r="46">
       <x:c r="A46" s="2"/>
@@ -5421,36 +7973,36 @@
       <x:c r="H46" s="2"/>
     </x:row>
     <x:row r="47" ht="26" customHeight="1">
-      <x:c r="A47" s="137" t="str">
+      <x:c r="A47" s="143" t="str">
         <x:v>Accounting rationale: Explain face debt versus carrying value and why interest expense lowers EBT and net income.</x:v>
       </x:c>
-      <x:c r="B47" s="138"/>
-      <x:c r="C47" s="138"/>
-      <x:c r="D47" s="138"/>
-      <x:c r="E47" s="138"/>
-      <x:c r="F47" s="138"/>
-      <x:c r="G47" s="138"/>
-      <x:c r="H47" s="139"/>
+      <x:c r="B47" s="144"/>
+      <x:c r="C47" s="144"/>
+      <x:c r="D47" s="144"/>
+      <x:c r="E47" s="144"/>
+      <x:c r="F47" s="144"/>
+      <x:c r="G47" s="144"/>
+      <x:c r="H47" s="145"/>
     </x:row>
     <x:row r="48" ht="28" customHeight="1">
-      <x:c r="A48" s="133"/>
-      <x:c r="B48" s="133"/>
-      <x:c r="C48" s="133"/>
-      <x:c r="D48" s="133"/>
-      <x:c r="E48" s="133"/>
-      <x:c r="F48" s="133"/>
-      <x:c r="G48" s="133"/>
-      <x:c r="H48" s="133"/>
+      <x:c r="A48" s="88"/>
+      <x:c r="B48" s="88"/>
+      <x:c r="C48" s="88"/>
+      <x:c r="D48" s="88"/>
+      <x:c r="E48" s="88"/>
+      <x:c r="F48" s="88"/>
+      <x:c r="G48" s="88"/>
+      <x:c r="H48" s="88"/>
     </x:row>
     <x:row r="49" ht="28" customHeight="1">
-      <x:c r="A49" s="133"/>
-      <x:c r="B49" s="133"/>
-      <x:c r="C49" s="133"/>
-      <x:c r="D49" s="133"/>
-      <x:c r="E49" s="133"/>
-      <x:c r="F49" s="133"/>
-      <x:c r="G49" s="133"/>
-      <x:c r="H49" s="133"/>
+      <x:c r="A49" s="88"/>
+      <x:c r="B49" s="88"/>
+      <x:c r="C49" s="88"/>
+      <x:c r="D49" s="88"/>
+      <x:c r="E49" s="88"/>
+      <x:c r="F49" s="88"/>
+      <x:c r="G49" s="88"/>
+      <x:c r="H49" s="88"/>
     </x:row>
     <x:row r="50">
       <x:c r="A50" s="2"/>
@@ -5463,36 +8015,36 @@
       <x:c r="H50" s="2"/>
     </x:row>
     <x:row r="51" ht="26" customHeight="1">
-      <x:c r="A51" s="137" t="str">
+      <x:c r="A51" s="143" t="str">
         <x:v>Primary risk: Name the leverage, execution, or liquidity risk most likely to change the decision.</x:v>
       </x:c>
-      <x:c r="B51" s="138"/>
-      <x:c r="C51" s="138"/>
-      <x:c r="D51" s="138"/>
-      <x:c r="E51" s="138"/>
-      <x:c r="F51" s="138"/>
-      <x:c r="G51" s="138"/>
-      <x:c r="H51" s="139"/>
+      <x:c r="B51" s="144"/>
+      <x:c r="C51" s="144"/>
+      <x:c r="D51" s="144"/>
+      <x:c r="E51" s="144"/>
+      <x:c r="F51" s="144"/>
+      <x:c r="G51" s="144"/>
+      <x:c r="H51" s="145"/>
     </x:row>
     <x:row r="52" ht="28" customHeight="1">
-      <x:c r="A52" s="133"/>
-      <x:c r="B52" s="133"/>
-      <x:c r="C52" s="133"/>
-      <x:c r="D52" s="133"/>
-      <x:c r="E52" s="133"/>
-      <x:c r="F52" s="133"/>
-      <x:c r="G52" s="133"/>
-      <x:c r="H52" s="133"/>
+      <x:c r="A52" s="88"/>
+      <x:c r="B52" s="88"/>
+      <x:c r="C52" s="88"/>
+      <x:c r="D52" s="88"/>
+      <x:c r="E52" s="88"/>
+      <x:c r="F52" s="88"/>
+      <x:c r="G52" s="88"/>
+      <x:c r="H52" s="88"/>
     </x:row>
     <x:row r="53" ht="28" customHeight="1">
-      <x:c r="A53" s="133"/>
-      <x:c r="B53" s="133"/>
-      <x:c r="C53" s="133"/>
-      <x:c r="D53" s="133"/>
-      <x:c r="E53" s="133"/>
-      <x:c r="F53" s="133"/>
-      <x:c r="G53" s="133"/>
-      <x:c r="H53" s="133"/>
+      <x:c r="A53" s="88"/>
+      <x:c r="B53" s="88"/>
+      <x:c r="C53" s="88"/>
+      <x:c r="D53" s="88"/>
+      <x:c r="E53" s="88"/>
+      <x:c r="F53" s="88"/>
+      <x:c r="G53" s="88"/>
+      <x:c r="H53" s="88"/>
     </x:row>
     <x:row r="54">
       <x:c r="A54" s="2"/>
@@ -5505,36 +8057,36 @@
       <x:c r="H54" s="2"/>
     </x:row>
     <x:row r="55" ht="26" customHeight="1">
-      <x:c r="A55" s="137" t="str">
+      <x:c r="A55" s="143" t="str">
         <x:v>Monitoring trigger: State a measurable threshold and the action management should take if breached.</x:v>
       </x:c>
-      <x:c r="B55" s="138"/>
-      <x:c r="C55" s="138"/>
-      <x:c r="D55" s="138"/>
-      <x:c r="E55" s="138"/>
-      <x:c r="F55" s="138"/>
-      <x:c r="G55" s="138"/>
-      <x:c r="H55" s="139"/>
+      <x:c r="B55" s="144"/>
+      <x:c r="C55" s="144"/>
+      <x:c r="D55" s="144"/>
+      <x:c r="E55" s="144"/>
+      <x:c r="F55" s="144"/>
+      <x:c r="G55" s="144"/>
+      <x:c r="H55" s="145"/>
     </x:row>
     <x:row r="56" ht="28" customHeight="1">
-      <x:c r="A56" s="133"/>
-      <x:c r="B56" s="133"/>
-      <x:c r="C56" s="133"/>
-      <x:c r="D56" s="133"/>
-      <x:c r="E56" s="133"/>
-      <x:c r="F56" s="133"/>
-      <x:c r="G56" s="133"/>
-      <x:c r="H56" s="133"/>
+      <x:c r="A56" s="88"/>
+      <x:c r="B56" s="88"/>
+      <x:c r="C56" s="88"/>
+      <x:c r="D56" s="88"/>
+      <x:c r="E56" s="88"/>
+      <x:c r="F56" s="88"/>
+      <x:c r="G56" s="88"/>
+      <x:c r="H56" s="88"/>
     </x:row>
     <x:row r="57" ht="28" customHeight="1">
-      <x:c r="A57" s="133"/>
-      <x:c r="B57" s="133"/>
-      <x:c r="C57" s="133"/>
-      <x:c r="D57" s="133"/>
-      <x:c r="E57" s="133"/>
-      <x:c r="F57" s="133"/>
-      <x:c r="G57" s="133"/>
-      <x:c r="H57" s="133"/>
+      <x:c r="A57" s="88"/>
+      <x:c r="B57" s="88"/>
+      <x:c r="C57" s="88"/>
+      <x:c r="D57" s="88"/>
+      <x:c r="E57" s="88"/>
+      <x:c r="F57" s="88"/>
+      <x:c r="G57" s="88"/>
+      <x:c r="H57" s="88"/>
     </x:row>
     <x:row r="58">
       <x:c r="A58" s="2"/>
@@ -5606,1256 +8158,4 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:sheetFormatPr defaultRowHeight="15"/>
-  <x:cols>
-    <x:col min="1" max="1" width="38" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="19" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="19" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="19" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="14" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="16" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="45" hidden="0" customWidth="1"/>
-  </x:cols>
-  <x:sheetData>
-    <x:row r="1" ht="30" customHeight="1">
-      <x:c r="A1" s="5" t="str">
-        <x:v>Meridian — Model Checks and Scenario Tie-Outs</x:v>
-      </x:c>
-      <x:c r="B1" s="5"/>
-      <x:c r="C1" s="5"/>
-      <x:c r="D1" s="5"/>
-      <x:c r="E1" s="5"/>
-      <x:c r="F1" s="5"/>
-      <x:c r="G1" s="5"/>
-    </x:row>
-    <x:row r="2">
-      <x:c r="A2" s="2"/>
-      <x:c r="B2" s="2"/>
-      <x:c r="C2" s="2"/>
-      <x:c r="D2" s="2"/>
-      <x:c r="E2" s="2"/>
-      <x:c r="F2" s="2"/>
-      <x:c r="G2" s="2"/>
-    </x:row>
-    <x:row r="3">
-      <x:c r="A3" s="143" t="str">
-        <x:v>MODEL STATUS</x:v>
-      </x:c>
-      <x:c r="B3" s="143" t="str">
-        <x:f>IF(COUNTIF(F7:F39,"CHECK")&gt;0,"FAIL",IF(COUNTIF(F7:F39,"COMPLETE")&gt;0,"COMPLETE MODEL","PASS"))</x:f>
-        <x:v>COMPLETE MODEL</x:v>
-      </x:c>
-      <x:c r="C3" s="143"/>
-      <x:c r="D3" s="143"/>
-      <x:c r="E3" s="2"/>
-      <x:c r="F3" s="2"/>
-      <x:c r="G3" s="2"/>
-    </x:row>
-    <x:row r="4">
-      <x:c r="A4" s="2"/>
-      <x:c r="B4" s="2"/>
-      <x:c r="C4" s="2"/>
-      <x:c r="D4" s="2"/>
-      <x:c r="E4" s="2"/>
-      <x:c r="F4" s="2"/>
-      <x:c r="G4" s="2"/>
-    </x:row>
-    <x:row r="5" ht="22" customHeight="1">
-      <x:c r="A5" s="27" t="str">
-        <x:v>One assertion per row — do not proceed while a completed row says CHECK</x:v>
-      </x:c>
-      <x:c r="B5" s="27"/>
-      <x:c r="C5" s="27"/>
-      <x:c r="D5" s="27"/>
-      <x:c r="E5" s="27"/>
-      <x:c r="F5" s="27"/>
-      <x:c r="G5" s="27"/>
-    </x:row>
-    <x:row r="6" ht="27" customHeight="1">
-      <x:c r="A6" s="38" t="str">
-        <x:v>Check</x:v>
-      </x:c>
-      <x:c r="B6" s="38" t="str">
-        <x:v>Actual</x:v>
-      </x:c>
-      <x:c r="C6" s="38" t="str">
-        <x:v>Expected</x:v>
-      </x:c>
-      <x:c r="D6" s="38" t="str">
-        <x:v>Difference</x:v>
-      </x:c>
-      <x:c r="E6" s="38" t="str">
-        <x:v>Tolerance</x:v>
-      </x:c>
-      <x:c r="F6" s="38" t="str">
-        <x:v>Status</x:v>
-      </x:c>
-      <x:c r="G6" s="38" t="str">
-        <x:v>Where to fix / meaning</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7" ht="27" customHeight="1">
-      <x:c r="A7" s="2" t="str">
-        <x:v>Baseline balance sheet</x:v>
-      </x:c>
-      <x:c r="B7" s="147" t="str">
-        <x:f>IF(ISBLANK('1 Assumptions-Baseline'!B31),"",'1 Assumptions-Baseline'!B31)</x:f>
-      </x:c>
-      <x:c r="C7" s="147" t="str">
-        <x:f>IF(ISBLANK('1 Assumptions-Baseline'!F34),"",'1 Assumptions-Baseline'!F34)</x:f>
-      </x:c>
-      <x:c r="D7" s="147" t="str">
-        <x:f>IF(OR(NOT(ISNUMBER(B7)),NOT(ISNUMBER(C7))),"",B7-C7)</x:f>
-      </x:c>
-      <x:c r="E7" s="147" t="n">
-        <x:v>0.1</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="str">
-        <x:f>IF(OR(NOT(ISNUMBER(B7)),NOT(ISNUMBER(C7))),"COMPLETE",IF(ABS(D7)&lt;=E7,"OK","CHECK"))</x:f>
-        <x:v>COMPLETE</x:v>
-      </x:c>
-      <x:c r="G7" s="33" t="str">
-        <x:v>1 Assumptions-Baseline · Total Assets vs L+E</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8" ht="27" customHeight="1">
-      <x:c r="A8" s="2" t="str">
-        <x:v>Baseline tax expense sign</x:v>
-      </x:c>
-      <x:c r="B8" s="147" t="n">
-        <x:f>'1 Assumptions-Baseline'!B16</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C8" s="147" t="str">
-        <x:f>IF('1 Assumptions-Baseline'!B14="","",MAX('1 Assumptions-Baseline'!B14,0)*'1 Assumptions-Baseline'!B15)</x:f>
-      </x:c>
-      <x:c r="D8" s="147" t="str">
-        <x:f>IF(OR(NOT(ISNUMBER(B8)),NOT(ISNUMBER(C8))),"",B8-C8)</x:f>
-      </x:c>
-      <x:c r="E8" s="147" t="n">
-        <x:v>0.1</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="str">
-        <x:f>IF(OR(NOT(ISNUMBER(B8)),NOT(ISNUMBER(C8))),"COMPLETE",IF(ABS(D8)&lt;=E8,"OK","CHECK"))</x:f>
-        <x:v>COMPLETE</x:v>
-      </x:c>
-      <x:c r="G8" s="33" t="str">
-        <x:v>Tax expense must be positive</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" ht="27" customHeight="1">
-      <x:c r="A9" s="2" t="str">
-        <x:v>Baseline net income</x:v>
-      </x:c>
-      <x:c r="B9" s="147" t="n">
-        <x:f>'1 Assumptions-Baseline'!B17</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C9" s="147" t="str">
-        <x:f>IF(OR('1 Assumptions-Baseline'!B14="",'1 Assumptions-Baseline'!B16=""),"",'1 Assumptions-Baseline'!B14-'1 Assumptions-Baseline'!B16)</x:f>
-      </x:c>
-      <x:c r="D9" s="147" t="str">
-        <x:f>IF(OR(NOT(ISNUMBER(B9)),NOT(ISNUMBER(C9))),"",B9-C9)</x:f>
-      </x:c>
-      <x:c r="E9" s="147" t="n">
-        <x:v>0.1</x:v>
-      </x:c>
-      <x:c r="F9" s="32" t="str">
-        <x:f>IF(OR(NOT(ISNUMBER(B9)),NOT(ISNUMBER(C9))),"COMPLETE",IF(ABS(D9)&lt;=E9,"OK","CHECK"))</x:f>
-        <x:v>COMPLETE</x:v>
-      </x:c>
-      <x:c r="G9" s="33" t="str">
-        <x:v>EBT − tax expense</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" ht="27" customHeight="1">
-      <x:c r="A10" s="2" t="str">
-        <x:v>Baseline EPS</x:v>
-      </x:c>
-      <x:c r="B10" s="147" t="n">
-        <x:f>'1 Assumptions-Baseline'!B19</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C10" s="147" t="str">
-        <x:f>IF(OR('1 Assumptions-Baseline'!B17="",'1 Assumptions-Baseline'!B18=""),"",'1 Assumptions-Baseline'!B17/'1 Assumptions-Baseline'!B18)</x:f>
-      </x:c>
-      <x:c r="D10" s="147" t="str">
-        <x:f>IF(OR(NOT(ISNUMBER(B10)),NOT(ISNUMBER(C10))),"",B10-C10)</x:f>
-      </x:c>
-      <x:c r="E10" s="147" t="n">
-        <x:v>0.0001</x:v>
-      </x:c>
-      <x:c r="F10" s="32" t="str">
-        <x:f>IF(OR(NOT(ISNUMBER(B10)),NOT(ISNUMBER(C10))),"COMPLETE",IF(ABS(D10)&lt;=E10,"OK","CHECK"))</x:f>
-        <x:v>COMPLETE</x:v>
-      </x:c>
-      <x:c r="G10" s="33" t="str">
-        <x:v>Net income ÷ shares</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" ht="27" customHeight="1">
-      <x:c r="A11" s="2" t="str">
-        <x:v>PV vs PRICE</x:v>
-      </x:c>
-      <x:c r="B11" s="147" t="str">
-        <x:f>IF(ISBLANK('2 Bond Pricing'!B24),"",'2 Bond Pricing'!B24)</x:f>
-      </x:c>
-      <x:c r="C11" s="147" t="n">
-        <x:f>0</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D11" s="147" t="str">
-        <x:f>IF(OR(NOT(ISNUMBER(B11)),NOT(ISNUMBER(C11))),"",B11-C11)</x:f>
-      </x:c>
-      <x:c r="E11" s="147" t="n">
-        <x:v>0.01</x:v>
-      </x:c>
-      <x:c r="F11" s="32" t="str">
-        <x:f>IF(OR(NOT(ISNUMBER(B11)),NOT(ISNUMBER(C11))),"COMPLETE",IF(ABS(D11)&lt;=E11,"OK","CHECK"))</x:f>
-        <x:v>COMPLETE</x:v>
-      </x:c>
-      <x:c r="G11" s="33" t="str">
-        <x:v>2 Bond Pricing · settlement is a coupon date</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" ht="27" customHeight="1">
-      <x:c r="A12" s="2" t="str">
-        <x:v>Gross proceeds calculation</x:v>
-      </x:c>
-      <x:c r="B12" s="147" t="n">
-        <x:f>'2 Bond Pricing'!B25</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C12" s="147" t="str">
-        <x:f>IF('2 Bond Pricing'!B22="","",'2 Bond Pricing'!B22*'2 Bond Pricing'!B8/1000)</x:f>
-      </x:c>
-      <x:c r="D12" s="147" t="str">
-        <x:f>IF(OR(NOT(ISNUMBER(B12)),NOT(ISNUMBER(C12))),"",B12-C12)</x:f>
-      </x:c>
-      <x:c r="E12" s="147" t="n">
-        <x:v>0.1</x:v>
-      </x:c>
-      <x:c r="F12" s="32" t="str">
-        <x:f>IF(OR(NOT(ISNUMBER(B12)),NOT(ISNUMBER(C12))),"COMPLETE",IF(ABS(D12)&lt;=E12,"OK","CHECK"))</x:f>
-        <x:v>COMPLETE</x:v>
-      </x:c>
-      <x:c r="G12" s="33" t="str">
-        <x:v>Price × bonds ÷ 1,000</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" ht="27" customHeight="1">
-      <x:c r="A13" s="2" t="str">
-        <x:v>Scenario A sources and uses</x:v>
-      </x:c>
-      <x:c r="B13" s="147" t="str">
-        <x:f>IF(ISBLANK('3 Sources-Uses'!B14),"",'3 Sources-Uses'!B14)</x:f>
-      </x:c>
-      <x:c r="C13" s="147" t="n">
-        <x:f>0</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D13" s="147" t="str">
-        <x:f>IF(OR(NOT(ISNUMBER(B13)),NOT(ISNUMBER(C13))),"",B13-C13)</x:f>
-      </x:c>
-      <x:c r="E13" s="147" t="n">
-        <x:v>0.1</x:v>
-      </x:c>
-      <x:c r="F13" s="32" t="str">
-        <x:f>IF(OR(NOT(ISNUMBER(B13)),NOT(ISNUMBER(C13))),"COMPLETE",IF(ABS(D13)&lt;=E13,"OK","CHECK"))</x:f>
-        <x:v>COMPLETE</x:v>
-      </x:c>
-      <x:c r="G13" s="33" t="str">
-        <x:v>3 Sources-Uses</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" ht="27" customHeight="1">
-      <x:c r="A14" s="2" t="str">
-        <x:v>Scenario B sources and uses</x:v>
-      </x:c>
-      <x:c r="B14" s="147" t="str">
-        <x:f>IF(ISBLANK('3 Sources-Uses'!C14),"",'3 Sources-Uses'!C14)</x:f>
-      </x:c>
-      <x:c r="C14" s="147" t="n">
-        <x:f>0</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D14" s="147" t="str">
-        <x:f>IF(OR(NOT(ISNUMBER(B14)),NOT(ISNUMBER(C14))),"",B14-C14)</x:f>
-      </x:c>
-      <x:c r="E14" s="147" t="n">
-        <x:v>0.1</x:v>
-      </x:c>
-      <x:c r="F14" s="32" t="str">
-        <x:f>IF(OR(NOT(ISNUMBER(B14)),NOT(ISNUMBER(C14))),"COMPLETE",IF(ABS(D14)&lt;=E14,"OK","CHECK"))</x:f>
-        <x:v>COMPLETE</x:v>
-      </x:c>
-      <x:c r="G14" s="33" t="str">
-        <x:v>3 Sources-Uses</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" ht="27" customHeight="1">
-      <x:c r="A15" s="2" t="str">
-        <x:v>Scenario C sources and uses</x:v>
-      </x:c>
-      <x:c r="B15" s="147" t="str">
-        <x:f>IF(ISBLANK('3 Sources-Uses'!D14),"",'3 Sources-Uses'!D14)</x:f>
-      </x:c>
-      <x:c r="C15" s="147" t="n">
-        <x:f>0</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D15" s="147" t="str">
-        <x:f>IF(OR(NOT(ISNUMBER(B15)),NOT(ISNUMBER(C15))),"",B15-C15)</x:f>
-      </x:c>
-      <x:c r="E15" s="147" t="n">
-        <x:v>0.1</x:v>
-      </x:c>
-      <x:c r="F15" s="32" t="str">
-        <x:f>IF(OR(NOT(ISNUMBER(B15)),NOT(ISNUMBER(C15))),"COMPLETE",IF(ABS(D15)&lt;=E15,"OK","CHECK"))</x:f>
-        <x:v>COMPLETE</x:v>
-      </x:c>
-      <x:c r="G15" s="33" t="str">
-        <x:v>3 Sources-Uses</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16" ht="27" customHeight="1">
-      <x:c r="A16" s="2" t="str">
-        <x:v>Scenario A net proceeds deployed</x:v>
-      </x:c>
-      <x:c r="B16" s="147" t="str">
-        <x:f>IF(ISBLANK('3 Sources-Uses'!B18),"",'3 Sources-Uses'!B18)</x:f>
-      </x:c>
-      <x:c r="C16" s="147" t="n">
-        <x:f>0</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D16" s="147" t="str">
-        <x:f>IF(OR(NOT(ISNUMBER(B16)),NOT(ISNUMBER(C16))),"",B16-C16)</x:f>
-      </x:c>
-      <x:c r="E16" s="147" t="n">
-        <x:v>0.1</x:v>
-      </x:c>
-      <x:c r="F16" s="32" t="str">
-        <x:f>IF(OR(NOT(ISNUMBER(B16)),NOT(ISNUMBER(C16))),"COMPLETE",IF(ABS(D16)&lt;=E16,"OK","CHECK"))</x:f>
-        <x:v>COMPLETE</x:v>
-      </x:c>
-      <x:c r="G16" s="33" t="str">
-        <x:v>Refi + CapEx + cash retained</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17" ht="27" customHeight="1">
-      <x:c r="A17" s="2" t="str">
-        <x:v>Scenario B net proceeds deployed</x:v>
-      </x:c>
-      <x:c r="B17" s="147" t="str">
-        <x:f>IF(ISBLANK('3 Sources-Uses'!C18),"",'3 Sources-Uses'!C18)</x:f>
-      </x:c>
-      <x:c r="C17" s="147" t="n">
-        <x:f>0</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D17" s="147" t="str">
-        <x:f>IF(OR(NOT(ISNUMBER(B17)),NOT(ISNUMBER(C17))),"",B17-C17)</x:f>
-      </x:c>
-      <x:c r="E17" s="147" t="n">
-        <x:v>0.1</x:v>
-      </x:c>
-      <x:c r="F17" s="32" t="str">
-        <x:f>IF(OR(NOT(ISNUMBER(B17)),NOT(ISNUMBER(C17))),"COMPLETE",IF(ABS(D17)&lt;=E17,"OK","CHECK"))</x:f>
-        <x:v>COMPLETE</x:v>
-      </x:c>
-      <x:c r="G17" s="33" t="str">
-        <x:v>Refi + CapEx + cash retained</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" ht="27" customHeight="1">
-      <x:c r="A18" s="2" t="str">
-        <x:v>Scenario C net proceeds deployed</x:v>
-      </x:c>
-      <x:c r="B18" s="147" t="str">
-        <x:f>IF(ISBLANK('3 Sources-Uses'!D18),"",'3 Sources-Uses'!D18)</x:f>
-      </x:c>
-      <x:c r="C18" s="147" t="n">
-        <x:f>0</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D18" s="147" t="str">
-        <x:f>IF(OR(NOT(ISNUMBER(B18)),NOT(ISNUMBER(C18))),"",B18-C18)</x:f>
-      </x:c>
-      <x:c r="E18" s="147" t="n">
-        <x:v>0.1</x:v>
-      </x:c>
-      <x:c r="F18" s="32" t="str">
-        <x:f>IF(OR(NOT(ISNUMBER(B18)),NOT(ISNUMBER(C18))),"COMPLETE",IF(ABS(D18)&lt;=E18,"OK","CHECK"))</x:f>
-        <x:v>COMPLETE</x:v>
-      </x:c>
-      <x:c r="G18" s="33" t="str">
-        <x:v>Refi + CapEx + cash retained</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" ht="27" customHeight="1">
-      <x:c r="A19" s="2" t="str">
-        <x:v>Scenario A debt face/carrying bridge</x:v>
-      </x:c>
-      <x:c r="B19" s="147" t="str">
-        <x:f>IF(ISBLANK('3 Sources-Uses'!B30),"",'3 Sources-Uses'!B30)</x:f>
-      </x:c>
-      <x:c r="C19" s="147" t="n">
-        <x:f>0</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D19" s="147" t="str">
-        <x:f>IF(OR(NOT(ISNUMBER(B19)),NOT(ISNUMBER(C19))),"",B19-C19)</x:f>
-      </x:c>
-      <x:c r="E19" s="147" t="n">
-        <x:v>0.1</x:v>
-      </x:c>
-      <x:c r="F19" s="32" t="str">
-        <x:f>IF(OR(NOT(ISNUMBER(B19)),NOT(ISNUMBER(C19))),"COMPLETE",IF(ABS(D19)&lt;=E19,"OK","CHECK"))</x:f>
-        <x:v>COMPLETE</x:v>
-      </x:c>
-      <x:c r="G19" s="33" t="str">
-        <x:v>Face − carrying − contra-debt</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="20" ht="27" customHeight="1">
-      <x:c r="A20" s="2" t="str">
-        <x:v>Scenario B debt face/carrying bridge</x:v>
-      </x:c>
-      <x:c r="B20" s="147" t="str">
-        <x:f>IF(ISBLANK('3 Sources-Uses'!C30),"",'3 Sources-Uses'!C30)</x:f>
-      </x:c>
-      <x:c r="C20" s="147" t="n">
-        <x:f>0</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D20" s="147" t="str">
-        <x:f>IF(OR(NOT(ISNUMBER(B20)),NOT(ISNUMBER(C20))),"",B20-C20)</x:f>
-      </x:c>
-      <x:c r="E20" s="147" t="n">
-        <x:v>0.1</x:v>
-      </x:c>
-      <x:c r="F20" s="32" t="str">
-        <x:f>IF(OR(NOT(ISNUMBER(B20)),NOT(ISNUMBER(C20))),"COMPLETE",IF(ABS(D20)&lt;=E20,"OK","CHECK"))</x:f>
-        <x:v>COMPLETE</x:v>
-      </x:c>
-      <x:c r="G20" s="33" t="str">
-        <x:v>Face − carrying − contra-debt</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="21" ht="27" customHeight="1">
-      <x:c r="A21" s="2" t="str">
-        <x:v>Scenario C debt face/carrying bridge</x:v>
-      </x:c>
-      <x:c r="B21" s="147" t="str">
-        <x:f>IF(ISBLANK('3 Sources-Uses'!D30),"",'3 Sources-Uses'!D30)</x:f>
-      </x:c>
-      <x:c r="C21" s="147" t="n">
-        <x:f>0</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D21" s="147" t="str">
-        <x:f>IF(OR(NOT(ISNUMBER(B21)),NOT(ISNUMBER(C21))),"",B21-C21)</x:f>
-      </x:c>
-      <x:c r="E21" s="147" t="n">
-        <x:v>0.1</x:v>
-      </x:c>
-      <x:c r="F21" s="32" t="str">
-        <x:f>IF(OR(NOT(ISNUMBER(B21)),NOT(ISNUMBER(C21))),"COMPLETE",IF(ABS(D21)&lt;=E21,"OK","CHECK"))</x:f>
-        <x:v>COMPLETE</x:v>
-      </x:c>
-      <x:c r="G21" s="33" t="str">
-        <x:v>Face − carrying − contra-debt</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="22" ht="27" customHeight="1">
-      <x:c r="A22" s="2" t="str">
-        <x:v>Scenario A balance sheet</x:v>
-      </x:c>
-      <x:c r="B22" s="147" t="str">
-        <x:f>IF(ISBLANK('4 Scenario Impact'!C27),"",'4 Scenario Impact'!C27)</x:f>
-      </x:c>
-      <x:c r="C22" s="147" t="n">
-        <x:f>0</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D22" s="147" t="str">
-        <x:f>IF(OR(NOT(ISNUMBER(B22)),NOT(ISNUMBER(C22))),"",B22-C22)</x:f>
-      </x:c>
-      <x:c r="E22" s="147" t="n">
-        <x:v>0.1</x:v>
-      </x:c>
-      <x:c r="F22" s="32" t="str">
-        <x:f>IF(OR(NOT(ISNUMBER(B22)),NOT(ISNUMBER(C22))),"COMPLETE",IF(ABS(D22)&lt;=E22,"OK","CHECK"))</x:f>
-        <x:v>COMPLETE</x:v>
-      </x:c>
-      <x:c r="G22" s="33" t="str">
-        <x:v>4 Scenario Impact</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="23" ht="27" customHeight="1">
-      <x:c r="A23" s="2" t="str">
-        <x:v>Scenario B balance sheet</x:v>
-      </x:c>
-      <x:c r="B23" s="147" t="str">
-        <x:f>IF(ISBLANK('4 Scenario Impact'!D27),"",'4 Scenario Impact'!D27)</x:f>
-      </x:c>
-      <x:c r="C23" s="147" t="n">
-        <x:f>0</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D23" s="147" t="str">
-        <x:f>IF(OR(NOT(ISNUMBER(B23)),NOT(ISNUMBER(C23))),"",B23-C23)</x:f>
-      </x:c>
-      <x:c r="E23" s="147" t="n">
-        <x:v>0.1</x:v>
-      </x:c>
-      <x:c r="F23" s="32" t="str">
-        <x:f>IF(OR(NOT(ISNUMBER(B23)),NOT(ISNUMBER(C23))),"COMPLETE",IF(ABS(D23)&lt;=E23,"OK","CHECK"))</x:f>
-        <x:v>COMPLETE</x:v>
-      </x:c>
-      <x:c r="G23" s="33" t="str">
-        <x:v>4 Scenario Impact</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="24" ht="27" customHeight="1">
-      <x:c r="A24" s="2" t="str">
-        <x:v>Scenario C balance sheet</x:v>
-      </x:c>
-      <x:c r="B24" s="147" t="str">
-        <x:f>IF(ISBLANK('4 Scenario Impact'!E27),"",'4 Scenario Impact'!E27)</x:f>
-      </x:c>
-      <x:c r="C24" s="147" t="n">
-        <x:f>0</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D24" s="147" t="str">
-        <x:f>IF(OR(NOT(ISNUMBER(B24)),NOT(ISNUMBER(C24))),"",B24-C24)</x:f>
-      </x:c>
-      <x:c r="E24" s="147" t="n">
-        <x:v>0.1</x:v>
-      </x:c>
-      <x:c r="F24" s="32" t="str">
-        <x:f>IF(OR(NOT(ISNUMBER(B24)),NOT(ISNUMBER(C24))),"COMPLETE",IF(ABS(D24)&lt;=E24,"OK","CHECK"))</x:f>
-        <x:v>COMPLETE</x:v>
-      </x:c>
-      <x:c r="G24" s="33" t="str">
-        <x:v>4 Scenario Impact</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="25" ht="27" customHeight="1">
-      <x:c r="A25" s="2" t="str">
-        <x:v>Scenario A ending ST debt</x:v>
-      </x:c>
-      <x:c r="B25" s="147" t="str">
-        <x:f>IF(ISBLANK('3 Sources-Uses'!B24),"",'3 Sources-Uses'!B24)</x:f>
-      </x:c>
-      <x:c r="C25" s="147" t="str">
-        <x:f>IF(OR(ISBLANK('3 Sources-Uses'!B22),ISBLANK('3 Sources-Uses'!B23)),"",'3 Sources-Uses'!B22-'3 Sources-Uses'!B23)</x:f>
-      </x:c>
-      <x:c r="D25" s="147" t="str">
-        <x:f>IF(OR(NOT(ISNUMBER(B25)),NOT(ISNUMBER(C25))),"",B25-C25)</x:f>
-      </x:c>
-      <x:c r="E25" s="147" t="n">
-        <x:v>0.1</x:v>
-      </x:c>
-      <x:c r="F25" s="32" t="str">
-        <x:f>IF(OR(NOT(ISNUMBER(B25)),NOT(ISNUMBER(C25))),"COMPLETE",IF(ABS(D25)&lt;=E25,"OK","CHECK"))</x:f>
-        <x:v>COMPLETE</x:v>
-      </x:c>
-      <x:c r="G25" s="33" t="str">
-        <x:v>Beginning ST − refinancing</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="26" ht="27" customHeight="1">
-      <x:c r="A26" s="2" t="str">
-        <x:v>Scenario B ending ST debt</x:v>
-      </x:c>
-      <x:c r="B26" s="147" t="str">
-        <x:f>IF(ISBLANK('3 Sources-Uses'!C24),"",'3 Sources-Uses'!C24)</x:f>
-      </x:c>
-      <x:c r="C26" s="147" t="str">
-        <x:f>IF(OR(ISBLANK('3 Sources-Uses'!C22),ISBLANK('3 Sources-Uses'!C23)),"",'3 Sources-Uses'!C22-'3 Sources-Uses'!C23)</x:f>
-      </x:c>
-      <x:c r="D26" s="147" t="str">
-        <x:f>IF(OR(NOT(ISNUMBER(B26)),NOT(ISNUMBER(C26))),"",B26-C26)</x:f>
-      </x:c>
-      <x:c r="E26" s="147" t="n">
-        <x:v>0.1</x:v>
-      </x:c>
-      <x:c r="F26" s="32" t="str">
-        <x:f>IF(OR(NOT(ISNUMBER(B26)),NOT(ISNUMBER(C26))),"COMPLETE",IF(ABS(D26)&lt;=E26,"OK","CHECK"))</x:f>
-        <x:v>COMPLETE</x:v>
-      </x:c>
-      <x:c r="G26" s="33" t="str">
-        <x:v>Beginning ST − refinancing</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="27" ht="27" customHeight="1">
-      <x:c r="A27" s="2" t="str">
-        <x:v>Scenario C ending ST debt</x:v>
-      </x:c>
-      <x:c r="B27" s="147" t="str">
-        <x:f>IF(ISBLANK('3 Sources-Uses'!D24),"",'3 Sources-Uses'!D24)</x:f>
-      </x:c>
-      <x:c r="C27" s="147" t="str">
-        <x:f>IF(OR(ISBLANK('3 Sources-Uses'!D22),ISBLANK('3 Sources-Uses'!D23)),"",'3 Sources-Uses'!D22-'3 Sources-Uses'!D23)</x:f>
-      </x:c>
-      <x:c r="D27" s="147" t="str">
-        <x:f>IF(OR(NOT(ISNUMBER(B27)),NOT(ISNUMBER(C27))),"",B27-C27)</x:f>
-      </x:c>
-      <x:c r="E27" s="147" t="n">
-        <x:v>0.1</x:v>
-      </x:c>
-      <x:c r="F27" s="32" t="str">
-        <x:f>IF(OR(NOT(ISNUMBER(B27)),NOT(ISNUMBER(C27))),"COMPLETE",IF(ABS(D27)&lt;=E27,"OK","CHECK"))</x:f>
-        <x:v>COMPLETE</x:v>
-      </x:c>
-      <x:c r="G27" s="33" t="str">
-        <x:v>Beginning ST − refinancing</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="28" ht="27" customHeight="1">
-      <x:c r="A28" s="2" t="str">
-        <x:v>Scenario A total interest expense</x:v>
-      </x:c>
-      <x:c r="B28" s="147" t="n">
-        <x:f>'4 Scenario Impact'!C38</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C28" s="147" t="str">
-        <x:f>IF(COUNT('4 Scenario Impact'!C35:C37)&lt;3,"",SUM('4 Scenario Impact'!C35:C37))</x:f>
-      </x:c>
-      <x:c r="D28" s="147" t="str">
-        <x:f>IF(OR(NOT(ISNUMBER(B28)),NOT(ISNUMBER(C28))),"",B28-C28)</x:f>
-      </x:c>
-      <x:c r="E28" s="147" t="n">
-        <x:v>0.1</x:v>
-      </x:c>
-      <x:c r="F28" s="32" t="str">
-        <x:f>IF(OR(NOT(ISNUMBER(B28)),NOT(ISNUMBER(C28))),"COMPLETE",IF(ABS(D28)&lt;=E28,"OK","CHECK"))</x:f>
-        <x:v>COMPLETE</x:v>
-      </x:c>
-      <x:c r="G28" s="33" t="str">
-        <x:v>ST + existing LT + new bond</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="29" ht="27" customHeight="1">
-      <x:c r="A29" s="2" t="str">
-        <x:v>Scenario B total interest expense</x:v>
-      </x:c>
-      <x:c r="B29" s="147" t="n">
-        <x:f>'4 Scenario Impact'!D38</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C29" s="147" t="str">
-        <x:f>IF(COUNT('4 Scenario Impact'!D35:D37)&lt;3,"",SUM('4 Scenario Impact'!D35:D37))</x:f>
-      </x:c>
-      <x:c r="D29" s="147" t="str">
-        <x:f>IF(OR(NOT(ISNUMBER(B29)),NOT(ISNUMBER(C29))),"",B29-C29)</x:f>
-      </x:c>
-      <x:c r="E29" s="147" t="n">
-        <x:v>0.1</x:v>
-      </x:c>
-      <x:c r="F29" s="32" t="str">
-        <x:f>IF(OR(NOT(ISNUMBER(B29)),NOT(ISNUMBER(C29))),"COMPLETE",IF(ABS(D29)&lt;=E29,"OK","CHECK"))</x:f>
-        <x:v>COMPLETE</x:v>
-      </x:c>
-      <x:c r="G29" s="33" t="str">
-        <x:v>ST + existing LT + new bond</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="30" ht="27" customHeight="1">
-      <x:c r="A30" s="2" t="str">
-        <x:v>Scenario C total interest expense</x:v>
-      </x:c>
-      <x:c r="B30" s="147" t="n">
-        <x:f>'4 Scenario Impact'!E38</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C30" s="147" t="str">
-        <x:f>IF(COUNT('4 Scenario Impact'!E35:E37)&lt;3,"",SUM('4 Scenario Impact'!E35:E37))</x:f>
-      </x:c>
-      <x:c r="D30" s="147" t="str">
-        <x:f>IF(OR(NOT(ISNUMBER(B30)),NOT(ISNUMBER(C30))),"",B30-C30)</x:f>
-      </x:c>
-      <x:c r="E30" s="147" t="n">
-        <x:v>0.1</x:v>
-      </x:c>
-      <x:c r="F30" s="32" t="str">
-        <x:f>IF(OR(NOT(ISNUMBER(B30)),NOT(ISNUMBER(C30))),"COMPLETE",IF(ABS(D30)&lt;=E30,"OK","CHECK"))</x:f>
-        <x:v>COMPLETE</x:v>
-      </x:c>
-      <x:c r="G30" s="33" t="str">
-        <x:v>ST + existing LT + new bond</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="31" ht="27" customHeight="1">
-      <x:c r="A31" s="2" t="str">
-        <x:v>Scenario A net income</x:v>
-      </x:c>
-      <x:c r="B31" s="147" t="n">
-        <x:f>'4 Scenario Impact'!C41</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C31" s="147" t="str">
-        <x:f>IF(OR('4 Scenario Impact'!C39="",'4 Scenario Impact'!C40=""),"",'4 Scenario Impact'!C39-'4 Scenario Impact'!C40)</x:f>
-      </x:c>
-      <x:c r="D31" s="147" t="str">
-        <x:f>IF(OR(NOT(ISNUMBER(B31)),NOT(ISNUMBER(C31))),"",B31-C31)</x:f>
-      </x:c>
-      <x:c r="E31" s="147" t="n">
-        <x:v>0.1</x:v>
-      </x:c>
-      <x:c r="F31" s="32" t="str">
-        <x:f>IF(OR(NOT(ISNUMBER(B31)),NOT(ISNUMBER(C31))),"COMPLETE",IF(ABS(D31)&lt;=E31,"OK","CHECK"))</x:f>
-        <x:v>COMPLETE</x:v>
-      </x:c>
-      <x:c r="G31" s="33" t="str">
-        <x:v>EBIT − interest − positive tax expense</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="32" ht="27" customHeight="1">
-      <x:c r="A32" s="2" t="str">
-        <x:v>Scenario B net income</x:v>
-      </x:c>
-      <x:c r="B32" s="147" t="n">
-        <x:f>'4 Scenario Impact'!D41</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C32" s="147" t="str">
-        <x:f>IF(OR('4 Scenario Impact'!D39="",'4 Scenario Impact'!D40=""),"",'4 Scenario Impact'!D39-'4 Scenario Impact'!D40)</x:f>
-      </x:c>
-      <x:c r="D32" s="147" t="str">
-        <x:f>IF(OR(NOT(ISNUMBER(B32)),NOT(ISNUMBER(C32))),"",B32-C32)</x:f>
-      </x:c>
-      <x:c r="E32" s="147" t="n">
-        <x:v>0.1</x:v>
-      </x:c>
-      <x:c r="F32" s="32" t="str">
-        <x:f>IF(OR(NOT(ISNUMBER(B32)),NOT(ISNUMBER(C32))),"COMPLETE",IF(ABS(D32)&lt;=E32,"OK","CHECK"))</x:f>
-        <x:v>COMPLETE</x:v>
-      </x:c>
-      <x:c r="G32" s="33" t="str">
-        <x:v>EBIT − interest − positive tax expense</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="33" ht="27" customHeight="1">
-      <x:c r="A33" s="2" t="str">
-        <x:v>Scenario C net income</x:v>
-      </x:c>
-      <x:c r="B33" s="147" t="n">
-        <x:f>'4 Scenario Impact'!E41</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="C33" s="147" t="str">
-        <x:f>IF(OR('4 Scenario Impact'!E39="",'4 Scenario Impact'!E40=""),"",'4 Scenario Impact'!E39-'4 Scenario Impact'!E40)</x:f>
-      </x:c>
-      <x:c r="D33" s="147" t="str">
-        <x:f>IF(OR(NOT(ISNUMBER(B33)),NOT(ISNUMBER(C33))),"",B33-C33)</x:f>
-      </x:c>
-      <x:c r="E33" s="147" t="n">
-        <x:v>0.1</x:v>
-      </x:c>
-      <x:c r="F33" s="32" t="str">
-        <x:f>IF(OR(NOT(ISNUMBER(B33)),NOT(ISNUMBER(C33))),"COMPLETE",IF(ABS(D33)&lt;=E33,"OK","CHECK"))</x:f>
-        <x:v>COMPLETE</x:v>
-      </x:c>
-      <x:c r="G33" s="33" t="str">
-        <x:v>EBIT − interest − positive tax expense</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="34" ht="27" customHeight="1">
-      <x:c r="A34" s="2" t="str">
-        <x:v>Scenario A closing equity unchanged</x:v>
-      </x:c>
-      <x:c r="B34" s="147" t="str">
-        <x:f>IF(ISBLANK('4 Scenario Impact'!C25),"",'4 Scenario Impact'!C25)</x:f>
-      </x:c>
-      <x:c r="C34" s="147" t="n">
-        <x:f>IF(ISBLANK('4 Scenario Impact'!B25),"",'4 Scenario Impact'!B25)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D34" s="147" t="str">
-        <x:f>IF(OR(NOT(ISNUMBER(B34)),NOT(ISNUMBER(C34))),"",B34-C34)</x:f>
-      </x:c>
-      <x:c r="E34" s="147" t="n">
-        <x:v>0.1</x:v>
-      </x:c>
-      <x:c r="F34" s="32" t="str">
-        <x:f>IF(OR(NOT(ISNUMBER(B34)),NOT(ISNUMBER(C34))),"COMPLETE",IF(ABS(D34)&lt;=E34,"OK","CHECK"))</x:f>
-        <x:v>COMPLETE</x:v>
-      </x:c>
-      <x:c r="G34" s="33" t="str">
-        <x:v>No equity issuance; closing timing</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="35" ht="27" customHeight="1">
-      <x:c r="A35" s="2" t="str">
-        <x:v>Scenario B closing equity unchanged</x:v>
-      </x:c>
-      <x:c r="B35" s="147" t="str">
-        <x:f>IF(ISBLANK('4 Scenario Impact'!D25),"",'4 Scenario Impact'!D25)</x:f>
-      </x:c>
-      <x:c r="C35" s="147" t="n">
-        <x:f>IF(ISBLANK('4 Scenario Impact'!B25),"",'4 Scenario Impact'!B25)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D35" s="147" t="str">
-        <x:f>IF(OR(NOT(ISNUMBER(B35)),NOT(ISNUMBER(C35))),"",B35-C35)</x:f>
-      </x:c>
-      <x:c r="E35" s="147" t="n">
-        <x:v>0.1</x:v>
-      </x:c>
-      <x:c r="F35" s="32" t="str">
-        <x:f>IF(OR(NOT(ISNUMBER(B35)),NOT(ISNUMBER(C35))),"COMPLETE",IF(ABS(D35)&lt;=E35,"OK","CHECK"))</x:f>
-        <x:v>COMPLETE</x:v>
-      </x:c>
-      <x:c r="G35" s="33" t="str">
-        <x:v>No equity issuance; closing timing</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="36" ht="27" customHeight="1">
-      <x:c r="A36" s="2" t="str">
-        <x:v>Scenario C closing equity unchanged</x:v>
-      </x:c>
-      <x:c r="B36" s="147" t="str">
-        <x:f>IF(ISBLANK('4 Scenario Impact'!E25),"",'4 Scenario Impact'!E25)</x:f>
-      </x:c>
-      <x:c r="C36" s="147" t="n">
-        <x:f>IF(ISBLANK('4 Scenario Impact'!B25),"",'4 Scenario Impact'!B25)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D36" s="147" t="str">
-        <x:f>IF(OR(NOT(ISNUMBER(B36)),NOT(ISNUMBER(C36))),"",B36-C36)</x:f>
-      </x:c>
-      <x:c r="E36" s="147" t="n">
-        <x:v>0.1</x:v>
-      </x:c>
-      <x:c r="F36" s="32" t="str">
-        <x:f>IF(OR(NOT(ISNUMBER(B36)),NOT(ISNUMBER(C36))),"COMPLETE",IF(ABS(D36)&lt;=E36,"OK","CHECK"))</x:f>
-        <x:v>COMPLETE</x:v>
-      </x:c>
-      <x:c r="G36" s="33" t="str">
-        <x:v>No equity issuance; closing timing</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="37" ht="27" customHeight="1">
-      <x:c r="A37" s="2" t="str">
-        <x:v>YIELD vs RATE from observed price</x:v>
-      </x:c>
-      <x:c r="B37" s="148" t="str">
-        <x:f>IF(ISBLANK('2 Bond Pricing'!B31),"",'2 Bond Pricing'!B31)</x:f>
-      </x:c>
-      <x:c r="C37" s="148" t="str">
-        <x:f>IF(ISBLANK('2 Bond Pricing'!B32),"",'2 Bond Pricing'!B32)</x:f>
-      </x:c>
-      <x:c r="D37" s="148" t="str">
-        <x:f>IF(OR(NOT(ISNUMBER(B37)),NOT(ISNUMBER(C37))),"",B37-C37)</x:f>
-      </x:c>
-      <x:c r="E37" s="148" t="n">
-        <x:v>0.000001</x:v>
-      </x:c>
-      <x:c r="F37" s="32" t="str">
-        <x:f>IF(OR(NOT(ISNUMBER(B37)),NOT(ISNUMBER(C37))),"COMPLETE",IF(ABS(D37)&lt;=E37,"OK","CHECK"))</x:f>
-        <x:v>COMPLETE</x:v>
-      </x:c>
-      <x:c r="G37" s="33" t="str">
-        <x:v>2 Bond Pricing · independent reverse-yield methods</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="38" ht="27" customHeight="1">
-      <x:c r="A38" s="2" t="str">
-        <x:v>Capacity sources and uses</x:v>
-      </x:c>
-      <x:c r="B38" s="147" t="str">
-        <x:f>IF(ISBLANK('5 Capacity-Decision'!B34),"",'5 Capacity-Decision'!B34)</x:f>
-      </x:c>
-      <x:c r="C38" s="147" t="n">
-        <x:f>0</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D38" s="147" t="str">
-        <x:f>IF(OR(NOT(ISNUMBER(B38)),NOT(ISNUMBER(C38))),"",B38-C38)</x:f>
-      </x:c>
-      <x:c r="E38" s="147" t="n">
-        <x:v>0.1</x:v>
-      </x:c>
-      <x:c r="F38" s="32" t="str">
-        <x:f>IF(OR(NOT(ISNUMBER(B38)),NOT(ISNUMBER(C38))),"COMPLETE",IF(ABS(D38)&lt;=E38,"OK","CHECK"))</x:f>
-        <x:v>COMPLETE</x:v>
-      </x:c>
-      <x:c r="G38" s="33" t="str">
-        <x:v>5 Capacity-Decision</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="39" ht="27" customHeight="1">
-      <x:c r="A39" s="2" t="str">
-        <x:v>Capacity Debt / EBITDA</x:v>
-      </x:c>
-      <x:c r="B39" s="149" t="str">
-        <x:f>IF(ISBLANK('5 Capacity-Decision'!B35),"",'5 Capacity-Decision'!B35)</x:f>
-      </x:c>
-      <x:c r="C39" s="149" t="n">
-        <x:f>'1 Assumptions-Baseline'!F48</x:f>
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D39" s="149" t="str">
-        <x:f>IF(OR(NOT(ISNUMBER(B39)),NOT(ISNUMBER(C39))),"",B39-C39)</x:f>
-      </x:c>
-      <x:c r="E39" s="149" t="n">
-        <x:v>0.0001</x:v>
-      </x:c>
-      <x:c r="F39" s="32" t="str">
-        <x:f>IF(OR(NOT(ISNUMBER(B39)),NOT(ISNUMBER(C39))),"COMPLETE",IF(ABS(D39)&lt;=E39,"OK","CHECK"))</x:f>
-        <x:v>COMPLETE</x:v>
-      </x:c>
-      <x:c r="G39" s="33" t="str">
-        <x:v>Must equal the binding 3.00x guardrail</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="40">
-      <x:c r="A40" s="2"/>
-      <x:c r="B40" s="2"/>
-      <x:c r="C40" s="2"/>
-      <x:c r="D40" s="2"/>
-      <x:c r="E40" s="2"/>
-      <x:c r="F40" s="2"/>
-      <x:c r="G40" s="2"/>
-    </x:row>
-    <x:row r="41">
-      <x:c r="A41" s="61" t="str">
-        <x:v>PASS means every required tie-out is complete within tolerance. It does not by itself prove the recommendation is economically sound; use the capacity analysis and explain the decision logic.</x:v>
-      </x:c>
-      <x:c r="B41" s="62"/>
-      <x:c r="C41" s="62"/>
-      <x:c r="D41" s="62"/>
-      <x:c r="E41" s="62"/>
-      <x:c r="F41" s="62"/>
-      <x:c r="G41" s="63"/>
-    </x:row>
-    <x:row r="42">
-      <x:c r="A42" s="64"/>
-      <x:c r="B42" s="65"/>
-      <x:c r="C42" s="65"/>
-      <x:c r="D42" s="65"/>
-      <x:c r="E42" s="65"/>
-      <x:c r="F42" s="65"/>
-      <x:c r="G42" s="66"/>
-    </x:row>
-    <x:row r="43">
-      <x:c r="A43" s="64"/>
-      <x:c r="B43" s="65"/>
-      <x:c r="C43" s="65"/>
-      <x:c r="D43" s="65"/>
-      <x:c r="E43" s="65"/>
-      <x:c r="F43" s="65"/>
-      <x:c r="G43" s="66"/>
-    </x:row>
-    <x:row r="44">
-      <x:c r="A44" s="67"/>
-      <x:c r="B44" s="68"/>
-      <x:c r="C44" s="68"/>
-      <x:c r="D44" s="68"/>
-      <x:c r="E44" s="68"/>
-      <x:c r="F44" s="68"/>
-      <x:c r="G44" s="69"/>
-    </x:row>
-  </x:sheetData>
-  <x:mergeCells>
-    <x:mergeCell ref="A1:G1"/>
-    <x:mergeCell ref="B3:D3"/>
-    <x:mergeCell ref="A5:G5"/>
-    <x:mergeCell ref="A41:G44"/>
-  </x:mergeCells>
-  <x:conditionalFormatting sqref="F7:F39">
-    <x:cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="OK"/>
-    <x:cfRule type="containsText" dxfId="1" priority="2" operator="containsText" text="CHECK"/>
-    <x:cfRule type="containsText" dxfId="2" priority="3" operator="containsText" text="COMPLETE"/>
-  </x:conditionalFormatting>
-  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</x:worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:sheetFormatPr defaultRowHeight="15"/>
-  <x:cols>
-    <x:col min="1" max="1" width="32" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="55" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="28" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="42" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="16" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="16" hidden="0" customWidth="1"/>
-  </x:cols>
-  <x:sheetData>
-    <x:row r="1" ht="30" customHeight="1">
-      <x:c r="A1" s="5" t="str">
-        <x:v>Bond Valuation, Interest Rates, and YTM</x:v>
-      </x:c>
-      <x:c r="B1" s="5"/>
-      <x:c r="C1" s="5"/>
-      <x:c r="D1" s="5"/>
-      <x:c r="E1" s="5"/>
-      <x:c r="F1" s="5"/>
-    </x:row>
-    <x:row r="2">
-      <x:c r="A2" s="2"/>
-      <x:c r="B2" s="2"/>
-      <x:c r="C2" s="2"/>
-      <x:c r="D2" s="2"/>
-      <x:c r="E2" s="2"/>
-      <x:c r="F2" s="2"/>
-    </x:row>
-    <x:row r="3">
-      <x:c r="A3" s="7" t="str">
-        <x:v>BUS311 · valuation-m02-l01 · display module M06 · FactSet required · student starter</x:v>
-      </x:c>
-      <x:c r="B3" s="7"/>
-      <x:c r="C3" s="7"/>
-      <x:c r="D3" s="7"/>
-      <x:c r="E3" s="7"/>
-      <x:c r="F3" s="7"/>
-    </x:row>
-    <x:row r="4">
-      <x:c r="A4" s="2"/>
-      <x:c r="B4" s="2"/>
-      <x:c r="C4" s="2"/>
-      <x:c r="D4" s="2"/>
-      <x:c r="E4" s="2"/>
-      <x:c r="F4" s="2"/>
-    </x:row>
-    <x:row r="5">
-      <x:c r="A5" s="38" t="str">
-        <x:v>Step</x:v>
-      </x:c>
-      <x:c r="B5" s="38" t="str">
-        <x:v>Required workflow</x:v>
-      </x:c>
-      <x:c r="C5" s="2"/>
-      <x:c r="D5" s="2"/>
-      <x:c r="E5" s="2"/>
-      <x:c r="F5" s="2"/>
-    </x:row>
-    <x:row r="6" ht="26" customHeight="1">
-      <x:c r="A6" s="32" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="B6" s="32" t="str">
-        <x:v>Read the lesson pre-reading and confirm FactSet access.</x:v>
-      </x:c>
-      <x:c r="C6" s="2"/>
-      <x:c r="D6" s="2"/>
-      <x:c r="E6" s="2"/>
-      <x:c r="F6" s="2"/>
-    </x:row>
-    <x:row r="7" ht="26" customHeight="1">
-      <x:c r="A7" s="32" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="B7" s="32" t="str">
-        <x:v>Enter or verify source values; keep units and periods consistent.</x:v>
-      </x:c>
-      <x:c r="C7" s="2"/>
-      <x:c r="D7" s="2"/>
-      <x:c r="E7" s="2"/>
-      <x:c r="F7" s="2"/>
-    </x:row>
-    <x:row r="8" ht="26" customHeight="1">
-      <x:c r="A8" s="32" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="B8" s="32" t="str">
-        <x:v>Document any live FactSet field, period, units, currency, and retrieval date below.</x:v>
-      </x:c>
-      <x:c r="C8" s="2"/>
-      <x:c r="D8" s="2"/>
-      <x:c r="E8" s="2"/>
-      <x:c r="F8" s="2"/>
-    </x:row>
-    <x:row r="9" ht="26" customHeight="1">
-      <x:c r="A9" s="32" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="B9" s="32" t="str">
-        <x:v>Complete calculations with visible, auditable Excel formulas.</x:v>
-      </x:c>
-      <x:c r="C9" s="2"/>
-      <x:c r="D9" s="2"/>
-      <x:c r="E9" s="2"/>
-      <x:c r="F9" s="2"/>
-    </x:row>
-    <x:row r="10" ht="26" customHeight="1">
-      <x:c r="A10" s="32" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="B10" s="32" t="str">
-        <x:v>Use the Checks sheet before stating a recommendation.</x:v>
-      </x:c>
-      <x:c r="C10" s="2"/>
-      <x:c r="D10" s="2"/>
-      <x:c r="E10" s="2"/>
-      <x:c r="F10" s="2"/>
-    </x:row>
-    <x:row r="11">
-      <x:c r="A11" s="2"/>
-      <x:c r="B11" s="2"/>
-      <x:c r="C11" s="2"/>
-      <x:c r="D11" s="2"/>
-      <x:c r="E11" s="2"/>
-      <x:c r="F11" s="2"/>
-    </x:row>
-    <x:row r="12">
-      <x:c r="A12" s="38" t="str">
-        <x:v>FactSet input</x:v>
-      </x:c>
-      <x:c r="B12" s="38" t="str">
-        <x:v>Field / definition</x:v>
-      </x:c>
-      <x:c r="C12" s="38" t="str">
-        <x:v>Period / units</x:v>
-      </x:c>
-      <x:c r="D12" s="38" t="str">
-        <x:v>Source note</x:v>
-      </x:c>
-      <x:c r="E12" s="2"/>
-      <x:c r="F12" s="2"/>
-    </x:row>
-    <x:row r="13" ht="28" customHeight="1">
-      <x:c r="A13" s="2" t="str">
-        <x:v>Company identifier</x:v>
-      </x:c>
-      <x:c r="B13" s="133"/>
-      <x:c r="C13" s="133"/>
-      <x:c r="D13" s="133"/>
-      <x:c r="E13" s="2"/>
-      <x:c r="F13" s="2"/>
-    </x:row>
-    <x:row r="14" ht="28" customHeight="1">
-      <x:c r="A14" s="2" t="str">
-        <x:v>Market or price input</x:v>
-      </x:c>
-      <x:c r="B14" s="133"/>
-      <x:c r="C14" s="133"/>
-      <x:c r="D14" s="133"/>
-      <x:c r="E14" s="2"/>
-      <x:c r="F14" s="2"/>
-    </x:row>
-    <x:row r="15" ht="28" customHeight="1">
-      <x:c r="A15" s="2" t="str">
-        <x:v>Financial statement input</x:v>
-      </x:c>
-      <x:c r="B15" s="133"/>
-      <x:c r="C15" s="133"/>
-      <x:c r="D15" s="133"/>
-      <x:c r="E15" s="2"/>
-      <x:c r="F15" s="2"/>
-    </x:row>
-    <x:row r="16" ht="28" customHeight="1">
-      <x:c r="A16" s="2" t="str">
-        <x:v>Risk or discount-rate input</x:v>
-      </x:c>
-      <x:c r="B16" s="133"/>
-      <x:c r="C16" s="133"/>
-      <x:c r="D16" s="133"/>
-      <x:c r="E16" s="2"/>
-      <x:c r="F16" s="2"/>
-    </x:row>
-    <x:row r="17" ht="28" customHeight="1">
-      <x:c r="A17" s="2" t="str">
-        <x:v>Comparison-company input</x:v>
-      </x:c>
-      <x:c r="B17" s="133"/>
-      <x:c r="C17" s="133"/>
-      <x:c r="D17" s="133"/>
-      <x:c r="E17" s="2"/>
-      <x:c r="F17" s="2"/>
-    </x:row>
-    <x:row r="18">
-      <x:c r="A18" s="2"/>
-      <x:c r="B18" s="2"/>
-      <x:c r="C18" s="2"/>
-      <x:c r="D18" s="2"/>
-      <x:c r="E18" s="2"/>
-      <x:c r="F18" s="2"/>
-    </x:row>
-    <x:row r="19">
-      <x:c r="A19" s="38" t="str">
-        <x:v>Decision output</x:v>
-      </x:c>
-      <x:c r="B19" s="38" t="str">
-        <x:v>Response</x:v>
-      </x:c>
-      <x:c r="C19" s="2"/>
-      <x:c r="D19" s="2"/>
-      <x:c r="E19" s="2"/>
-      <x:c r="F19" s="2"/>
-    </x:row>
-    <x:row r="20" ht="30" customHeight="1">
-      <x:c r="A20" s="2" t="str">
-        <x:v>Recommendation</x:v>
-      </x:c>
-      <x:c r="B20" s="133"/>
-      <x:c r="C20" s="2"/>
-      <x:c r="D20" s="2"/>
-      <x:c r="E20" s="2"/>
-      <x:c r="F20" s="2"/>
-    </x:row>
-    <x:row r="21" ht="30" customHeight="1">
-      <x:c r="A21" s="2" t="str">
-        <x:v>Evidence from the model</x:v>
-      </x:c>
-      <x:c r="B21" s="133"/>
-      <x:c r="C21" s="2"/>
-      <x:c r="D21" s="2"/>
-      <x:c r="E21" s="2"/>
-      <x:c r="F21" s="2"/>
-    </x:row>
-    <x:row r="22" ht="30" customHeight="1">
-      <x:c r="A22" s="2" t="str">
-        <x:v>Primary risk or limitation</x:v>
-      </x:c>
-      <x:c r="B22" s="133"/>
-      <x:c r="C22" s="2"/>
-      <x:c r="D22" s="2"/>
-      <x:c r="E22" s="2"/>
-      <x:c r="F22" s="2"/>
-    </x:row>
-    <x:row r="23" ht="30" customHeight="1">
-      <x:c r="A23" s="2" t="str">
-        <x:v>Monitoring trigger</x:v>
-      </x:c>
-      <x:c r="B23" s="133"/>
-      <x:c r="C23" s="2"/>
-      <x:c r="D23" s="2"/>
-      <x:c r="E23" s="2"/>
-      <x:c r="F23" s="2"/>
-    </x:row>
-    <x:row r="24">
-      <x:c r="A24" s="2"/>
-      <x:c r="B24" s="2"/>
-      <x:c r="C24" s="2"/>
-      <x:c r="D24" s="2"/>
-      <x:c r="E24" s="2"/>
-      <x:c r="F24" s="2"/>
-    </x:row>
-    <x:row r="25">
-      <x:c r="A25" s="2"/>
-      <x:c r="B25" s="2"/>
-      <x:c r="C25" s="2"/>
-      <x:c r="D25" s="2"/>
-      <x:c r="E25" s="2"/>
-      <x:c r="F25" s="2"/>
-    </x:row>
-  </x:sheetData>
-  <x:mergeCells>
-    <x:mergeCell ref="A1:F1"/>
-    <x:mergeCell ref="A3:F3"/>
-  </x:mergeCells>
-  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</x:worksheet>
 </file>